--- a/Financial Analysis/Models (Tech).xlsx
+++ b/Financial Analysis/Models (Tech).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF40C99-7586-495B-936E-C90CBF9CD045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F59636-8A39-4951-882D-1BFC9A9993A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4E122305-8C8A-4700-8BB3-18DD9512A165}"/>
   </bookViews>
@@ -765,12 +765,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -784,6 +778,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -869,20 +869,20 @@
     <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -915,10 +915,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>205.35</v>
+            <v>198.81</v>
           </cell>
           <cell r="E3">
-            <v>45781</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45861</v>
@@ -926,7 +926,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>3067066.53</v>
+            <v>2969386.398</v>
           </cell>
         </row>
         <row r="8">
@@ -984,7 +984,7 @@
         </row>
         <row r="36">
           <cell r="BQ36">
-            <v>-0.16472620891373135</v>
+            <v>-0.13724926814765226</v>
           </cell>
         </row>
         <row r="37">
@@ -1012,18 +1012,18 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>559.39</v>
+            <v>568.04</v>
           </cell>
           <cell r="E3">
-            <v>45751</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
-            <v>45771</v>
+            <v>45862</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>507982.05899999995</v>
+            <v>515837.12399999989</v>
           </cell>
         </row>
         <row r="8">
@@ -1033,7 +1033,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>518890.05899999995</v>
+            <v>526745.12399999984</v>
           </cell>
         </row>
       </sheetData>
@@ -1088,7 +1088,7 @@
         </row>
         <row r="30">
           <cell r="AM30">
-            <v>-0.35142924937740316</v>
+            <v>-0.36130555561091737</v>
           </cell>
         </row>
         <row r="31">
@@ -1116,10 +1116,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>996.3</v>
+            <v>1194.18</v>
           </cell>
           <cell r="E3">
-            <v>45769</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45854</v>
@@ -1127,7 +1127,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>424124.91</v>
+            <v>508362.42600000004</v>
           </cell>
         </row>
         <row r="8">
@@ -1137,7 +1137,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>430770.91</v>
+            <v>515008.42600000004</v>
           </cell>
         </row>
       </sheetData>
@@ -1190,7 +1190,7 @@
         </row>
         <row r="53">
           <cell r="CE53">
-            <v>-0.45650787239829793</v>
+            <v>-0.5465665086255207</v>
           </cell>
         </row>
         <row r="54">
@@ -1218,10 +1218,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>253.63</v>
+            <v>277.49</v>
           </cell>
           <cell r="E3">
-            <v>45751</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45805</v>
@@ -1229,7 +1229,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>243738.43</v>
+            <v>266667.89</v>
           </cell>
         </row>
         <row r="8">
@@ -1239,7 +1239,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>233287.43</v>
+            <v>256216.89</v>
           </cell>
         </row>
       </sheetData>
@@ -1294,7 +1294,7 @@
         </row>
         <row r="37">
           <cell r="BM37">
-            <v>-0.42844692622181901</v>
+            <v>-0.47759196330548825</v>
           </cell>
         </row>
         <row r="38">
@@ -1322,10 +1322,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>245.15</v>
+            <v>291.27999999999997</v>
           </cell>
           <cell r="F3">
-            <v>45769</v>
+            <v>45804</v>
           </cell>
           <cell r="H3">
             <v>45856</v>
@@ -1333,7 +1333,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>171752.09</v>
+            <v>204070.76799999998</v>
           </cell>
         </row>
         <row r="8">
@@ -1343,7 +1343,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>172039.09</v>
+            <v>204357.76799999998</v>
           </cell>
         </row>
       </sheetData>
@@ -1398,12 +1398,12 @@
         </row>
         <row r="46">
           <cell r="AN46">
-            <v>0.20252062275431082</v>
+            <v>1.2077487874963433E-2</v>
           </cell>
         </row>
         <row r="47">
           <cell r="AN47" t="str">
-            <v>Slightly undervalued</v>
+            <v>Fairly valued</v>
           </cell>
         </row>
       </sheetData>
@@ -1426,10 +1426,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>112.86</v>
+            <v>127.59</v>
           </cell>
           <cell r="E3">
-            <v>45783</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45880</v>
@@ -1437,7 +1437,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>265074.28200000001</v>
+            <v>299670.63299999997</v>
           </cell>
         </row>
         <row r="8">
@@ -1447,7 +1447,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>259844.28200000001</v>
+            <v>294440.63299999997</v>
           </cell>
         </row>
       </sheetData>
@@ -1502,7 +1502,7 @@
         </row>
         <row r="32">
           <cell r="AZ32">
-            <v>-0.65985115258855642</v>
+            <v>-0.69912062921188567</v>
           </cell>
         </row>
         <row r="33">
@@ -1585,10 +1585,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>364.59</v>
+            <v>412.39</v>
           </cell>
           <cell r="E3">
-            <v>45751</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45820</v>
@@ -1596,7 +1596,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>158961.24</v>
+            <v>179802.04</v>
           </cell>
         </row>
         <row r="8">
@@ -1606,7 +1606,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>157681.24</v>
+            <v>178522.04</v>
           </cell>
         </row>
       </sheetData>
@@ -1659,12 +1659,12 @@
         </row>
         <row r="39">
           <cell r="BD39">
-            <v>-3.1856995145475464E-2</v>
+            <v>-0.14407415761800457</v>
           </cell>
         </row>
         <row r="40">
           <cell r="BD40" t="str">
-            <v>Fairly valued</v>
+            <v>Slightly overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1781,86 +1781,83 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>176.85</v>
+            <v>658.88</v>
           </cell>
           <cell r="E3">
-            <v>45772</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
-            <v>45867</v>
+            <v>45861</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>98045.64</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="D8">
-            <v>-27120</v>
+            <v>134740.96</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>125165.64</v>
+            <v>9337.5</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="5">
-          <cell r="Y5">
-            <v>20456</v>
+        <row r="3">
+          <cell r="AC3">
+            <v>15673</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="AC14">
+            <v>1138</v>
+          </cell>
+          <cell r="AD14">
+            <v>1714.8216375000011</v>
+          </cell>
+          <cell r="AE14">
+            <v>2705.1588352000008</v>
+          </cell>
+          <cell r="AF14">
+            <v>3302.4492121600006</v>
+          </cell>
+          <cell r="AG14">
+            <v>3926.5754672320013</v>
+          </cell>
+          <cell r="AN14">
+            <v>7420.0315107195465</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="AB18">
+            <v>0.12961541741280813</v>
+          </cell>
+          <cell r="AC18">
+            <v>0.18313580433305665</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="AC19">
+            <v>0.30141006827027372</v>
           </cell>
         </row>
         <row r="20">
-          <cell r="Y20">
-            <v>3131</v>
-          </cell>
-          <cell r="Z20">
-            <v>4134.5485600000011</v>
-          </cell>
-          <cell r="AA20">
-            <v>4434.1943512000025</v>
-          </cell>
-          <cell r="AB20">
-            <v>4673.9038504240007</v>
-          </cell>
-          <cell r="AC20">
-            <v>4878.0582544244799</v>
-          </cell>
-          <cell r="AJ20">
-            <v>5410.536198602269</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="X26">
-            <v>7.6450358008682384E-2</v>
-          </cell>
-          <cell r="Y26">
-            <v>7.1387419473105229E-2</v>
-          </cell>
-          <cell r="AM26">
+          <cell r="AQ20">
             <v>7.0000000000000007E-2</v>
           </cell>
         </row>
-        <row r="29">
-          <cell r="Y29">
-            <v>0.60828118889323424</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="Y31">
-            <v>0.28739734063355493</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="AM32">
-            <v>-0.57655076564752616</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="AM33" t="str">
-            <v>Heavily overvalued</v>
+        <row r="23">
+          <cell r="AC23">
+            <v>8.7092451987494421E-2</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="AQ27">
+            <v>-0.30747310836503361</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="AQ28" t="str">
+            <v>Overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1883,78 +1880,86 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>20.14</v>
+            <v>161.83000000000001</v>
           </cell>
           <cell r="E3">
-            <v>45771</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
-            <v>45862</v>
+            <v>45867</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>87468.02</v>
+            <v>89718.551999999996</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-24076</v>
+            <v>-27120</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>111544.02</v>
+            <v>116838.552</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="11">
-          <cell r="AE11">
-            <v>53101</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="AE24">
-            <v>-18756</v>
-          </cell>
-          <cell r="AF24">
-            <v>-2055.2711750000058</v>
-          </cell>
-          <cell r="AG24">
-            <v>727.91294399999822</v>
-          </cell>
-          <cell r="AH24">
-            <v>2613.394682207997</v>
-          </cell>
-          <cell r="AI24">
-            <v>3383.2235656655957</v>
-          </cell>
-          <cell r="AP24">
-            <v>6928.7986179926265</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="AD35">
-            <v>-0.13997525930155108</v>
-          </cell>
-          <cell r="AE35">
-            <v>-2.0782621523935951E-2</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="AS38">
-            <v>0.06</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="AS44">
-            <v>-0.37659448511523141</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="AS45" t="str">
-            <v>Overvalued</v>
+        <row r="5">
+          <cell r="Y5">
+            <v>20456</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="Y20">
+            <v>3131</v>
+          </cell>
+          <cell r="Z20">
+            <v>4134.5485600000011</v>
+          </cell>
+          <cell r="AA20">
+            <v>4434.1943512000025</v>
+          </cell>
+          <cell r="AB20">
+            <v>4673.9038504240007</v>
+          </cell>
+          <cell r="AC20">
+            <v>4878.0582544244799</v>
+          </cell>
+          <cell r="AJ20">
+            <v>5410.536198602269</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="X26">
+            <v>7.6450358008682384E-2</v>
+          </cell>
+          <cell r="Y26">
+            <v>7.1387419473105229E-2</v>
+          </cell>
+          <cell r="AM26">
+            <v>7.0000000000000007E-2</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="Y29">
+            <v>0.60828118889323424</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="Y31">
+            <v>0.28739734063355493</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="AM32">
+            <v>-0.53724898291271705</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="AM33" t="str">
+            <v>Heavily overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1977,18 +1982,18 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>100.63</v>
+            <v>138.85</v>
           </cell>
           <cell r="E3">
-            <v>45755</v>
+            <v>45806</v>
           </cell>
           <cell r="G3">
-            <v>45804</v>
+            <v>45889</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2464328.0699999998</v>
+            <v>3400297.65</v>
           </cell>
         </row>
         <row r="8">
@@ -2000,7 +2005,7 @@
       <sheetData sheetId="1">
         <row r="3">
           <cell r="Y3">
-            <v>198750.4</v>
+            <v>199812</v>
           </cell>
         </row>
         <row r="14">
@@ -2008,19 +2013,19 @@
             <v>72880</v>
           </cell>
           <cell r="Y14">
-            <v>104531.63087999998</v>
+            <v>101482</v>
           </cell>
           <cell r="Z14">
-            <v>138376.62797079998</v>
+            <v>135410.6400704</v>
           </cell>
           <cell r="AA14">
-            <v>154262.79080951604</v>
+            <v>150898.36641084799</v>
           </cell>
           <cell r="AB14">
-            <v>166521.33564958585</v>
+            <v>162871.73855803587</v>
           </cell>
           <cell r="AE14">
-            <v>187475.35501624318</v>
+            <v>183360.5549251223</v>
           </cell>
         </row>
         <row r="18">
@@ -2048,12 +2053,12 @@
         </row>
         <row r="26">
           <cell r="AL26">
-            <v>0.37440044199781752</v>
+            <v>-2.3831140218091185E-2</v>
           </cell>
         </row>
         <row r="27">
           <cell r="AL27" t="str">
-            <v>Undervalued</v>
+            <v>Fairly valued</v>
           </cell>
         </row>
       </sheetData>
@@ -2076,83 +2081,78 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>573.16999999999996</v>
+            <v>20.5</v>
           </cell>
           <cell r="E3">
-            <v>45777</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
-            <v>45861</v>
+            <v>45862</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>117213.26499999998</v>
+            <v>89031.5</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>-24076</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>9337.5</v>
+            <v>113107.5</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="3">
-          <cell r="AC3">
-            <v>15673</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="AC14">
-            <v>1138</v>
-          </cell>
-          <cell r="AD14">
-            <v>1714.8216375000011</v>
-          </cell>
-          <cell r="AE14">
-            <v>2705.1588352000008</v>
-          </cell>
-          <cell r="AF14">
-            <v>3302.4492121600006</v>
-          </cell>
-          <cell r="AG14">
-            <v>3926.5754672320013</v>
-          </cell>
-          <cell r="AN14">
-            <v>7420.0315107195465</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="AB18">
-            <v>0.12961541741280813</v>
-          </cell>
-          <cell r="AC18">
-            <v>0.18313580433305665</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="AC19">
-            <v>0.30141006827027372</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="AQ20">
-            <v>7.0000000000000007E-2</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="AC23">
-            <v>8.7092451987494421E-2</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="AQ27">
-            <v>-0.20391486232627898</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="AQ28" t="str">
-            <v>Slightly overvalued</v>
+        <row r="11">
+          <cell r="AE11">
+            <v>53101</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="AE24">
+            <v>-18756</v>
+          </cell>
+          <cell r="AF24">
+            <v>-2055.2711750000058</v>
+          </cell>
+          <cell r="AG24">
+            <v>727.91294399999822</v>
+          </cell>
+          <cell r="AH24">
+            <v>2613.394682207997</v>
+          </cell>
+          <cell r="AI24">
+            <v>3383.2235656655957</v>
+          </cell>
+          <cell r="AP24">
+            <v>6928.7986179926265</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="AD35">
+            <v>-0.13997525930155108</v>
+          </cell>
+          <cell r="AE35">
+            <v>-2.0782621523935951E-2</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="AS38">
+            <v>0.06</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="AS44">
+            <v>-0.38754209415711027</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="AS45" t="str">
+            <v>Overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -2175,10 +2175,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>62.89</v>
+            <v>71.069999999999993</v>
           </cell>
           <cell r="E3">
-            <v>45776</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45867</v>
@@ -2186,7 +2186,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>62210.788</v>
+            <v>70302.444000000003</v>
           </cell>
         </row>
         <row r="8">
@@ -2196,7 +2196,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>57803.788</v>
+            <v>65895.444000000003</v>
           </cell>
         </row>
       </sheetData>
@@ -2251,12 +2251,12 @@
         </row>
         <row r="29">
           <cell r="AX29">
-            <v>0.35514137882871299</v>
+            <v>0.16312964835446042</v>
           </cell>
         </row>
         <row r="30">
           <cell r="AX30" t="str">
-            <v>Undervalued</v>
+            <v>Slightly undervalued</v>
           </cell>
         </row>
       </sheetData>
@@ -2279,10 +2279,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>170.76</v>
+            <v>269.39999999999998</v>
           </cell>
           <cell r="E3">
-            <v>45751</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45784</v>
@@ -2290,7 +2290,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>43355.963999999993</v>
+            <v>68400.659999999989</v>
           </cell>
         </row>
         <row r="8">
@@ -2300,7 +2300,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>39046.16399999999</v>
+            <v>64090.859999999986</v>
           </cell>
         </row>
       </sheetData>
@@ -2315,19 +2315,19 @@
             <v>2578.7999999999997</v>
           </cell>
           <cell r="AI19">
-            <v>1236.7858699999997</v>
+            <v>1846.8473600000007</v>
           </cell>
           <cell r="AJ19">
-            <v>2030.6664069599997</v>
+            <v>2788.00629888</v>
           </cell>
           <cell r="AK19">
-            <v>2587.6999560556801</v>
+            <v>3451.5623911910393</v>
           </cell>
           <cell r="AL19">
-            <v>2936.7207553924445</v>
+            <v>3870.059668153528</v>
           </cell>
           <cell r="AS19">
-            <v>3789.7259638880496</v>
+            <v>4948.6247481145883</v>
           </cell>
         </row>
         <row r="23">
@@ -2345,12 +2345,12 @@
         </row>
         <row r="32">
           <cell r="AV32">
-            <v>-2.3447287090133662E-2</v>
+            <v>-0.2163449663847643</v>
           </cell>
         </row>
         <row r="33">
           <cell r="AV33" t="str">
-            <v>Fairly valued</v>
+            <v>Slightly overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -2373,55 +2373,55 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>138.38999999999999</v>
+            <v>205.72</v>
           </cell>
           <cell r="E3">
-            <v>45751</v>
+            <v>45805</v>
           </cell>
           <cell r="G3">
-            <v>45798</v>
+            <v>45889</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>45862.445999999989</v>
+            <v>68443.043999999994</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>3024.7000000000007</v>
+            <v>2593.2000000000003</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>42837.745999999985</v>
+            <v>65849.843999999997</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
           <cell r="AN3">
-            <v>7381.8418175999986</v>
+            <v>7462.6884287999992</v>
           </cell>
         </row>
         <row r="16">
           <cell r="AN16">
-            <v>-240.01066769136114</v>
+            <v>-104.65711413616123</v>
           </cell>
           <cell r="AO16">
-            <v>198.13126283928906</v>
+            <v>355.93835647866615</v>
           </cell>
           <cell r="AP16">
-            <v>506.19203596408926</v>
+            <v>670.48578238868038</v>
           </cell>
           <cell r="AQ16">
-            <v>771.45115546614261</v>
+            <v>940.00566118122208</v>
           </cell>
           <cell r="AR16">
-            <v>946.1797826811702</v>
+            <v>1112.4269691830461</v>
           </cell>
           <cell r="AY16">
-            <v>1331.4376511076018</v>
+            <v>1504.9271568131473</v>
           </cell>
         </row>
         <row r="20">
@@ -2444,7 +2444,7 @@
         </row>
         <row r="90">
           <cell r="AX90">
-            <v>-0.5208349517611679</v>
+            <v>-0.59373967106754755</v>
           </cell>
         </row>
       </sheetData>
@@ -2467,78 +2467,86 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>92.41</v>
-          </cell>
-          <cell r="F3">
-            <v>45751</v>
-          </cell>
-          <cell r="H3">
-            <v>45782</v>
+            <v>74.09</v>
+          </cell>
+          <cell r="E3">
+            <v>45781</v>
+          </cell>
+          <cell r="G3">
+            <v>45784</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>22880.716</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="D8">
-            <v>-14205.4</v>
+            <v>50255.246999999996</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="D6">
+            <v>4510.5</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>37086.116000000002</v>
+            <v>46751.446999999993</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
-          <cell r="Y3">
-            <v>10106</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="Y15">
-            <v>1570.3999999999994</v>
-          </cell>
-          <cell r="Z15">
-            <v>1591.795564100001</v>
-          </cell>
-          <cell r="AA15">
-            <v>1847.0743551644998</v>
-          </cell>
-          <cell r="AB15">
-            <v>1992.9255918762433</v>
-          </cell>
-          <cell r="AC15">
-            <v>2050.8211370533554</v>
-          </cell>
-          <cell r="AJ15">
-            <v>2328.3213452553787</v>
+          <cell r="AQ3">
+            <v>3602</v>
           </cell>
         </row>
         <row r="19">
-          <cell r="X19">
-            <v>7.562725611658272E-2</v>
-          </cell>
-          <cell r="Y19">
-            <v>4.6776599270798913E-2</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="AN21">
+          <cell r="AQ19">
+            <v>-935.1</v>
+          </cell>
+          <cell r="AR19">
+            <v>-645.97905000000014</v>
+          </cell>
+          <cell r="AS19">
+            <v>-190.06624810800022</v>
+          </cell>
+          <cell r="AT19">
+            <v>287.02723014899908</v>
+          </cell>
+          <cell r="AU19">
+            <v>778.71748128609477</v>
+          </cell>
+          <cell r="BB19">
+            <v>2894.0092545097446</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="AP23">
+            <v>0.25806741573033709</v>
+          </cell>
+          <cell r="AQ23">
+            <v>0.28679622749356937</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="AQ27">
+            <v>0.26724042198778453</v>
+          </cell>
+          <cell r="BE27">
             <v>0.08</v>
           </cell>
         </row>
-        <row r="27">
-          <cell r="AN27">
-            <v>-0.50305134589738842</v>
-          </cell>
-        </row>
         <row r="28">
-          <cell r="AN28" t="str">
-            <v>Heavily overvalued</v>
+          <cell r="AQ28">
+            <v>-0.29516935036091063</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="BE33">
+            <v>-0.5028026588253911</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="BE34" t="str">
+            <v>Overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -2561,85 +2569,87 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>74.09</v>
+            <v>75</v>
           </cell>
           <cell r="E3">
-            <v>45781</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
-            <v>45784</v>
+            <v>45873</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>50255.246999999996</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="D6">
-            <v>4510.5</v>
+            <v>18502.5</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>-14026.8</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>46751.446999999993</v>
+            <v>32529.3</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
-          <cell r="AQ3">
-            <v>3602</v>
+          <cell r="Y3">
+            <v>10106</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="Y15">
+            <v>1570.3999999999994</v>
+          </cell>
+          <cell r="Z15">
+            <v>1583.1879707000001</v>
+          </cell>
+          <cell r="AA15">
+            <v>1815.8713334915003</v>
+          </cell>
+          <cell r="AB15">
+            <v>1958.8265588715878</v>
+          </cell>
+          <cell r="AC15">
+            <v>2015.8131094093987</v>
+          </cell>
+          <cell r="AJ15">
+            <v>2290.018738913438</v>
           </cell>
         </row>
         <row r="19">
-          <cell r="AQ19">
-            <v>-935.1</v>
-          </cell>
-          <cell r="AR19">
-            <v>-645.97905000000014</v>
-          </cell>
-          <cell r="AS19">
-            <v>-190.06624810800022</v>
-          </cell>
-          <cell r="AT19">
-            <v>287.02723014899908</v>
-          </cell>
-          <cell r="AU19">
-            <v>778.71748128609477</v>
-          </cell>
-          <cell r="BB19">
-            <v>2894.0092545097446</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="AP23">
-            <v>0.25806741573033709</v>
-          </cell>
-          <cell r="AQ23">
-            <v>0.28679622749356937</v>
+          <cell r="X19">
+            <v>7.562725611658272E-2</v>
+          </cell>
+          <cell r="Y19">
+            <v>4.6776599270798913E-2</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="Y20">
+            <v>0.6279339006530773</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="AN21">
+            <v>0.08</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="Y22">
+            <v>0.20389867405501677</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="AQ27">
-            <v>0.26724042198778453</v>
-          </cell>
-          <cell r="BE27">
-            <v>0.08</v>
+          <cell r="AN27">
+            <v>-0.39795366055345971</v>
           </cell>
         </row>
         <row r="28">
-          <cell r="AQ28">
-            <v>-0.29516935036091063</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="BE33">
-            <v>-0.5028026588253911</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="BE34" t="str">
+          <cell r="AN28" t="str">
             <v>Overvalued</v>
           </cell>
         </row>
@@ -2663,10 +2673,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>44.8</v>
+            <v>60.41</v>
           </cell>
           <cell r="E3">
-            <v>45779</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45870</v>
@@ -2674,7 +2684,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>27552</v>
+            <v>37152.15</v>
           </cell>
         </row>
         <row r="8">
@@ -2684,7 +2694,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>25571.599999999999</v>
+            <v>35171.75</v>
           </cell>
         </row>
       </sheetData>
@@ -2729,7 +2739,7 @@
         </row>
         <row r="42">
           <cell r="AN42">
-            <v>0.11667361343101468</v>
+            <v>-0.17187588343470517</v>
           </cell>
         </row>
         <row r="43">
@@ -2737,7 +2747,7 @@
             <v>0.36851967779247219</v>
           </cell>
           <cell r="AN43" t="str">
-            <v>Slightly undervalued</v>
+            <v>Slightly overvalued</v>
           </cell>
         </row>
         <row r="47">
@@ -2864,10 +2874,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>7.86</v>
+            <v>8.39</v>
           </cell>
           <cell r="E3">
-            <v>45777</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45867</v>
@@ -2875,7 +2885,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>13332.918</v>
+            <v>14231.957</v>
           </cell>
         </row>
         <row r="8">
@@ -2885,7 +2895,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>13738.918</v>
+            <v>14637.957</v>
           </cell>
         </row>
       </sheetData>
@@ -2940,7 +2950,7 @@
         </row>
         <row r="54">
           <cell r="BE54">
-            <v>-0.33764030354459329</v>
+            <v>-0.37948185767109699</v>
           </cell>
         </row>
       </sheetData>
@@ -3057,10 +3067,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>435.28</v>
+            <v>454.26</v>
           </cell>
           <cell r="E3">
-            <v>45781</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45868</v>
@@ -3068,7 +3078,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>3235218.5999999996</v>
+            <v>3376287.4499999997</v>
           </cell>
         </row>
         <row r="8">
@@ -3128,7 +3138,7 @@
         </row>
         <row r="28">
           <cell r="BI28">
-            <v>-0.1306971479613509</v>
+            <v>-0.16701856770267431</v>
           </cell>
         </row>
         <row r="29">
@@ -3156,10 +3166,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>486.42</v>
+            <v>528.66999999999996</v>
           </cell>
           <cell r="E3">
-            <v>45781</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45875</v>
@@ -3167,7 +3177,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>22132.11</v>
+            <v>24054.484999999997</v>
           </cell>
         </row>
         <row r="8">
@@ -3177,7 +3187,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>21049.510000000002</v>
+            <v>22971.884999999998</v>
           </cell>
         </row>
       </sheetData>
@@ -3229,12 +3239,12 @@
         </row>
         <row r="28">
           <cell r="AR28">
-            <v>-0.65814945001941016</v>
+            <v>-0.68546930122466088</v>
           </cell>
         </row>
         <row r="29">
           <cell r="AR29" t="str">
-            <v>Overvalued</v>
+            <v>Heavily overvalued</v>
           </cell>
         </row>
         <row r="43">
@@ -3262,10 +3272,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>12.7</v>
+            <v>13.43</v>
           </cell>
           <cell r="E3">
-            <v>45781</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45874</v>
@@ -3273,7 +3283,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>13944.599999999999</v>
+            <v>14746.14</v>
           </cell>
         </row>
         <row r="8">
@@ -3283,7 +3293,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>12121.699999999997</v>
+            <v>12923.239999999998</v>
           </cell>
         </row>
       </sheetData>
@@ -3338,7 +3348,7 @@
         </row>
         <row r="29">
           <cell r="AN29">
-            <v>-0.32894234972067471</v>
+            <v>-0.36541830539483011</v>
           </cell>
         </row>
         <row r="30">
@@ -3366,10 +3376,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>78.150000000000006</v>
+            <v>85.53</v>
           </cell>
           <cell r="E3">
-            <v>45781</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45866</v>
@@ -3377,7 +3387,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>11644.35</v>
+            <v>12743.97</v>
           </cell>
         </row>
         <row r="8">
@@ -3387,7 +3397,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>10141.15</v>
+            <v>11240.769999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -3442,12 +3452,12 @@
         </row>
         <row r="31">
           <cell r="BI31">
-            <v>-4.3547613894122761E-2</v>
+            <v>-0.12607559950690628</v>
           </cell>
         </row>
         <row r="32">
           <cell r="BI32" t="str">
-            <v>Fairly valued</v>
+            <v>Slightly overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -3564,10 +3574,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>82.36</v>
+            <v>90.43</v>
           </cell>
           <cell r="E3">
-            <v>45781</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45867</v>
@@ -3575,7 +3585,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>7338.2759999999998</v>
+            <v>8057.3130000000001</v>
           </cell>
         </row>
         <row r="8">
@@ -3585,7 +3595,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>9014.4760000000006</v>
+            <v>9733.5130000000008</v>
           </cell>
         </row>
       </sheetData>
@@ -3637,7 +3647,7 @@
         </row>
         <row r="36">
           <cell r="AO36">
-            <v>-0.35523475844729624</v>
+            <v>-0.41277379968726446</v>
           </cell>
         </row>
         <row r="37">
@@ -3665,87 +3675,87 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>149.62</v>
+            <v>70.45</v>
           </cell>
           <cell r="E3">
-            <v>45764</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
-            <v>45785</v>
+            <v>45869</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>8513.3780000000006</v>
+            <v>10327.969999999999</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>1262.8</v>
+            <v>2256.1</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>7250.5780000000004</v>
+            <v>8071.869999999999</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="3">
-          <cell r="AZ3">
-            <v>4727.8999999999996</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="AZ13">
-            <v>454.49999999999966</v>
-          </cell>
-          <cell r="BA13">
-            <v>449.57382599999983</v>
-          </cell>
-          <cell r="BB13">
-            <v>445.48834746</v>
-          </cell>
-          <cell r="BC13">
-            <v>441.07713379859996</v>
-          </cell>
-          <cell r="BD13">
-            <v>443.01880423842584</v>
-          </cell>
-          <cell r="BK13">
-            <v>451.90847390519497</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="AY17">
-            <v>-2.7815200945136453E-2</v>
-          </cell>
-          <cell r="AZ17">
-            <v>7.9735635859716769E-3</v>
+        <row r="5">
+          <cell r="AP5">
+            <v>4112.7</v>
           </cell>
         </row>
         <row r="18">
-          <cell r="AZ18">
-            <v>0.30677467797542246</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="AZ19">
-            <v>0.11516741047822494</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="BN20">
+          <cell r="AP18">
+            <v>-129.40000000000018</v>
+          </cell>
+          <cell r="AQ18">
+            <v>-8.2235920000007852</v>
+          </cell>
+          <cell r="AR18">
+            <v>196.63455295999964</v>
+          </cell>
+          <cell r="AS18">
+            <v>342.45798946879961</v>
+          </cell>
+          <cell r="AT18">
+            <v>465.99155682684778</v>
+          </cell>
+          <cell r="BA18">
+            <v>644.32339683926773</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="AO24">
+            <v>0.11452969584546024</v>
+          </cell>
+          <cell r="AP24">
+            <v>0.18018250688705217</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="BD26">
             <v>0.09</v>
           </cell>
         </row>
-        <row r="26">
-          <cell r="BN26">
-            <v>-0.29684783704459616</v>
-          </cell>
-        </row>
         <row r="27">
-          <cell r="BN27" t="str">
+          <cell r="AP27">
+            <v>0.43898169086001887</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="AP28">
+            <v>-5.3079485496146134E-2</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="BD32">
+            <v>-0.324767276419479</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="BD33" t="str">
             <v>Overvalued</v>
           </cell>
         </row>
@@ -3769,88 +3779,88 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>59.53</v>
+            <v>149.62</v>
           </cell>
           <cell r="E3">
-            <v>45783</v>
+            <v>45764</v>
           </cell>
           <cell r="G3">
-            <v>45869</v>
+            <v>45785</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>8727.098</v>
+            <v>8513.3780000000006</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>2256.1</v>
+            <v>1262.8</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>6470.9979999999996</v>
+            <v>7250.5780000000004</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="5">
-          <cell r="AP5">
-            <v>4112.7</v>
+        <row r="3">
+          <cell r="AZ3">
+            <v>4727.8999999999996</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="AZ13">
+            <v>454.49999999999966</v>
+          </cell>
+          <cell r="BA13">
+            <v>449.57382599999983</v>
+          </cell>
+          <cell r="BB13">
+            <v>445.48834746</v>
+          </cell>
+          <cell r="BC13">
+            <v>441.07713379859996</v>
+          </cell>
+          <cell r="BD13">
+            <v>443.01880423842584</v>
+          </cell>
+          <cell r="BK13">
+            <v>451.90847390519497</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="AY17">
+            <v>-2.7815200945136453E-2</v>
+          </cell>
+          <cell r="AZ17">
+            <v>7.9735635859716769E-3</v>
           </cell>
         </row>
         <row r="18">
-          <cell r="AP18">
-            <v>-129.40000000000018</v>
-          </cell>
-          <cell r="AQ18">
-            <v>-8.2235920000007852</v>
-          </cell>
-          <cell r="AR18">
-            <v>196.63455295999964</v>
-          </cell>
-          <cell r="AS18">
-            <v>342.45798946879961</v>
-          </cell>
-          <cell r="AT18">
-            <v>465.99155682684778</v>
-          </cell>
-          <cell r="BA18">
-            <v>644.32339683926773</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="AO24">
-            <v>0.11452969584546024</v>
-          </cell>
-          <cell r="AP24">
-            <v>0.18018250688705217</v>
+          <cell r="AZ18">
+            <v>0.30677467797542246</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="AZ19">
+            <v>0.11516741047822494</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="BN20">
+            <v>0.09</v>
           </cell>
         </row>
         <row r="26">
-          <cell r="BD26">
-            <v>0.09</v>
+          <cell r="BN26">
+            <v>-0.29684783704459616</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="AP27">
-            <v>0.43898169086001887</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="AP28">
-            <v>-5.3079485496146134E-2</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="BD32">
-            <v>-0.2009046635940247</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="BD33" t="str">
-            <v>Slightly overvalued</v>
+          <cell r="BN27" t="str">
+            <v>Overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -4175,10 +4185,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>165.81</v>
+            <v>172.63</v>
           </cell>
           <cell r="E3">
-            <v>45781</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45862</v>
@@ -4186,7 +4196,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2021223.9000000001</v>
+            <v>2104359.6999999997</v>
           </cell>
         </row>
         <row r="8">
@@ -4246,7 +4256,7 @@
         </row>
         <row r="39">
           <cell r="BI39">
-            <v>0.18618961424609415</v>
+            <v>0.13932746300263488</v>
           </cell>
         </row>
         <row r="40">
@@ -4274,7 +4284,7 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>22.57</v>
+            <v>47.13</v>
           </cell>
           <cell r="E3">
             <v>45729</v>
@@ -4285,17 +4295,17 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>4918.0030000000006</v>
+            <v>11678.814</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>364.29999999999995</v>
+            <v>697.19999999999993</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>4553.7030000000004</v>
+            <v>10981.614</v>
           </cell>
         </row>
       </sheetData>
@@ -4310,19 +4320,19 @@
             <v>-331.7</v>
           </cell>
           <cell r="AB18">
-            <v>-240.65150000000003</v>
+            <v>-241.196</v>
           </cell>
           <cell r="AC18">
-            <v>-249.37895000000003</v>
+            <v>-251.43716000000001</v>
           </cell>
           <cell r="AD18">
-            <v>-234.94165740000014</v>
+            <v>-239.27369940000014</v>
           </cell>
           <cell r="AE18">
-            <v>-201.95642231800011</v>
+            <v>-209.42086391800015</v>
           </cell>
           <cell r="AL18">
-            <v>471.97088145323158</v>
+            <v>414.20922455798171</v>
           </cell>
         </row>
         <row r="22">
@@ -4340,7 +4350,7 @@
         </row>
         <row r="30">
           <cell r="AP30">
-            <v>-0.68463910360246483</v>
+            <v>-0.84815666913938215</v>
           </cell>
         </row>
         <row r="31">
@@ -4368,7 +4378,7 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>8.98</v>
+            <v>11.17</v>
           </cell>
           <cell r="F3">
             <v>45730</v>
@@ -4379,7 +4389,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>9241.3179999999993</v>
+            <v>11495.046999999999</v>
           </cell>
         </row>
         <row r="8">
@@ -4389,7 +4399,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>4372.1179999999995</v>
+            <v>6625.8469999999988</v>
           </cell>
         </row>
       </sheetData>
@@ -4442,12 +4452,12 @@
         </row>
         <row r="42">
           <cell r="AE42">
-            <v>0.29282192477201852</v>
+            <v>3.9350123943842963E-2</v>
           </cell>
         </row>
         <row r="43">
           <cell r="AE43" t="str">
-            <v>Undervalued</v>
+            <v>Fairly valued</v>
           </cell>
         </row>
       </sheetData>
@@ -4569,28 +4579,28 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>13.77</v>
+            <v>13.28</v>
           </cell>
           <cell r="E3">
-            <v>45780</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
-            <v>45832</v>
+            <v>45882</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>4035.9870000000001</v>
+            <v>3715.7440000000001</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>-1257.5441696113076</v>
+            <v>-1344.0106007067136</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>5293.5311696113076</v>
+            <v>5059.754600706714</v>
           </cell>
         </row>
         <row r="13">
@@ -4610,19 +4620,19 @@
             <v>-1513.1999999999989</v>
           </cell>
           <cell r="AN18">
-            <v>2347.7740160000003</v>
+            <v>2482.4962560000022</v>
           </cell>
           <cell r="AO18">
-            <v>2787.1722259499988</v>
+            <v>3064.6565245799993</v>
           </cell>
           <cell r="AP18">
-            <v>3030.7280011533003</v>
+            <v>3337.690153690201</v>
           </cell>
           <cell r="AQ18">
-            <v>3213.3589068391652</v>
+            <v>3543.4832449213268</v>
           </cell>
           <cell r="AX18">
-            <v>3468.1040439939879</v>
+            <v>3844.7458015207562</v>
           </cell>
         </row>
         <row r="24">
@@ -4650,12 +4660,12 @@
         </row>
         <row r="31">
           <cell r="BC31">
-            <v>0.21988243594280066</v>
+            <v>0.44726581851393532</v>
           </cell>
         </row>
         <row r="32">
           <cell r="BC32" t="str">
-            <v>Slightly undervalued</v>
+            <v>Undervalued</v>
           </cell>
         </row>
       </sheetData>
@@ -4769,10 +4779,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>16.87</v>
+            <v>17.59</v>
           </cell>
           <cell r="E3">
-            <v>45776</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45890</v>
@@ -4780,7 +4790,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>1509.865</v>
+            <v>1574.3050000000001</v>
           </cell>
         </row>
         <row r="8">
@@ -4790,7 +4800,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>1383.0650000000001</v>
+            <v>1447.5050000000001</v>
           </cell>
         </row>
       </sheetData>
@@ -4845,7 +4855,7 @@
         </row>
         <row r="47">
           <cell r="AO47">
-            <v>0.11399138868960712</v>
+            <v>6.8393105582357894E-2</v>
           </cell>
         </row>
         <row r="48">
@@ -5150,28 +5160,28 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>12.25</v>
+            <v>12.02</v>
           </cell>
           <cell r="E3">
-            <v>45751</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
-            <v>45792</v>
+            <v>45883</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>426.29999999999995</v>
+            <v>427.91199999999998</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-9.2000000000000028</v>
+            <v>-67</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>435.49999999999994</v>
+            <v>494.91199999999998</v>
           </cell>
         </row>
       </sheetData>
@@ -5189,16 +5199,16 @@
             <v>44.091199999999979</v>
           </cell>
           <cell r="AA18">
-            <v>51.848129999999976</v>
+            <v>53.957115999999999</v>
           </cell>
           <cell r="AB18">
-            <v>55.878580949999979</v>
+            <v>59.411664090000002</v>
           </cell>
           <cell r="AC18">
-            <v>60.321196610999991</v>
+            <v>64.116644099999988</v>
           </cell>
           <cell r="AJ18">
-            <v>95.855297968775517</v>
+            <v>104.5201009457941</v>
           </cell>
         </row>
         <row r="22">
@@ -5226,7 +5236,7 @@
         </row>
         <row r="31">
           <cell r="AM31">
-            <v>0.5144913850915962</v>
+            <v>0.51669166859676285</v>
           </cell>
         </row>
         <row r="32">
@@ -5254,10 +5264,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>189.98</v>
+            <v>204.88</v>
           </cell>
           <cell r="E3">
-            <v>45781</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45869</v>
@@ -5265,7 +5275,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2016903.6719999998</v>
+            <v>2175088.0319999997</v>
           </cell>
         </row>
         <row r="8">
@@ -5325,7 +5335,7 @@
         </row>
         <row r="36">
           <cell r="BL36">
-            <v>4.0562329874762826E-2</v>
+            <v>-3.5113083611834073E-2</v>
           </cell>
         </row>
         <row r="37">
@@ -5353,28 +5363,28 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>6.1</v>
+            <v>8.4700000000000006</v>
           </cell>
           <cell r="E3">
-            <v>45751</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
-            <v>45777</v>
+            <v>45875</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>85.399999999999991</v>
+            <v>127.05000000000001</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-17.099999999999994</v>
+            <v>-21.599999999999994</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>102.49999999999999</v>
+            <v>148.65</v>
           </cell>
         </row>
       </sheetData>
@@ -5389,16 +5399,16 @@
             <v>3.1999999999999886</v>
           </cell>
           <cell r="AV23">
-            <v>0.61426499999996054</v>
+            <v>-2.171889999999951</v>
           </cell>
           <cell r="AW23">
-            <v>13.698367175999968</v>
+            <v>11.015718799999986</v>
           </cell>
           <cell r="AX23">
-            <v>17.129505912479978</v>
+            <v>14.285659768000007</v>
           </cell>
           <cell r="AY23">
-            <v>19.595469755830393</v>
+            <v>16.629577081600026</v>
           </cell>
         </row>
         <row r="31">
@@ -5416,12 +5426,12 @@
         </row>
         <row r="39">
           <cell r="BI39">
-            <v>0.51120802229567275</v>
+            <v>-0.18276999339899935</v>
           </cell>
         </row>
         <row r="40">
           <cell r="BI40" t="str">
-            <v>Heavily undervalued</v>
+            <v>Slightly overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -5505,28 +5515,28 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>0.56620000000000004</v>
+            <v>0.98009999999999997</v>
           </cell>
           <cell r="E3">
-            <v>45751</v>
+            <v>45799</v>
           </cell>
           <cell r="G3">
-            <v>45802</v>
+            <v>45880</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>59.507620000000003</v>
+            <v>104.47865999999999</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>401.09999999999997</v>
+            <v>63.900000000000006</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>-341.59237999999993</v>
+            <v>40.578659999999985</v>
           </cell>
         </row>
       </sheetData>
@@ -5536,44 +5546,44 @@
             <v>617.6</v>
           </cell>
         </row>
-        <row r="15">
-          <cell r="AD15">
+        <row r="16">
+          <cell r="AD16">
             <v>-29.899999999999945</v>
           </cell>
-          <cell r="AE15">
-            <v>-99.47824999999996</v>
-          </cell>
-          <cell r="AF15">
-            <v>-83.16289500000002</v>
-          </cell>
-          <cell r="AG15">
-            <v>-59.940097869999995</v>
-          </cell>
-          <cell r="AH15">
-            <v>-44.752185381000011</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="AC19">
+          <cell r="AE16">
+            <v>-76.877200000000073</v>
+          </cell>
+          <cell r="AF16">
+            <v>-44.391073200000065</v>
+          </cell>
+          <cell r="AG16">
+            <v>-18.839740000000013</v>
+          </cell>
+          <cell r="AH16">
+            <v>-1.8089114494499596</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="AC20">
             <v>-6.5727699530516381E-2</v>
           </cell>
-          <cell r="AD19">
+          <cell r="AD20">
             <v>-0.13791178112786151</v>
           </cell>
         </row>
-        <row r="21">
-          <cell r="AS21">
+        <row r="22">
+          <cell r="AS22">
             <v>0.12</v>
           </cell>
         </row>
-        <row r="27">
-          <cell r="AS27">
-            <v>0.25066821021641306</v>
-          </cell>
-        </row>
         <row r="28">
-          <cell r="AS28" t="str">
-            <v>Slightly undervalued</v>
+          <cell r="AS28">
+            <v>-9.9901697844603232E-2</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="AS29" t="str">
+            <v>Slightly overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -5784,10 +5794,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>3.72</v>
+            <v>5.6</v>
           </cell>
           <cell r="E3">
-            <v>45772</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45817</v>
@@ -5795,7 +5805,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>78.492000000000004</v>
+            <v>118.16</v>
           </cell>
         </row>
         <row r="8">
@@ -5805,7 +5815,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>-49.507999999999996</v>
+            <v>-9.8400000000000034</v>
           </cell>
         </row>
       </sheetData>
@@ -5852,12 +5862,12 @@
         </row>
         <row r="48">
           <cell r="AS48">
-            <v>0.5117314448778445</v>
+            <v>4.2216026688539632E-3</v>
           </cell>
         </row>
         <row r="49">
           <cell r="AS49" t="str">
-            <v>Heavily undervalued</v>
+            <v>Fairly valued</v>
           </cell>
         </row>
       </sheetData>
@@ -6068,10 +6078,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>597.02</v>
+            <v>640.84</v>
           </cell>
           <cell r="E3">
-            <v>45781</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45868</v>
@@ -6079,7 +6089,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>1508669.54</v>
+            <v>1619402.6800000002</v>
           </cell>
         </row>
         <row r="8">
@@ -6137,7 +6147,7 @@
         </row>
         <row r="25">
           <cell r="BI25">
-            <v>7.9710547986230784E-2</v>
+            <v>5.8810176623484978E-3</v>
           </cell>
         </row>
         <row r="26">
@@ -6165,10 +6175,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>256.58999999999997</v>
+            <v>348.37</v>
           </cell>
           <cell r="E3">
-            <v>45770</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45867</v>
@@ -6176,7 +6186,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>826476.3899999999</v>
+            <v>1122099.77</v>
           </cell>
         </row>
         <row r="8">
@@ -6186,7 +6196,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>797009.3899999999</v>
+            <v>1092632.77</v>
           </cell>
         </row>
       </sheetData>
@@ -6231,7 +6241,7 @@
         </row>
         <row r="37">
           <cell r="BJ37">
-            <v>-0.62575831274388716</v>
+            <v>-0.72435435160017803</v>
           </cell>
         </row>
         <row r="38">
@@ -6311,10 +6321,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>347.6</v>
+            <v>357.98</v>
           </cell>
           <cell r="E3">
-            <v>45781</v>
+            <v>45804</v>
           </cell>
           <cell r="G3">
             <v>45867</v>
@@ -6322,7 +6332,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>641356.76</v>
+            <v>660508.89800000004</v>
           </cell>
         </row>
         <row r="8">
@@ -6332,7 +6342,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>646897.76</v>
+            <v>666049.89800000004</v>
           </cell>
         </row>
       </sheetData>
@@ -6385,7 +6395,7 @@
             <v>0.65676668707899566</v>
           </cell>
           <cell r="AN30">
-            <v>-0.34683629154151641</v>
+            <v>-0.36577544818099084</v>
           </cell>
         </row>
         <row r="31">
@@ -6772,10 +6782,10 @@
       <c r="R2" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="S2" s="26" t="s">
+      <c r="S2" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="T2" s="26" t="s">
+      <c r="T2" s="25" t="s">
         <v>199</v>
       </c>
       <c r="U2" s="2" t="s">
@@ -6829,32 +6839,32 @@
       <c r="L3" s="2"/>
       <c r="M3" s="4">
         <f t="shared" ref="M3:R3" si="0">TRIMMEAN(M4:M1048576,80%)</f>
-        <v>22.679034854684605</v>
+        <v>24.283566190892213</v>
       </c>
       <c r="N3" s="4">
         <f t="shared" si="0"/>
-        <v>25.105121300587093</v>
+        <v>24.947525024826675</v>
       </c>
       <c r="O3" s="4">
         <f t="shared" si="0"/>
-        <v>19.070810881802391</v>
+        <v>21.008797522370536</v>
       </c>
       <c r="P3" s="4">
         <f t="shared" si="0"/>
-        <v>16.749983330221287</v>
+        <v>18.777044400924648</v>
       </c>
       <c r="Q3" s="4">
         <f t="shared" si="0"/>
-        <v>15.701174206326655</v>
+        <v>17.24060624063106</v>
       </c>
       <c r="R3" s="4">
         <f t="shared" si="0"/>
-        <v>13.481513827176512</v>
+        <v>14.85165507412399</v>
       </c>
       <c r="S3" s="23"/>
-      <c r="T3" s="32">
+      <c r="T3" s="31">
         <f t="shared" ref="T3:Z3" si="1">TRIMMEAN(T4:T1048576,80%)</f>
-        <v>3.4178769674376195</v>
+        <v>3.6446667598884601</v>
       </c>
       <c r="U3" s="5">
         <f t="shared" si="1"/>
@@ -6866,11 +6876,11 @@
       </c>
       <c r="W3" s="5">
         <f t="shared" si="1"/>
-        <v>0.57565628849809225</v>
+        <v>0.58157479121181299</v>
       </c>
       <c r="X3" s="5">
         <f t="shared" si="1"/>
-        <v>0.17183058360319287</v>
+        <v>0.17886489419918369</v>
       </c>
       <c r="Y3" s="5">
         <f t="shared" si="1"/>
@@ -6878,7 +6888,7 @@
       </c>
       <c r="Z3" s="5">
         <f t="shared" si="1"/>
-        <v>-0.12975489028566323</v>
+        <v>-0.19615953856979987</v>
       </c>
       <c r="AA3" s="14" t="str">
         <f>INDEX(AA4:AA60,MODE(MATCH(AA4:AA60,AA4:AA60,0)))</f>
@@ -6897,11 +6907,11 @@
       </c>
       <c r="D4" s="12">
         <f>[1]Main!$D$3</f>
-        <v>205.35</v>
+        <v>198.81</v>
       </c>
       <c r="E4" s="8">
         <f>[1]Main!$D$5</f>
-        <v>3067066.53</v>
+        <v>2969386.398</v>
       </c>
       <c r="F4" s="8">
         <f>[1]Main!$D$8</f>
@@ -6909,7 +6919,7 @@
       </c>
       <c r="G4" s="8">
         <f t="shared" ref="G4:G9" si="2">E4-F4</f>
-        <v>3032330.53</v>
+        <v>2934650.398</v>
       </c>
       <c r="H4" s="8">
         <f>[1]Model!BC17</f>
@@ -6933,35 +6943,35 @@
       </c>
       <c r="M4" s="9">
         <f t="shared" ref="M4:Q10" si="3">$G4/H4</f>
-        <v>32.349689873687801</v>
+        <v>31.307612848852095</v>
       </c>
       <c r="N4" s="9">
         <f t="shared" si="3"/>
-        <v>27.801377639411189</v>
+        <v>26.90581489955396</v>
       </c>
       <c r="O4" s="9">
         <f t="shared" si="3"/>
-        <v>27.16913086419067</v>
+        <v>26.293934620613815</v>
       </c>
       <c r="P4" s="9">
         <f t="shared" si="3"/>
-        <v>26.115584134987024</v>
+        <v>25.27432567706996</v>
       </c>
       <c r="Q4" s="9">
         <f t="shared" si="3"/>
-        <v>25.180067649368247</v>
+        <v>24.368944881772322</v>
       </c>
       <c r="R4" s="9">
         <f>G4/[1]Model!$BN$17</f>
-        <v>21.883175898130119</v>
+        <v>21.178255544243576</v>
       </c>
       <c r="S4" s="10">
         <f>[1]Model!$BC$5</f>
         <v>391035</v>
       </c>
-      <c r="T4" s="31">
+      <c r="T4" s="30">
         <f>G4/S4</f>
-        <v>7.7546269004053343</v>
+        <v>7.5048279514621452</v>
       </c>
       <c r="U4" s="11">
         <f>[1]Model!BB$30</f>
@@ -6985,7 +6995,7 @@
       </c>
       <c r="Z4" s="11">
         <f>[1]Model!$BQ$36</f>
-        <v>-0.16472620891373135</v>
+        <v>-0.13724926814765226</v>
       </c>
       <c r="AA4" s="11" t="str">
         <f>[1]Model!$BQ$37</f>
@@ -6999,7 +7009,7 @@
       </c>
       <c r="AE4" s="17">
         <f>[1]Main!$E$3</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="AF4" s="17">
         <f>[1]Main!$G$3</f>
@@ -7007,7 +7017,7 @@
       </c>
     </row>
     <row r="5" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -7015,11 +7025,11 @@
       </c>
       <c r="D5" s="12">
         <f>[2]Main!$D$3</f>
-        <v>100.63</v>
+        <v>138.85</v>
       </c>
       <c r="E5" s="8">
         <f>[2]Main!$D$5</f>
-        <v>2464328.0699999998</v>
+        <v>3400297.65</v>
       </c>
       <c r="F5" s="8">
         <f>[2]Main!$D$8</f>
@@ -7027,7 +7037,7 @@
       </c>
       <c r="G5" s="8">
         <f t="shared" si="2"/>
-        <v>2429581.0699999998</v>
+        <v>3365550.65</v>
       </c>
       <c r="H5" s="8">
         <f>[2]Model!X$14</f>
@@ -7035,51 +7045,51 @@
       </c>
       <c r="I5" s="8">
         <f>[2]Model!Y$14</f>
-        <v>104531.63087999998</v>
+        <v>101482</v>
       </c>
       <c r="J5" s="8">
         <f>[2]Model!Z$14</f>
-        <v>138376.62797079998</v>
+        <v>135410.6400704</v>
       </c>
       <c r="K5" s="8">
         <f>[2]Model!AA$14</f>
-        <v>154262.79080951604</v>
+        <v>150898.36641084799</v>
       </c>
       <c r="L5" s="8">
         <f>[2]Model!AB$14</f>
-        <v>166521.33564958585</v>
+        <v>162871.73855803587</v>
       </c>
       <c r="M5" s="9">
         <f t="shared" si="3"/>
-        <v>33.336732574094398</v>
+        <v>46.179344813391879</v>
       </c>
       <c r="N5" s="9">
         <f t="shared" si="3"/>
-        <v>23.242544381509799</v>
+        <v>33.164015786050726</v>
       </c>
       <c r="O5" s="9">
         <f t="shared" si="3"/>
-        <v>17.557741546590414</v>
+        <v>24.854403230427462</v>
       </c>
       <c r="P5" s="9">
         <f t="shared" si="3"/>
-        <v>15.749624762072733</v>
+        <v>22.303426670880466</v>
       </c>
       <c r="Q5" s="9">
         <f t="shared" si="3"/>
-        <v>14.590208879375167</v>
+        <v>20.663809939013806</v>
       </c>
       <c r="R5" s="9">
         <f>G5/[2]Model!$AE$14</f>
-        <v>12.959469098162245</v>
+        <v>18.354823649908603</v>
       </c>
       <c r="S5" s="10">
         <f>[2]Model!$Y$3</f>
-        <v>198750.4</v>
-      </c>
-      <c r="T5" s="31">
+        <v>199812</v>
+      </c>
+      <c r="T5" s="30">
         <f t="shared" ref="T5:T10" si="4">G5/S5</f>
-        <v>12.224282668110353</v>
+        <v>16.843586221047783</v>
       </c>
       <c r="U5" s="11">
         <f>[2]Model!W$18</f>
@@ -7103,11 +7113,11 @@
       </c>
       <c r="Z5" s="11">
         <f>[2]Model!$AL$26</f>
-        <v>0.37440044199781752</v>
+        <v>-2.3831140218091185E-2</v>
       </c>
       <c r="AA5" s="7" t="str">
         <f>[2]Model!$AL$27</f>
-        <v>Undervalued</v>
+        <v>Fairly valued</v>
       </c>
       <c r="AB5" s="7" t="s">
         <v>65</v>
@@ -7117,11 +7127,11 @@
       </c>
       <c r="AE5" s="17">
         <f>[2]Main!$E$3</f>
-        <v>45755</v>
+        <v>45806</v>
       </c>
       <c r="AF5" s="17">
         <f>[2]Main!$G$3</f>
-        <v>45804</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="6" spans="2:32" x14ac:dyDescent="0.3">
@@ -7133,11 +7143,11 @@
       </c>
       <c r="D6" s="12">
         <f>[3]Main!$D$3</f>
-        <v>435.28</v>
+        <v>454.26</v>
       </c>
       <c r="E6" s="8">
         <f>[3]Main!$D$5</f>
-        <v>3235218.5999999996</v>
+        <v>3376287.4499999997</v>
       </c>
       <c r="F6" s="8">
         <f>[3]Main!$D$8</f>
@@ -7145,7 +7155,7 @@
       </c>
       <c r="G6" s="8">
         <f t="shared" si="2"/>
-        <v>3193052.5999999996</v>
+        <v>3334121.4499999997</v>
       </c>
       <c r="H6" s="8">
         <f>[3]Model!AU17</f>
@@ -7169,35 +7179,35 @@
       </c>
       <c r="M6" s="9">
         <f t="shared" si="3"/>
-        <v>36.084583220323658</v>
+        <v>37.67879769008227</v>
       </c>
       <c r="N6" s="9">
         <f t="shared" si="3"/>
-        <v>31.844285444998913</v>
+        <v>33.251163843055288</v>
       </c>
       <c r="O6" s="9">
         <f t="shared" si="3"/>
-        <v>27.319142083457095</v>
+        <v>28.526099950890881</v>
       </c>
       <c r="P6" s="9">
         <f t="shared" si="3"/>
-        <v>25.254939527154363</v>
+        <v>26.370701063909255</v>
       </c>
       <c r="Q6" s="9">
         <f t="shared" si="3"/>
-        <v>23.74365363695042</v>
+        <v>24.792646664300772</v>
       </c>
       <c r="R6" s="9">
         <f>G6/[3]Model!$BF$17</f>
-        <v>19.110340230938036</v>
+        <v>19.954633782346228</v>
       </c>
       <c r="S6" s="10">
         <f>[3]Model!$AU$5</f>
         <v>239781</v>
       </c>
-      <c r="T6" s="31">
+      <c r="T6" s="30">
         <f t="shared" si="4"/>
-        <v>13.316537173504154</v>
+        <v>13.904860893899015</v>
       </c>
       <c r="U6" s="11">
         <f>[3]Model!AT$23</f>
@@ -7221,7 +7231,7 @@
       </c>
       <c r="Z6" s="11">
         <f>[3]Model!$BI$28</f>
-        <v>-0.1306971479613509</v>
+        <v>-0.16701856770267431</v>
       </c>
       <c r="AA6" s="11" t="str">
         <f>[3]Model!$BI$29</f>
@@ -7235,7 +7245,7 @@
       </c>
       <c r="AE6" s="17">
         <f>[3]Main!$E$3</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="AF6" s="17">
         <f>[3]Main!$G$3</f>
@@ -7243,7 +7253,7 @@
       </c>
     </row>
     <row r="7" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="26" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -7251,11 +7261,11 @@
       </c>
       <c r="D7" s="12">
         <f>[4]Main!$D$3</f>
-        <v>165.81</v>
+        <v>172.63</v>
       </c>
       <c r="E7" s="8">
         <f>[4]Main!$D$5</f>
-        <v>2021223.9000000001</v>
+        <v>2104359.6999999997</v>
       </c>
       <c r="F7" s="8">
         <f>[4]Main!$D$8</f>
@@ -7263,7 +7273,7 @@
       </c>
       <c r="G7" s="8">
         <f t="shared" si="2"/>
-        <v>1898467.9000000001</v>
+        <v>1981603.6999999997</v>
       </c>
       <c r="H7" s="8">
         <f>[4]Model!AU20</f>
@@ -7287,35 +7297,35 @@
       </c>
       <c r="M7" s="9">
         <f t="shared" si="3"/>
-        <v>18.962303481891368</v>
+        <v>19.792681635669908</v>
       </c>
       <c r="N7" s="9">
         <f t="shared" si="3"/>
-        <v>15.602014763380089</v>
+        <v>16.285242527708053</v>
       </c>
       <c r="O7" s="9">
         <f t="shared" si="3"/>
-        <v>15.434119342856945</v>
+        <v>16.10999479951538</v>
       </c>
       <c r="P7" s="9">
         <f t="shared" si="3"/>
-        <v>14.605780087929224</v>
+        <v>15.245381743682298</v>
       </c>
       <c r="Q7" s="9">
         <f t="shared" si="3"/>
-        <v>13.932011567150671</v>
+        <v>14.542108228381718</v>
       </c>
       <c r="R7" s="9">
         <f>G7/[4]Model!$BF$20</f>
-        <v>12.071901174109126</v>
+        <v>12.600541748769619</v>
       </c>
       <c r="S7" s="10">
         <f>[4]Model!$AU$10</f>
         <v>350018</v>
       </c>
-      <c r="T7" s="31">
+      <c r="T7" s="30">
         <f t="shared" si="4"/>
-        <v>5.4239150557971305</v>
+        <v>5.6614336976955464</v>
       </c>
       <c r="U7" s="11">
         <f>[4]Model!AT$30</f>
@@ -7339,7 +7349,7 @@
       </c>
       <c r="Z7" s="11">
         <f>[4]Model!$BI$39</f>
-        <v>0.18618961424609415</v>
+        <v>0.13932746300263488</v>
       </c>
       <c r="AA7" s="11" t="str">
         <f>[4]Model!$BI$40</f>
@@ -7353,7 +7363,7 @@
       </c>
       <c r="AE7" s="17">
         <f>[4]Main!$E$3</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="AF7" s="17">
         <f>[4]Main!$G$3</f>
@@ -7369,11 +7379,11 @@
       </c>
       <c r="D8" s="12">
         <f>[5]Main!$D$3</f>
-        <v>189.98</v>
+        <v>204.88</v>
       </c>
       <c r="E8" s="8">
         <f>[5]Main!$D$5</f>
-        <v>2016903.6719999998</v>
+        <v>2175088.0319999997</v>
       </c>
       <c r="F8" s="8">
         <f>[5]Main!$D$8</f>
@@ -7381,7 +7391,7 @@
       </c>
       <c r="G8" s="8">
         <f t="shared" si="2"/>
-        <v>1968324.6719999998</v>
+        <v>2126509.0319999997</v>
       </c>
       <c r="H8" s="8">
         <f>[5]Model!AX21</f>
@@ -7405,35 +7415,35 @@
       </c>
       <c r="M8" s="9">
         <f t="shared" si="3"/>
-        <v>33.221790980286251</v>
+        <v>35.891659330272745</v>
       </c>
       <c r="N8" s="9">
         <f t="shared" si="3"/>
-        <v>27.250164729306807</v>
+        <v>29.440123494199007</v>
       </c>
       <c r="O8" s="9">
         <f t="shared" si="3"/>
-        <v>21.779705060752718</v>
+        <v>23.53003047963967</v>
       </c>
       <c r="P8" s="9">
         <f t="shared" si="3"/>
-        <v>19.801673006849136</v>
+        <v>21.393033932247171</v>
       </c>
       <c r="Q8" s="9">
         <f t="shared" si="3"/>
-        <v>18.404002240228813</v>
+        <v>19.883039391580009</v>
       </c>
       <c r="R8" s="9">
         <f>G8/[5]Model!$BI$21</f>
-        <v>15.731749304775747</v>
+        <v>16.996030919926074</v>
       </c>
       <c r="S8" s="10">
         <f>[5]Model!$AX$5</f>
         <v>637959</v>
       </c>
-      <c r="T8" s="31">
+      <c r="T8" s="30">
         <f t="shared" si="4"/>
-        <v>3.0853466633435689</v>
+        <v>3.3333004660174081</v>
       </c>
       <c r="U8" s="11">
         <f>[5]Model!AW$27</f>
@@ -7457,7 +7467,7 @@
       </c>
       <c r="Z8" s="11">
         <f>[5]Model!$BL$36</f>
-        <v>4.0562329874762826E-2</v>
+        <v>-3.5113083611834073E-2</v>
       </c>
       <c r="AA8" s="7" t="str">
         <f>[5]Model!$BL$37</f>
@@ -7471,7 +7481,7 @@
       </c>
       <c r="AE8" s="17">
         <f>[5]Main!$E$3</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="AF8" s="17">
         <f>[5]Main!$G$3</f>
@@ -7487,11 +7497,11 @@
       </c>
       <c r="D9" s="12">
         <f>[6]Main!$D$3</f>
-        <v>597.02</v>
+        <v>640.84</v>
       </c>
       <c r="E9" s="8">
         <f>[6]Main!$D$5</f>
-        <v>1508669.54</v>
+        <v>1619402.6800000002</v>
       </c>
       <c r="F9" s="8">
         <f>[6]Main!$D$8</f>
@@ -7499,7 +7509,7 @@
       </c>
       <c r="G9" s="8">
         <f t="shared" si="2"/>
-        <v>1461100.54</v>
+        <v>1571833.6800000002</v>
       </c>
       <c r="H9" s="8">
         <f>[6]Model!AU13</f>
@@ -7523,35 +7533,35 @@
       </c>
       <c r="M9" s="9">
         <f t="shared" si="3"/>
-        <v>24.027307021871405</v>
+        <v>25.848276270350276</v>
       </c>
       <c r="N9" s="9">
         <f t="shared" si="3"/>
-        <v>21.06543545379672</v>
+        <v>22.66193189562696</v>
       </c>
       <c r="O9" s="9">
         <f t="shared" si="3"/>
-        <v>19.358339159330527</v>
+        <v>20.825459060810839</v>
       </c>
       <c r="P9" s="9">
         <f t="shared" si="3"/>
-        <v>18.233938688731076</v>
+        <v>19.615843102763172</v>
       </c>
       <c r="Q9" s="9">
         <f t="shared" si="3"/>
-        <v>17.367407823224127</v>
+        <v>18.683640039472692</v>
       </c>
       <c r="R9" s="9">
         <f>G9/[6]Model!$BF$13</f>
-        <v>15.707046930132082</v>
+        <v>16.897444564712991</v>
       </c>
       <c r="S9" s="10">
         <f>[6]Model!$AU$3</f>
         <v>164500</v>
       </c>
-      <c r="T9" s="31">
+      <c r="T9" s="30">
         <f t="shared" si="4"/>
-        <v>8.8820701519756842</v>
+        <v>9.5552199392097279</v>
       </c>
       <c r="U9" s="11">
         <f>[6]Model!AT$17</f>
@@ -7575,7 +7585,7 @@
       </c>
       <c r="Z9" s="11">
         <f>[6]Model!$BI$25</f>
-        <v>7.9710547986230784E-2</v>
+        <v>5.8810176623484978E-3</v>
       </c>
       <c r="AA9" s="11" t="str">
         <f>[6]Model!$BI$26</f>
@@ -7589,7 +7599,7 @@
       </c>
       <c r="AE9" s="17">
         <f>[6]Main!$E$3</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="AF9" s="17">
         <f>[6]Main!$G$3</f>
@@ -7605,11 +7615,11 @@
       </c>
       <c r="D10" s="12">
         <f>[7]Main!$D$3</f>
-        <v>256.58999999999997</v>
+        <v>348.37</v>
       </c>
       <c r="E10" s="8">
         <f>[7]Main!$D$5</f>
-        <v>826476.3899999999</v>
+        <v>1122099.77</v>
       </c>
       <c r="F10" s="8">
         <f>[7]Main!$D$8</f>
@@ -7617,7 +7627,7 @@
       </c>
       <c r="G10" s="8">
         <f>[7]Main!$D$9</f>
-        <v>797009.3899999999</v>
+        <v>1092632.77</v>
       </c>
       <c r="H10" s="8">
         <f>[7]Model!AV27</f>
@@ -7641,35 +7651,35 @@
       </c>
       <c r="M10" s="9">
         <f t="shared" si="3"/>
-        <v>112.39731913693413</v>
+        <v>154.08726131716261</v>
       </c>
       <c r="N10" s="9">
         <f t="shared" si="3"/>
-        <v>176.03852424968355</v>
+        <v>241.33399529664757</v>
       </c>
       <c r="O10" s="9">
         <f t="shared" si="3"/>
-        <v>99.926385108424967</v>
+        <v>136.99066074629954</v>
       </c>
       <c r="P10" s="9">
         <f t="shared" si="3"/>
-        <v>91.496881186706787</v>
+        <v>125.43452058625348</v>
       </c>
       <c r="Q10" s="9">
         <f t="shared" si="3"/>
-        <v>80.114895390360317</v>
+        <v>109.83077635839352</v>
       </c>
       <c r="R10" s="9">
         <f>G10/[7]Model!$BG$27</f>
-        <v>42.053420367444744</v>
+        <v>57.651698663243565</v>
       </c>
       <c r="S10" s="10">
         <f>[7]Model!$AV$9</f>
         <v>97690</v>
       </c>
-      <c r="T10" s="31">
+      <c r="T10" s="30">
         <f t="shared" si="4"/>
-        <v>8.1585565564540889</v>
+        <v>11.184694134507115</v>
       </c>
       <c r="U10" s="11">
         <f>[7]Model!AU$36</f>
@@ -7687,7 +7697,7 @@
       </c>
       <c r="Z10" s="11">
         <f>[7]Model!$BJ$37</f>
-        <v>-0.62575831274388716</v>
+        <v>-0.72435435160017803</v>
       </c>
       <c r="AA10" s="7" t="str">
         <f>[7]Model!$BJ$38</f>
@@ -7701,7 +7711,7 @@
       </c>
       <c r="AE10" s="17">
         <f>[7]Main!$E$3</f>
-        <v>45770</v>
+        <v>45804</v>
       </c>
       <c r="AF10" s="17">
         <f>[7]Main!$G$3</f>
@@ -7709,7 +7719,7 @@
       </c>
     </row>
     <row r="11" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="29" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -7781,11 +7791,11 @@
       </c>
       <c r="D12" s="12">
         <f>[9]Main!$D$3</f>
-        <v>347.6</v>
+        <v>357.98</v>
       </c>
       <c r="E12" s="8">
         <f>[9]Main!$D$5</f>
-        <v>641356.76</v>
+        <v>660508.89800000004</v>
       </c>
       <c r="F12" s="8">
         <f>[9]Main!$D$8</f>
@@ -7793,7 +7803,7 @@
       </c>
       <c r="G12" s="8">
         <f>[9]Main!$D$9</f>
-        <v>646897.76</v>
+        <v>666049.89800000004</v>
       </c>
       <c r="H12" s="8">
         <f>[9]Model!Y18</f>
@@ -7817,35 +7827,35 @@
       </c>
       <c r="M12" s="9">
         <f t="shared" ref="M12:Q17" si="5">$G12/H12</f>
-        <v>32.76593020310996</v>
+        <v>33.736002532543182</v>
       </c>
       <c r="N12" s="9">
         <f t="shared" si="5"/>
-        <v>33.366763156400246</v>
+        <v>34.354623823261562</v>
       </c>
       <c r="O12" s="9">
         <f t="shared" si="5"/>
-        <v>27.204807515757427</v>
+        <v>28.010236534100638</v>
       </c>
       <c r="P12" s="9">
         <f t="shared" si="5"/>
-        <v>25.88071881727199</v>
+        <v>26.646946695890076</v>
       </c>
       <c r="Q12" s="9">
         <f t="shared" si="5"/>
-        <v>25.122676239606569</v>
+        <v>25.866461412506638</v>
       </c>
       <c r="R12" s="9">
         <f>G12/[9]Model!$AJ$18</f>
-        <v>21.822498897485879</v>
+        <v>22.468578596988159</v>
       </c>
       <c r="S12" s="10">
         <f>[9]Model!$Y$3</f>
         <v>35926</v>
       </c>
-      <c r="T12" s="31">
+      <c r="T12" s="30">
         <f t="shared" ref="T12:T17" si="6">G12/S12</f>
-        <v>18.006395368256975</v>
+        <v>18.539495017536048</v>
       </c>
       <c r="U12" s="11">
         <f>[9]Model!X$22</f>
@@ -7869,7 +7879,7 @@
       </c>
       <c r="Z12" s="11">
         <f>[9]Model!$AN$30</f>
-        <v>-0.34683629154151641</v>
+        <v>-0.36577544818099084</v>
       </c>
       <c r="AA12" s="7" t="str">
         <f>[9]Model!$AN$31</f>
@@ -7883,7 +7893,7 @@
       </c>
       <c r="AE12" s="17">
         <f>[9]Main!$E$3</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="AF12" s="17">
         <f>[9]Main!$G$3</f>
@@ -7899,11 +7909,11 @@
       </c>
       <c r="D13" s="12">
         <f>[10]Main!$D$3</f>
-        <v>559.39</v>
+        <v>568.04</v>
       </c>
       <c r="E13" s="8">
         <f>[10]Main!$D$5</f>
-        <v>507982.05899999995</v>
+        <v>515837.12399999989</v>
       </c>
       <c r="F13" s="8">
         <f>[10]Main!$D$8</f>
@@ -7911,7 +7921,7 @@
       </c>
       <c r="G13" s="8">
         <f>[10]Main!$D$9</f>
-        <v>518890.05899999995</v>
+        <v>526745.12399999984</v>
       </c>
       <c r="H13" s="8">
         <f>[10]Model!Y17</f>
@@ -7935,35 +7945,35 @@
       </c>
       <c r="M13" s="9">
         <f t="shared" si="5"/>
-        <v>40.305271011340686</v>
+        <v>40.915420537517463</v>
       </c>
       <c r="N13" s="9">
         <f t="shared" si="5"/>
-        <v>36.45775768239762</v>
+        <v>37.009662756280484</v>
       </c>
       <c r="O13" s="9">
         <f t="shared" si="5"/>
-        <v>30.793104924521675</v>
+        <v>31.259257313719662</v>
       </c>
       <c r="P13" s="9">
         <f t="shared" si="5"/>
-        <v>28.474569521439314</v>
+        <v>28.905623442319925</v>
       </c>
       <c r="Q13" s="9">
         <f t="shared" si="5"/>
-        <v>26.838646512663114</v>
+        <v>27.244935492789807</v>
       </c>
       <c r="R13" s="9">
         <f>G13/[10]Model!$AJ$17</f>
-        <v>21.140243055262044</v>
+        <v>21.460268425636077</v>
       </c>
       <c r="S13" s="10">
         <f>[10]Model!$Y$3</f>
         <v>28167</v>
       </c>
-      <c r="T13" s="31">
+      <c r="T13" s="30">
         <f t="shared" si="6"/>
-        <v>18.421914261369686</v>
+        <v>18.700789008414095</v>
       </c>
       <c r="U13" s="11">
         <f>[10]Model!X$21</f>
@@ -7987,7 +7997,7 @@
       </c>
       <c r="Z13" s="11">
         <f>[10]Model!$AM$30</f>
-        <v>-0.35142924937740316</v>
+        <v>-0.36130555561091737</v>
       </c>
       <c r="AA13" s="7" t="str">
         <f>[10]Model!$AM$31</f>
@@ -8001,11 +8011,11 @@
       </c>
       <c r="AE13" s="17">
         <f>[10]Main!$E$3</f>
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="AF13" s="17">
         <f>[10]Main!$G$3</f>
-        <v>45771</v>
+        <v>45862</v>
       </c>
     </row>
     <row r="14" spans="2:32" x14ac:dyDescent="0.3">
@@ -8017,11 +8027,11 @@
       </c>
       <c r="D14" s="12">
         <f>[11]Main!$D$3</f>
-        <v>996.3</v>
+        <v>1194.18</v>
       </c>
       <c r="E14" s="8">
         <f>[11]Main!$D$5</f>
-        <v>424124.91</v>
+        <v>508362.42600000004</v>
       </c>
       <c r="F14" s="8">
         <f>[11]Main!$D$8</f>
@@ -8029,7 +8039,7 @@
       </c>
       <c r="G14" s="8">
         <f>[11]Main!$D$9</f>
-        <v>430770.91</v>
+        <v>515008.42600000004</v>
       </c>
       <c r="H14" s="8">
         <f>[11]Model!BM37</f>
@@ -8053,35 +8063,35 @@
       </c>
       <c r="M14" s="9">
         <f t="shared" si="5"/>
-        <v>156.20658882402003</v>
+        <v>186.75288319976795</v>
       </c>
       <c r="N14" s="9">
         <f t="shared" si="5"/>
-        <v>84.182624924273554</v>
+        <v>100.64458892732218</v>
       </c>
       <c r="O14" s="9">
         <f t="shared" si="5"/>
-        <v>95.901622957389066</v>
+        <v>114.65524422280608</v>
       </c>
       <c r="P14" s="9">
         <f t="shared" si="5"/>
-        <v>79.654384245562127</v>
+        <v>95.230848002958581</v>
       </c>
       <c r="Q14" s="9">
         <f t="shared" si="5"/>
-        <v>49.449102325688216</v>
+        <v>59.118904653672253</v>
       </c>
       <c r="R14" s="9">
         <f>G14/[11]Model!$BX$37</f>
-        <v>26.484273856565483</v>
+        <v>31.663289874013874</v>
       </c>
       <c r="S14" s="10">
         <f>[11]Model!$BM$26</f>
         <v>24992</v>
       </c>
-      <c r="T14" s="31">
+      <c r="T14" s="30">
         <f t="shared" si="6"/>
-        <v>17.236352032650448</v>
+        <v>20.606931258002561</v>
       </c>
       <c r="U14" s="11">
         <f>[11]Model!BL$47</f>
@@ -8105,7 +8115,7 @@
       </c>
       <c r="Z14" s="11">
         <f>[11]Model!$CE$53</f>
-        <v>-0.45650787239829793</v>
+        <v>-0.5465665086255207</v>
       </c>
       <c r="AA14" s="7" t="str">
         <f>[11]Model!$CE$54</f>
@@ -8119,7 +8129,7 @@
       </c>
       <c r="AE14" s="17">
         <f>[11]Main!$E$3</f>
-        <v>45769</v>
+        <v>45804</v>
       </c>
       <c r="AF14" s="17">
         <f>[11]Main!$G$3</f>
@@ -8127,7 +8137,7 @@
       </c>
     </row>
     <row r="15" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="29" t="s">
         <v>185</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -8135,11 +8145,11 @@
       </c>
       <c r="D15" s="12">
         <f>[12]Main!$D$3</f>
-        <v>253.63</v>
+        <v>277.49</v>
       </c>
       <c r="E15" s="8">
         <f>[12]Main!$D$5</f>
-        <v>243738.43</v>
+        <v>266667.89</v>
       </c>
       <c r="F15" s="8">
         <f>[12]Main!$D$8</f>
@@ -8147,7 +8157,7 @@
       </c>
       <c r="G15" s="8">
         <f>[12]Main!$D$9</f>
-        <v>233287.43</v>
+        <v>256216.89</v>
       </c>
       <c r="H15" s="8">
         <f>[12]Model!AY$20</f>
@@ -8171,35 +8181,35 @@
       </c>
       <c r="M15" s="9">
         <f t="shared" si="5"/>
-        <v>37.645220267871551</v>
+        <v>41.345310634177828</v>
       </c>
       <c r="N15" s="9">
         <f t="shared" si="5"/>
-        <v>35.281064328782605</v>
+        <v>38.748785471255857</v>
       </c>
       <c r="O15" s="9">
         <f t="shared" si="5"/>
-        <v>30.732109495991956</v>
+        <v>33.752720916864348</v>
       </c>
       <c r="P15" s="9">
         <f t="shared" si="5"/>
-        <v>27.82804399189488</v>
+        <v>30.563219314416092</v>
       </c>
       <c r="Q15" s="9">
         <f t="shared" si="5"/>
-        <v>26.836428631312494</v>
+        <v>29.474139616617339</v>
       </c>
       <c r="R15" s="9">
         <f>G15/[12]Model!$BJ$20</f>
-        <v>21.906850822622594</v>
+        <v>24.060041243826568</v>
       </c>
       <c r="S15" s="10">
         <f>[12]Model!$AY$5</f>
         <v>37895</v>
       </c>
-      <c r="T15" s="31">
+      <c r="T15" s="30">
         <f t="shared" si="6"/>
-        <v>6.156153318379733</v>
+        <v>6.7612320886660511</v>
       </c>
       <c r="U15" s="11">
         <f>[12]Model!AX$26</f>
@@ -8223,7 +8233,7 @@
       </c>
       <c r="Z15" s="11">
         <f>[12]Model!$BM$37</f>
-        <v>-0.42844692622181901</v>
+        <v>-0.47759196330548825</v>
       </c>
       <c r="AA15" s="7" t="str">
         <f>[12]Model!$BM$38</f>
@@ -8237,7 +8247,7 @@
       </c>
       <c r="AE15" s="17">
         <f>[12]Main!$E$3</f>
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="AF15" s="17">
         <f>[12]Main!$G$3</f>
@@ -8253,11 +8263,11 @@
       </c>
       <c r="D16" s="12">
         <f>[13]Main!$D$3</f>
-        <v>245.15</v>
+        <v>291.27999999999997</v>
       </c>
       <c r="E16" s="8">
         <f>[13]Main!$D$5</f>
-        <v>171752.09</v>
+        <v>204070.76799999998</v>
       </c>
       <c r="F16" s="8">
         <f>[13]Main!$D$8</f>
@@ -8265,7 +8275,7 @@
       </c>
       <c r="G16" s="8">
         <f>[13]Main!$D$9</f>
-        <v>172039.09</v>
+        <v>204357.76799999998</v>
       </c>
       <c r="H16" s="8">
         <f>[13]Model!Y27</f>
@@ -8289,35 +8299,35 @@
       </c>
       <c r="M16" s="9">
         <f t="shared" si="5"/>
-        <v>16.984805015302594</v>
+        <v>20.175512686346131</v>
       </c>
       <c r="N16" s="9">
         <f t="shared" si="5"/>
-        <v>15.981893492781067</v>
+        <v>18.984197618102158</v>
       </c>
       <c r="O16" s="9">
         <f t="shared" si="5"/>
-        <v>14.113605633757777</v>
+        <v>16.764939559648706</v>
       </c>
       <c r="P16" s="9">
         <f t="shared" si="5"/>
-        <v>13.674888263402625</v>
+        <v>16.243806237049711</v>
       </c>
       <c r="Q16" s="9">
         <f t="shared" si="5"/>
-        <v>13.362838189271637</v>
+        <v>15.873135497895932</v>
       </c>
       <c r="R16" s="9">
         <f>G16/[13]Model!$AJ$27</f>
-        <v>12.193096190769147</v>
+        <v>14.483649748175749</v>
       </c>
       <c r="S16" s="10">
         <f>[13]Model!$Y$16</f>
         <v>74201</v>
       </c>
-      <c r="T16" s="31">
+      <c r="T16" s="30">
         <f t="shared" si="6"/>
-        <v>2.3185548712281507</v>
+        <v>2.7541106993167204</v>
       </c>
       <c r="U16" s="11">
         <f>[13]Model!X$38</f>
@@ -8341,11 +8351,11 @@
       </c>
       <c r="Z16" s="11">
         <f>[13]Model!$AN$46</f>
-        <v>0.20252062275431082</v>
+        <v>1.2077487874963433E-2</v>
       </c>
       <c r="AA16" s="7" t="str">
         <f>[13]Model!$AN$47</f>
-        <v>Slightly undervalued</v>
+        <v>Fairly valued</v>
       </c>
       <c r="AB16" s="7" t="s">
         <v>94</v>
@@ -8355,7 +8365,7 @@
       </c>
       <c r="AE16" s="17">
         <f>[13]Main!$F$3</f>
-        <v>45769</v>
+        <v>45804</v>
       </c>
       <c r="AF16" s="17">
         <f>[13]Main!$H$3</f>
@@ -8363,7 +8373,7 @@
       </c>
     </row>
     <row r="17" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="27" t="s">
         <v>79</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -8371,11 +8381,11 @@
       </c>
       <c r="D17" s="12">
         <f>[14]Main!$D$3</f>
-        <v>112.86</v>
+        <v>127.59</v>
       </c>
       <c r="E17" s="8">
         <f>[14]Main!$D$5</f>
-        <v>265074.28200000001</v>
+        <v>299670.63299999997</v>
       </c>
       <c r="F17" s="8">
         <f>[14]Main!$D$8</f>
@@ -8383,7 +8393,7 @@
       </c>
       <c r="G17" s="8">
         <f>[14]Main!$D$9</f>
-        <v>259844.28200000001</v>
+        <v>294440.63299999997</v>
       </c>
       <c r="H17" s="8">
         <f>[14]Model!AL18</f>
@@ -8407,35 +8417,35 @@
       </c>
       <c r="M17" s="9">
         <f t="shared" si="5"/>
-        <v>559.88856280973903</v>
+        <v>634.43359836242155</v>
       </c>
       <c r="N17" s="9">
         <f t="shared" si="5"/>
-        <v>284.77376496185485</v>
+        <v>322.68929287873169</v>
       </c>
       <c r="O17" s="9">
         <f t="shared" si="5"/>
-        <v>184.45359494045692</v>
+        <v>209.0122316156787</v>
       </c>
       <c r="P17" s="9">
         <f t="shared" si="5"/>
-        <v>118.33048941345294</v>
+        <v>134.08532193945632</v>
       </c>
       <c r="Q17" s="9">
         <f t="shared" si="5"/>
-        <v>81.808667837708199</v>
+        <v>92.700889000211049</v>
       </c>
       <c r="R17" s="9">
         <f>G17/[14]Model!$AW$18</f>
-        <v>36.205411374657338</v>
+        <v>41.025895051943088</v>
       </c>
       <c r="S17" s="10">
         <f>[14]Model!$AL$3</f>
         <v>2865.4</v>
       </c>
-      <c r="T17" s="31">
+      <c r="T17" s="30">
         <f t="shared" si="6"/>
-        <v>90.683423605779296</v>
+        <v>102.757253088574</v>
       </c>
       <c r="U17" s="11">
         <f>[14]Model!AK$22</f>
@@ -8459,7 +8469,7 @@
       </c>
       <c r="Z17" s="11">
         <f>[14]Model!$AZ$32</f>
-        <v>-0.65985115258855642</v>
+        <v>-0.69912062921188567</v>
       </c>
       <c r="AA17" s="7" t="str">
         <f>[14]Model!$AZ$33</f>
@@ -8473,7 +8483,7 @@
       </c>
       <c r="AE17" s="17">
         <f>[14]Main!$E$3</f>
-        <v>45783</v>
+        <v>45804</v>
       </c>
       <c r="AF17" s="17">
         <f>[14]Main!$G$3</f>
@@ -8481,7 +8491,7 @@
       </c>
     </row>
     <row r="18" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="29" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="7" t="s">
@@ -8546,7 +8556,7 @@
       </c>
     </row>
     <row r="19" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -8554,11 +8564,11 @@
       </c>
       <c r="D19" s="12">
         <f>[16]Main!$D$3</f>
-        <v>364.59</v>
+        <v>412.39</v>
       </c>
       <c r="E19" s="8">
         <f>[16]Main!$D$5</f>
-        <v>158961.24</v>
+        <v>179802.04</v>
       </c>
       <c r="F19" s="8">
         <f>[16]Main!$D$8</f>
@@ -8566,7 +8576,7 @@
       </c>
       <c r="G19" s="8">
         <f>[16]Main!$D$9</f>
-        <v>157681.24</v>
+        <v>178522.04</v>
       </c>
       <c r="H19" s="8">
         <f>[16]Model!AP$24</f>
@@ -8590,35 +8600,35 @@
       </c>
       <c r="M19" s="9">
         <f t="shared" ref="M19:Q25" si="7">$G19/H19</f>
-        <v>28.359935251798561</v>
+        <v>32.108280575539567</v>
       </c>
       <c r="N19" s="9">
         <f t="shared" si="7"/>
-        <v>21.250898024142785</v>
+        <v>24.059638718606855</v>
       </c>
       <c r="O19" s="9">
         <f t="shared" si="7"/>
-        <v>18.368772604142503</v>
+        <v>20.796581493065585</v>
       </c>
       <c r="P19" s="9">
         <f t="shared" si="7"/>
-        <v>17.036984605852396</v>
+        <v>19.288770479515293</v>
       </c>
       <c r="Q19" s="9">
         <f t="shared" si="7"/>
-        <v>16.061449717403747</v>
+        <v>18.184298708637378</v>
       </c>
       <c r="R19" s="9">
         <f>G19/[16]Model!$BA$24</f>
-        <v>12.962246179758647</v>
+        <v>14.675472053572896</v>
       </c>
       <c r="S19" s="10">
         <f>[16]Model!$AP$6</f>
         <v>21505</v>
       </c>
-      <c r="T19" s="31">
+      <c r="T19" s="30">
         <f t="shared" ref="T19:T40" si="8">G19/S19</f>
-        <v>7.3323059753545685</v>
+        <v>8.3014201348523606</v>
       </c>
       <c r="U19" s="11">
         <f>[16]Model!$AO$31</f>
@@ -8642,11 +8652,11 @@
       </c>
       <c r="Z19" s="11">
         <f>[16]Model!$BD$39</f>
-        <v>-3.1856995145475464E-2</v>
+        <v>-0.14407415761800457</v>
       </c>
       <c r="AA19" s="7" t="str">
         <f>[16]Model!$BD$40</f>
-        <v>Fairly valued</v>
+        <v>Slightly overvalued</v>
       </c>
       <c r="AB19" s="7" t="s">
         <v>53</v>
@@ -8656,7 +8666,7 @@
       </c>
       <c r="AE19" s="17">
         <f>[16]Main!$E$3</f>
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="AF19" s="17">
         <f>[16]Main!$G$3</f>
@@ -8664,7 +8674,7 @@
       </c>
     </row>
     <row r="20" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="29" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="7" t="s">
@@ -8734,7 +8744,7 @@
         <f>[17]Model!$AD$3</f>
         <v>25785</v>
       </c>
-      <c r="T20" s="31">
+      <c r="T20" s="30">
         <f t="shared" si="8"/>
         <v>5.7456354469652906</v>
       </c>
@@ -8777,354 +8787,354 @@
     </row>
     <row r="21" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="D21" s="12">
         <f>[18]Main!$D$3</f>
-        <v>176.85</v>
+        <v>658.88</v>
       </c>
       <c r="E21" s="8">
         <f>[18]Main!$D$5</f>
-        <v>98045.64</v>
+        <v>134740.96</v>
       </c>
       <c r="F21" s="8">
-        <f>[18]Main!$D$8</f>
-        <v>-27120</v>
+        <f>[18]Main!$D$9</f>
+        <v>9337.5</v>
       </c>
       <c r="G21" s="8">
-        <f>[18]Main!$D$9</f>
-        <v>125165.64</v>
+        <f>E21-F21</f>
+        <v>125403.45999999999</v>
       </c>
       <c r="H21" s="8">
-        <f>[18]Model!Y$20</f>
-        <v>3131</v>
+        <f>[18]Model!AC14</f>
+        <v>1138</v>
       </c>
       <c r="I21" s="8">
-        <f>[18]Model!Z$20</f>
-        <v>4134.5485600000011</v>
+        <f>[18]Model!AD14</f>
+        <v>1714.8216375000011</v>
       </c>
       <c r="J21" s="8">
-        <f>[18]Model!AA$20</f>
-        <v>4434.1943512000025</v>
+        <f>[18]Model!AE14</f>
+        <v>2705.1588352000008</v>
       </c>
       <c r="K21" s="8">
-        <f>[18]Model!AB$20</f>
-        <v>4673.9038504240007</v>
+        <f>[18]Model!AF14</f>
+        <v>3302.4492121600006</v>
       </c>
       <c r="L21" s="8">
-        <f>[18]Model!AC$20</f>
-        <v>4878.0582544244799</v>
+        <f>[18]Model!AG14</f>
+        <v>3926.5754672320013</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" ref="M21" si="9">$G21/H21</f>
-        <v>39.976250399233471</v>
+        <f>$G21/H21</f>
+        <v>110.19636203866432</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" ref="N21" si="10">$G21/I21</f>
-        <v>30.273109188007691</v>
+        <f>$G21/I21</f>
+        <v>73.129156559292554</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" ref="O21" si="11">$G21/J21</f>
-        <v>28.227368961878518</v>
+        <f>$G21/J21</f>
+        <v>46.357152255988886</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" ref="P21" si="12">$G21/K21</f>
-        <v>26.779677974900018</v>
+        <f>$G21/K21</f>
+        <v>37.972865574510557</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" ref="Q21" si="13">$G21/L21</f>
-        <v>25.658906366374918</v>
+        <f>$G21/L21</f>
+        <v>31.93710678592964</v>
       </c>
       <c r="R21" s="9">
-        <f>G21/[18]Model!$AJ$20</f>
-        <v>23.133684981598435</v>
+        <f>G21/[18]Model!$AN$14</f>
+        <v>16.900664076538291</v>
       </c>
       <c r="S21" s="10">
-        <f>[18]Model!$Y$5</f>
-        <v>20456</v>
-      </c>
-      <c r="T21" s="31">
-        <f t="shared" si="8"/>
-        <v>6.1187739538521706</v>
+        <f>[18]Model!$AC$3</f>
+        <v>15673</v>
+      </c>
+      <c r="T21" s="30">
+        <f>G21/S21</f>
+        <v>8.0012416257257701</v>
       </c>
       <c r="U21" s="11">
-        <f>[18]Model!$X$26</f>
-        <v>7.6450358008682384E-2</v>
+        <f>[18]Model!AB$18</f>
+        <v>0.12961541741280813</v>
       </c>
       <c r="V21" s="11">
-        <f>[18]Model!$Y$26</f>
-        <v>7.1387419473105229E-2</v>
+        <f>[18]Model!AC$18</f>
+        <v>0.18313580433305665</v>
       </c>
       <c r="W21" s="11">
-        <f>[18]Model!$Y$29</f>
-        <v>0.60828118889323424</v>
+        <f>[18]Model!$AC$19</f>
+        <v>0.30141006827027372</v>
       </c>
       <c r="X21" s="11">
-        <f>[18]Model!$Y$31</f>
-        <v>0.28739734063355493</v>
+        <f>[18]Model!$AC$23</f>
+        <v>8.7092451987494421E-2</v>
       </c>
       <c r="Y21" s="11">
-        <f>[18]Model!$AM$26</f>
+        <f>[18]Model!$AQ$20</f>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="Z21" s="11">
-        <f>[18]Model!$AM$32</f>
-        <v>-0.57655076564752616</v>
+        <f>[18]Model!$AQ$27</f>
+        <v>-0.30747310836503361</v>
       </c>
       <c r="AA21" s="7" t="str">
-        <f>[18]Model!$AM$33</f>
-        <v>Heavily overvalued</v>
+        <f>[18]Model!$AQ$28</f>
+        <v>Overvalued</v>
       </c>
       <c r="AB21" s="7" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="AC21" s="7">
-        <v>1984</v>
+        <v>2007</v>
       </c>
       <c r="AE21" s="17">
         <f>[18]Main!$E$3</f>
-        <v>45772</v>
+        <v>45804</v>
       </c>
       <c r="AF21" s="17">
         <f>[18]Main!$G$3</f>
-        <v>45867</v>
+        <v>45861</v>
       </c>
     </row>
     <row r="22" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B22" s="27" t="s">
-        <v>22</v>
+      <c r="B22" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>34</v>
+        <v>196</v>
       </c>
       <c r="D22" s="12">
         <f>[19]Main!$D$3</f>
-        <v>20.14</v>
+        <v>161.83000000000001</v>
       </c>
       <c r="E22" s="8">
         <f>[19]Main!$D$5</f>
-        <v>87468.02</v>
+        <v>89718.551999999996</v>
       </c>
       <c r="F22" s="8">
         <f>[19]Main!$D$8</f>
-        <v>-24076</v>
+        <v>-27120</v>
       </c>
       <c r="G22" s="8">
         <f>[19]Main!$D$9</f>
-        <v>111544.02</v>
+        <v>116838.552</v>
       </c>
       <c r="H22" s="8">
-        <f>[19]Model!AE$24</f>
-        <v>-18756</v>
+        <f>[19]Model!Y$20</f>
+        <v>3131</v>
       </c>
       <c r="I22" s="8">
-        <f>[19]Model!AF$24</f>
-        <v>-2055.2711750000058</v>
+        <f>[19]Model!Z$20</f>
+        <v>4134.5485600000011</v>
       </c>
       <c r="J22" s="8">
-        <f>[19]Model!AG$24</f>
-        <v>727.91294399999822</v>
+        <f>[19]Model!AA$20</f>
+        <v>4434.1943512000025</v>
       </c>
       <c r="K22" s="8">
-        <f>[19]Model!AH$24</f>
-        <v>2613.394682207997</v>
+        <f>[19]Model!AB$20</f>
+        <v>4673.9038504240007</v>
       </c>
       <c r="L22" s="8">
-        <f>[19]Model!AI$24</f>
-        <v>3383.2235656655957</v>
+        <f>[19]Model!AC$20</f>
+        <v>4878.0582544244799</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="7"/>
-        <v>-5.9471113243762002</v>
+        <f t="shared" ref="M22" si="9">$G22/H22</f>
+        <v>37.316688597892046</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="7"/>
-        <v>-54.272166785971535</v>
+        <f t="shared" ref="N22" si="10">$G22/I22</f>
+        <v>28.259083260108078</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="7"/>
-        <v>153.23813227863175</v>
+        <f t="shared" ref="O22" si="11">$G22/J22</f>
+        <v>26.349443156090032</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="7"/>
-        <v>42.681658748061366</v>
+        <f t="shared" ref="P22" si="12">$G22/K22</f>
+        <v>24.998064945088846</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="7"/>
-        <v>32.969745520809376</v>
+        <f t="shared" ref="Q22" si="13">$G22/L22</f>
+        <v>23.951856641733521</v>
       </c>
       <c r="R22" s="9">
-        <f>G22/[19]Model!$AP$24</f>
-        <v>16.098609030192296</v>
+        <f>G22/[19]Model!$AJ$20</f>
+        <v>21.594634563240422</v>
       </c>
       <c r="S22" s="10">
-        <f>[19]Model!$AE$11</f>
-        <v>53101</v>
-      </c>
-      <c r="T22" s="31">
+        <f>[19]Model!$Y$5</f>
+        <v>20456</v>
+      </c>
+      <c r="T22" s="30">
         <f t="shared" si="8"/>
-        <v>2.1006011186230014</v>
+        <v>5.7117008212749312</v>
       </c>
       <c r="U22" s="11">
-        <f>[19]Model!AD$35</f>
-        <v>-0.13997525930155108</v>
+        <f>[19]Model!$X$26</f>
+        <v>7.6450358008682384E-2</v>
       </c>
       <c r="V22" s="11">
-        <f>[19]Model!AE$35</f>
-        <v>-2.0782621523935951E-2</v>
-      </c>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
+        <f>[19]Model!$Y$26</f>
+        <v>7.1387419473105229E-2</v>
+      </c>
+      <c r="W22" s="11">
+        <f>[19]Model!$Y$29</f>
+        <v>0.60828118889323424</v>
+      </c>
+      <c r="X22" s="11">
+        <f>[19]Model!$Y$31</f>
+        <v>0.28739734063355493</v>
+      </c>
       <c r="Y22" s="11">
-        <f>[19]Model!$AS$38</f>
-        <v>0.06</v>
+        <f>[19]Model!$AM$26</f>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Z22" s="11">
-        <f>[19]Model!$AS$44</f>
-        <v>-0.37659448511523141</v>
-      </c>
-      <c r="AA22" s="11" t="str">
-        <f>[19]Model!$AS$45</f>
-        <v>Overvalued</v>
+        <f>[19]Model!$AM$32</f>
+        <v>-0.53724898291271705</v>
+      </c>
+      <c r="AA22" s="7" t="str">
+        <f>[19]Model!$AM$33</f>
+        <v>Heavily overvalued</v>
       </c>
       <c r="AB22" s="7" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AC22" s="7">
-        <v>1968</v>
+        <v>1984</v>
       </c>
       <c r="AE22" s="17">
         <f>[19]Main!$E$3</f>
-        <v>45771</v>
+        <v>45804</v>
       </c>
       <c r="AF22" s="17">
         <f>[19]Main!$G$3</f>
-        <v>45862</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="23" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B23" s="6" t="s">
-        <v>135</v>
+      <c r="B23" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="D23" s="12">
         <f>[20]Main!$D$3</f>
-        <v>573.16999999999996</v>
+        <v>20.5</v>
       </c>
       <c r="E23" s="8">
         <f>[20]Main!$D$5</f>
-        <v>117213.26499999998</v>
+        <v>89031.5</v>
       </c>
       <c r="F23" s="8">
+        <f>[20]Main!$D$8</f>
+        <v>-24076</v>
+      </c>
+      <c r="G23" s="8">
         <f>[20]Main!$D$9</f>
-        <v>9337.5</v>
-      </c>
-      <c r="G23" s="8">
-        <f>E23-F23</f>
-        <v>107875.76499999998</v>
+        <v>113107.5</v>
       </c>
       <c r="H23" s="8">
-        <f>[20]Model!AC14</f>
-        <v>1138</v>
+        <f>[20]Model!AE$24</f>
+        <v>-18756</v>
       </c>
       <c r="I23" s="8">
-        <f>[20]Model!AD14</f>
-        <v>1714.8216375000011</v>
+        <f>[20]Model!AF$24</f>
+        <v>-2055.2711750000058</v>
       </c>
       <c r="J23" s="8">
-        <f>[20]Model!AE14</f>
-        <v>2705.1588352000008</v>
+        <f>[20]Model!AG$24</f>
+        <v>727.91294399999822</v>
       </c>
       <c r="K23" s="8">
-        <f>[20]Model!AF14</f>
-        <v>3302.4492121600006</v>
+        <f>[20]Model!AH$24</f>
+        <v>2613.394682207997</v>
       </c>
       <c r="L23" s="8">
-        <f>[20]Model!AG14</f>
-        <v>3926.5754672320013</v>
+        <f>[20]Model!AI$24</f>
+        <v>3383.2235656655957</v>
       </c>
       <c r="M23" s="9">
         <f t="shared" si="7"/>
-        <v>94.794169595782066</v>
+        <v>-6.0304702495201532</v>
       </c>
       <c r="N23" s="9">
         <f t="shared" si="7"/>
-        <v>62.907863209184583</v>
+        <v>-55.032883921023064</v>
       </c>
       <c r="O23" s="9">
         <f t="shared" si="7"/>
-        <v>39.877793346661065</v>
+        <v>155.38602649165182</v>
       </c>
       <c r="P23" s="9">
         <f t="shared" si="7"/>
-        <v>32.66538198461582</v>
+        <v>43.279915111956257</v>
       </c>
       <c r="Q23" s="9">
         <f t="shared" si="7"/>
-        <v>27.473243771893141</v>
+        <v>33.431872829174942</v>
       </c>
       <c r="R23" s="9">
-        <f>G23/[20]Model!$AN$14</f>
-        <v>14.538451062391633</v>
+        <f>G23/[20]Model!$AP$24</f>
+        <v>16.324258538310481</v>
       </c>
       <c r="S23" s="10">
-        <f>[20]Model!$AC$3</f>
-        <v>15673</v>
-      </c>
-      <c r="T23" s="31">
+        <f>[20]Model!$AE$11</f>
+        <v>53101</v>
+      </c>
+      <c r="T23" s="30">
         <f t="shared" si="8"/>
-        <v>6.8829046768327684</v>
+        <v>2.1300446319278357</v>
       </c>
       <c r="U23" s="11">
-        <f>[20]Model!AB$18</f>
-        <v>0.12961541741280813</v>
+        <f>[20]Model!AD$35</f>
+        <v>-0.13997525930155108</v>
       </c>
       <c r="V23" s="11">
-        <f>[20]Model!AC$18</f>
-        <v>0.18313580433305665</v>
-      </c>
-      <c r="W23" s="11">
-        <f>[20]Model!$AC$19</f>
-        <v>0.30141006827027372</v>
-      </c>
-      <c r="X23" s="11">
-        <f>[20]Model!$AC$23</f>
-        <v>8.7092451987494421E-2</v>
-      </c>
+        <f>[20]Model!AE$35</f>
+        <v>-2.0782621523935951E-2</v>
+      </c>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
       <c r="Y23" s="11">
-        <f>[20]Model!$AQ$20</f>
-        <v>7.0000000000000007E-2</v>
+        <f>[20]Model!$AS$38</f>
+        <v>0.06</v>
       </c>
       <c r="Z23" s="11">
-        <f>[20]Model!$AQ$27</f>
-        <v>-0.20391486232627898</v>
-      </c>
-      <c r="AA23" s="7" t="str">
-        <f>[20]Model!$AQ$28</f>
-        <v>Slightly overvalued</v>
+        <f>[20]Model!$AS$44</f>
+        <v>-0.38754209415711027</v>
+      </c>
+      <c r="AA23" s="11" t="str">
+        <f>[20]Model!$AS$45</f>
+        <v>Overvalued</v>
       </c>
       <c r="AB23" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AC23" s="7">
-        <v>2007</v>
+        <v>1968</v>
       </c>
       <c r="AE23" s="17">
         <f>[20]Main!$E$3</f>
-        <v>45777</v>
+        <v>45804</v>
       </c>
       <c r="AF23" s="17">
         <f>[20]Main!$G$3</f>
-        <v>45861</v>
+        <v>45862</v>
       </c>
     </row>
     <row r="24" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="26" t="s">
         <v>120</v>
       </c>
       <c r="C24" s="7" t="s">
@@ -9132,11 +9142,11 @@
       </c>
       <c r="D24" s="12">
         <f>[21]Main!$D$3</f>
-        <v>62.89</v>
+        <v>71.069999999999993</v>
       </c>
       <c r="E24" s="8">
         <f>[21]Main!$D$5</f>
-        <v>62210.788</v>
+        <v>70302.444000000003</v>
       </c>
       <c r="F24" s="8">
         <f>[21]Main!$D$8</f>
@@ -9144,7 +9154,7 @@
       </c>
       <c r="G24" s="8">
         <f>[21]Main!$D$9</f>
-        <v>57803.788</v>
+        <v>65895.444000000003</v>
       </c>
       <c r="H24" s="8">
         <f>[21]Model!AI17</f>
@@ -9168,35 +9178,35 @@
       </c>
       <c r="M24" s="9">
         <f t="shared" si="7"/>
-        <v>13.938699782975645</v>
+        <v>15.889906920665542</v>
       </c>
       <c r="N24" s="9">
         <f t="shared" si="7"/>
-        <v>11.210514069324915</v>
+        <v>12.779816472692275</v>
       </c>
       <c r="O24" s="9">
         <f t="shared" si="7"/>
-        <v>9.9078985858155821</v>
+        <v>11.294854524400545</v>
       </c>
       <c r="P24" s="9">
         <f t="shared" si="7"/>
-        <v>9.2392768852067348</v>
+        <v>10.532635899045834</v>
       </c>
       <c r="Q24" s="9">
         <f t="shared" si="7"/>
-        <v>8.997097926605214</v>
+        <v>10.256555549354827</v>
       </c>
       <c r="R24" s="9">
         <f>G24/[21]Model!$AT$17</f>
-        <v>8.2487928817653593</v>
+        <v>9.4034991168393312</v>
       </c>
       <c r="S24" s="10">
         <f>[21]Model!$AI$3</f>
         <v>31797</v>
       </c>
-      <c r="T24" s="31">
+      <c r="T24" s="30">
         <f t="shared" si="8"/>
-        <v>1.8179006824543196</v>
+        <v>2.0723792810642516</v>
       </c>
       <c r="U24" s="11">
         <f>[21]Model!AH$21</f>
@@ -9220,11 +9230,11 @@
       </c>
       <c r="Z24" s="11">
         <f>[21]Model!$AX$29</f>
-        <v>0.35514137882871299</v>
+        <v>0.16312964835446042</v>
       </c>
       <c r="AA24" s="7" t="str">
         <f>[21]Model!$AX$30</f>
-        <v>Undervalued</v>
+        <v>Slightly undervalued</v>
       </c>
       <c r="AB24" s="7" t="s">
         <v>94</v>
@@ -9234,7 +9244,7 @@
       </c>
       <c r="AE24" s="17">
         <f>[21]Main!$E$3</f>
-        <v>45776</v>
+        <v>45804</v>
       </c>
       <c r="AF24" s="17">
         <f>[21]Main!$G$3</f>
@@ -9242,7 +9252,7 @@
       </c>
     </row>
     <row r="25" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="29" t="s">
         <v>92</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -9250,11 +9260,11 @@
       </c>
       <c r="D25" s="12">
         <f>[22]Main!$D$3</f>
-        <v>170.76</v>
+        <v>269.39999999999998</v>
       </c>
       <c r="E25" s="8">
         <f>[22]Main!$D$5</f>
-        <v>43355.963999999993</v>
+        <v>68400.659999999989</v>
       </c>
       <c r="F25" s="8">
         <f>[22]Main!$D$8</f>
@@ -9262,7 +9272,7 @@
       </c>
       <c r="G25" s="8">
         <f>[22]Main!$D$9</f>
-        <v>39046.16399999999</v>
+        <v>64090.859999999986</v>
       </c>
       <c r="H25" s="8">
         <f>[22]Model!AH19</f>
@@ -9270,51 +9280,51 @@
       </c>
       <c r="I25" s="8">
         <f>[22]Model!AI19</f>
-        <v>1236.7858699999997</v>
+        <v>1846.8473600000007</v>
       </c>
       <c r="J25" s="8">
         <f>[22]Model!AJ19</f>
-        <v>2030.6664069599997</v>
+        <v>2788.00629888</v>
       </c>
       <c r="K25" s="8">
         <f>[22]Model!AK19</f>
-        <v>2587.6999560556801</v>
+        <v>3451.5623911910393</v>
       </c>
       <c r="L25" s="8">
         <f>[22]Model!AL19</f>
-        <v>2936.7207553924445</v>
+        <v>3870.059668153528</v>
       </c>
       <c r="M25" s="9">
         <f t="shared" si="7"/>
-        <v>15.141214518380639</v>
+        <v>24.852978129362491</v>
       </c>
       <c r="N25" s="9">
         <f t="shared" si="7"/>
-        <v>31.570674396530741</v>
+        <v>34.702846260126208</v>
       </c>
       <c r="O25" s="9">
         <f t="shared" si="7"/>
-        <v>19.228251310097694</v>
+        <v>22.988061406370068</v>
       </c>
       <c r="P25" s="9">
         <f t="shared" si="7"/>
-        <v>15.089138873548686</v>
+        <v>18.568651739736911</v>
       </c>
       <c r="Q25" s="9">
         <f t="shared" si="7"/>
-        <v>13.295838199223716</v>
+        <v>16.560690401597565</v>
       </c>
       <c r="R25" s="9">
         <f>G25/[22]Model!$AS$19</f>
-        <v>10.303162912587164</v>
+        <v>12.951246712416095</v>
       </c>
       <c r="S25" s="10">
         <f>[22]Model!$AH$5</f>
         <v>6564</v>
       </c>
-      <c r="T25" s="31">
+      <c r="T25" s="30">
         <f t="shared" si="8"/>
-        <v>5.9485319926873839</v>
+        <v>9.763994515539304</v>
       </c>
       <c r="U25" s="11">
         <f>[22]Model!AG$23</f>
@@ -9332,11 +9342,11 @@
       </c>
       <c r="Z25" s="11">
         <f>[22]Model!$AV$32</f>
-        <v>-2.3447287090133662E-2</v>
+        <v>-0.2163449663847643</v>
       </c>
       <c r="AA25" s="7" t="str">
         <f>[22]Model!$AV$33</f>
-        <v>Fairly valued</v>
+        <v>Slightly overvalued</v>
       </c>
       <c r="AB25" s="7" t="s">
         <v>94</v>
@@ -9346,7 +9356,7 @@
       </c>
       <c r="AE25" s="17">
         <f>[22]Main!$E$3</f>
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="AF25" s="17">
         <f>[22]Main!$G$3</f>
@@ -9354,7 +9364,7 @@
       </c>
     </row>
     <row r="26" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C26" s="7" t="s">
@@ -9362,39 +9372,39 @@
       </c>
       <c r="D26" s="12">
         <f>[23]Main!$D$3</f>
-        <v>138.38999999999999</v>
+        <v>205.72</v>
       </c>
       <c r="E26" s="8">
         <f>[23]Main!$D$5</f>
-        <v>45862.445999999989</v>
+        <v>68443.043999999994</v>
       </c>
       <c r="F26" s="8">
         <f>[23]Main!$D$8</f>
-        <v>3024.7000000000007</v>
+        <v>2593.2000000000003</v>
       </c>
       <c r="G26" s="8">
         <f>[23]Main!$D$9</f>
-        <v>42837.745999999985</v>
+        <v>65849.843999999997</v>
       </c>
       <c r="H26" s="8">
         <f>[23]Model!AN$16</f>
-        <v>-240.01066769136114</v>
+        <v>-104.65711413616123</v>
       </c>
       <c r="I26" s="8">
         <f>[23]Model!AO$16</f>
-        <v>198.13126283928906</v>
+        <v>355.93835647866615</v>
       </c>
       <c r="J26" s="8">
         <f>[23]Model!AP$16</f>
-        <v>506.19203596408926</v>
+        <v>670.48578238868038</v>
       </c>
       <c r="K26" s="8">
         <f>[23]Model!AQ$16</f>
-        <v>771.45115546614261</v>
+        <v>940.00566118122208</v>
       </c>
       <c r="L26" s="8">
         <f>[23]Model!AR$16</f>
-        <v>946.1797826811702</v>
+        <v>1112.4269691830461</v>
       </c>
       <c r="M26" s="9"/>
       <c r="N26" s="9"/>
@@ -9403,15 +9413,15 @@
       <c r="Q26" s="9"/>
       <c r="R26" s="9">
         <f>G26/[23]Model!$AY$16</f>
-        <v>32.174053335778765</v>
+        <v>43.756167002424526</v>
       </c>
       <c r="S26" s="10">
         <f>[23]Model!$AN$3</f>
-        <v>7381.8418175999986</v>
-      </c>
-      <c r="T26" s="31">
+        <v>7462.6884287999992</v>
+      </c>
+      <c r="T26" s="30">
         <f t="shared" si="8"/>
-        <v>5.8031243500592229</v>
+        <v>8.82387689480273</v>
       </c>
       <c r="U26" s="11">
         <f>[23]Model!AM$20</f>
@@ -9429,7 +9439,7 @@
       </c>
       <c r="Z26" s="11">
         <f>[23]Model!$AX$90</f>
-        <v>-0.5208349517611679</v>
+        <v>-0.59373967106754755</v>
       </c>
       <c r="AA26" s="7" t="str">
         <f>[23]Model!$AX$30</f>
@@ -9443,232 +9453,238 @@
       </c>
       <c r="AE26" s="17">
         <f>[23]Main!$E$3</f>
-        <v>45751</v>
+        <v>45805</v>
       </c>
       <c r="AF26" s="17">
         <f>[23]Main!$G$3</f>
-        <v>45798</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="27" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B27" s="27" t="s">
-        <v>132</v>
+      <c r="B27" s="29" t="s">
+        <v>82</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="D27" s="12">
         <f>[24]Main!$D$3</f>
-        <v>92.41</v>
+        <v>74.09</v>
       </c>
       <c r="E27" s="8">
         <f>[24]Main!$D$5</f>
-        <v>22880.716</v>
+        <v>50255.246999999996</v>
       </c>
       <c r="F27" s="8">
-        <f>[24]Main!$D$8</f>
-        <v>-14205.4</v>
+        <f>[24]Main!$D$6</f>
+        <v>4510.5</v>
       </c>
       <c r="G27" s="8">
         <f>[24]Main!$D$9</f>
-        <v>37086.116000000002</v>
+        <v>46751.446999999993</v>
       </c>
       <c r="H27" s="8">
-        <f>[24]Model!Y15</f>
-        <v>1570.3999999999994</v>
+        <f>[24]Model!AQ$19</f>
+        <v>-935.1</v>
       </c>
       <c r="I27" s="8">
-        <f>[24]Model!Z15</f>
-        <v>1591.795564100001</v>
+        <f>[24]Model!AR$19</f>
+        <v>-645.97905000000014</v>
       </c>
       <c r="J27" s="8">
-        <f>[24]Model!AA15</f>
-        <v>1847.0743551644998</v>
+        <f>[24]Model!AS$19</f>
+        <v>-190.06624810800022</v>
       </c>
       <c r="K27" s="8">
-        <f>[24]Model!AB15</f>
-        <v>1992.9255918762433</v>
+        <f>[24]Model!AT$19</f>
+        <v>287.02723014899908</v>
       </c>
       <c r="L27" s="8">
-        <f>[24]Model!AC15</f>
-        <v>2050.8211370533554</v>
-      </c>
-      <c r="M27" s="9">
-        <f>$G27/H27</f>
-        <v>23.615713194090688</v>
-      </c>
-      <c r="N27" s="9">
-        <f>$G27/I27</f>
-        <v>23.298290833577262</v>
-      </c>
-      <c r="O27" s="9">
-        <f>$G27/J27</f>
-        <v>20.078301610493167</v>
-      </c>
+        <f>[24]Model!AU$19</f>
+        <v>778.71748128609477</v>
+      </c>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
       <c r="P27" s="9">
         <f>$G27/K27</f>
-        <v>18.608881410913696</v>
+        <v>162.88157390408844</v>
       </c>
       <c r="Q27" s="9">
         <f>$G27/L27</f>
-        <v>18.083544844523001</v>
+        <v>60.036467812161355</v>
       </c>
       <c r="R27" s="9">
-        <f>G27/[24]Model!$AJ$15</f>
-        <v>15.928263542991425</v>
+        <f>G27/[24]Model!$BB$19</f>
+        <v>16.154560296290363</v>
       </c>
       <c r="S27" s="10">
-        <f>[24]Model!$Y$3</f>
-        <v>10106</v>
-      </c>
-      <c r="T27" s="31">
+        <f>[24]Model!$AQ$3</f>
+        <v>3602</v>
+      </c>
+      <c r="T27" s="30">
         <f t="shared" si="8"/>
-        <v>3.6697126459528993</v>
+        <v>12.979302332037754</v>
       </c>
       <c r="U27" s="11">
-        <f>[24]Model!X$19</f>
-        <v>7.562725611658272E-2</v>
+        <f>[24]Model!AP$23</f>
+        <v>0.25806741573033709</v>
       </c>
       <c r="V27" s="11">
-        <f>[24]Model!Y$19</f>
-        <v>4.6776599270798913E-2</v>
-      </c>
-      <c r="W27" s="11"/>
-      <c r="X27" s="11"/>
+        <f>[24]Model!AQ$23</f>
+        <v>0.28679622749356937</v>
+      </c>
+      <c r="W27" s="11">
+        <f>[24]Model!$AQ$27</f>
+        <v>0.26724042198778453</v>
+      </c>
+      <c r="X27" s="11">
+        <f>[24]Model!$AQ$28</f>
+        <v>-0.29516935036091063</v>
+      </c>
       <c r="Y27" s="11">
-        <f>[24]Model!$AN$21</f>
+        <f>[24]Model!$BE$27</f>
         <v>0.08</v>
       </c>
       <c r="Z27" s="11">
-        <f>[24]Model!$AN$27</f>
-        <v>-0.50305134589738842</v>
+        <f>[24]Model!$BE$33</f>
+        <v>-0.5028026588253911</v>
       </c>
       <c r="AA27" s="7" t="str">
-        <f>[24]Model!$AN$28</f>
-        <v>Heavily overvalued</v>
+        <f>[24]Model!$BE$34</f>
+        <v>Overvalued</v>
       </c>
       <c r="AB27" s="7" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="AC27" s="7">
-        <v>1967</v>
+        <v>2006</v>
       </c>
       <c r="AE27" s="17">
-        <f>[24]Main!$F$3</f>
-        <v>45751</v>
+        <f>[24]Main!$E$3</f>
+        <v>45781</v>
       </c>
       <c r="AF27" s="17">
-        <f>[24]Main!$H$3</f>
-        <v>45782</v>
+        <f>[24]Main!$G$3</f>
+        <v>45784</v>
       </c>
     </row>
     <row r="28" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B28" s="28" t="s">
-        <v>82</v>
+      <c r="B28" s="26" t="s">
+        <v>132</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="D28" s="12">
         <f>[25]Main!$D$3</f>
-        <v>74.09</v>
+        <v>75</v>
       </c>
       <c r="E28" s="8">
         <f>[25]Main!$D$5</f>
-        <v>50255.246999999996</v>
+        <v>18502.5</v>
       </c>
       <c r="F28" s="8">
-        <f>[25]Main!$D$6</f>
-        <v>4510.5</v>
+        <f>[25]Main!$D$8</f>
+        <v>-14026.8</v>
       </c>
       <c r="G28" s="8">
         <f>[25]Main!$D$9</f>
-        <v>46751.446999999993</v>
+        <v>32529.3</v>
       </c>
       <c r="H28" s="8">
-        <f>[25]Model!AQ$19</f>
-        <v>-935.1</v>
+        <f>[25]Model!Y15</f>
+        <v>1570.3999999999994</v>
       </c>
       <c r="I28" s="8">
-        <f>[25]Model!AR$19</f>
-        <v>-645.97905000000014</v>
+        <f>[25]Model!Z15</f>
+        <v>1583.1879707000001</v>
       </c>
       <c r="J28" s="8">
-        <f>[25]Model!AS$19</f>
-        <v>-190.06624810800022</v>
+        <f>[25]Model!AA15</f>
+        <v>1815.8713334915003</v>
       </c>
       <c r="K28" s="8">
-        <f>[25]Model!AT$19</f>
-        <v>287.02723014899908</v>
+        <f>[25]Model!AB15</f>
+        <v>1958.8265588715878</v>
       </c>
       <c r="L28" s="8">
-        <f>[25]Model!AU$19</f>
-        <v>778.71748128609477</v>
-      </c>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
+        <f>[25]Model!AC15</f>
+        <v>2015.8131094093987</v>
+      </c>
+      <c r="M28" s="9">
+        <f>$G28/H28</f>
+        <v>20.71402190524708</v>
+      </c>
+      <c r="N28" s="9">
+        <f>$G28/I28</f>
+        <v>20.546707404312389</v>
+      </c>
+      <c r="O28" s="9">
+        <f>$G28/J28</f>
+        <v>17.913879359201999</v>
+      </c>
       <c r="P28" s="9">
         <f>$G28/K28</f>
-        <v>162.88157390408844</v>
+        <v>16.606523866379984</v>
       </c>
       <c r="Q28" s="9">
         <f>$G28/L28</f>
-        <v>60.036467812161355</v>
+        <v>16.13706144094408</v>
       </c>
       <c r="R28" s="9">
-        <f>G28/[25]Model!$BB$19</f>
-        <v>16.154560296290363</v>
+        <f>G28/[25]Model!$AJ$15</f>
+        <v>14.204818260759916</v>
       </c>
       <c r="S28" s="10">
-        <f>[25]Model!$AQ$3</f>
-        <v>3602</v>
-      </c>
-      <c r="T28" s="31">
-        <f t="shared" si="8"/>
-        <v>12.979302332037754</v>
+        <f>[25]Model!$Y$3</f>
+        <v>10106</v>
+      </c>
+      <c r="T28" s="30">
+        <f>G28/S28</f>
+        <v>3.2188106075598655</v>
       </c>
       <c r="U28" s="11">
-        <f>[25]Model!AP$23</f>
-        <v>0.25806741573033709</v>
+        <f>[25]Model!X$19</f>
+        <v>7.562725611658272E-2</v>
       </c>
       <c r="V28" s="11">
-        <f>[25]Model!AQ$23</f>
-        <v>0.28679622749356937</v>
+        <f>[25]Model!Y$19</f>
+        <v>4.6776599270798913E-2</v>
       </c>
       <c r="W28" s="11">
-        <f>[25]Model!$AQ$27</f>
-        <v>0.26724042198778453</v>
+        <f>[25]Model!$Y$20</f>
+        <v>0.6279339006530773</v>
       </c>
       <c r="X28" s="11">
-        <f>[25]Model!$AQ$28</f>
-        <v>-0.29516935036091063</v>
+        <f>[25]Model!$Y$22</f>
+        <v>0.20389867405501677</v>
       </c>
       <c r="Y28" s="11">
-        <f>[25]Model!$BE$27</f>
+        <f>[25]Model!$AN$21</f>
         <v>0.08</v>
       </c>
       <c r="Z28" s="11">
-        <f>[25]Model!$BE$33</f>
-        <v>-0.5028026588253911</v>
+        <f>[25]Model!$AN$27</f>
+        <v>-0.39795366055345971</v>
       </c>
       <c r="AA28" s="7" t="str">
-        <f>[25]Model!$BE$34</f>
+        <f>[25]Model!$AN$28</f>
         <v>Overvalued</v>
       </c>
       <c r="AB28" s="7" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="AC28" s="7">
-        <v>2006</v>
+        <v>1967</v>
       </c>
       <c r="AE28" s="17">
         <f>[25]Main!$E$3</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="AF28" s="17">
         <f>[25]Main!$G$3</f>
-        <v>45784</v>
+        <v>45873</v>
       </c>
     </row>
     <row r="29" spans="2:32" x14ac:dyDescent="0.3">
@@ -9680,11 +9696,11 @@
       </c>
       <c r="D29" s="12">
         <f>[26]Main!$D$3</f>
-        <v>44.8</v>
+        <v>60.41</v>
       </c>
       <c r="E29" s="8">
         <f>[26]Main!$D$5</f>
-        <v>27552</v>
+        <v>37152.15</v>
       </c>
       <c r="F29" s="8">
         <f>[26]Main!$D$8</f>
@@ -9692,7 +9708,7 @@
       </c>
       <c r="G29" s="8">
         <f>[26]Main!$D$9</f>
-        <v>25571.599999999999</v>
+        <v>35171.75</v>
       </c>
       <c r="H29" s="8">
         <f>[26]Model!Y$30</f>
@@ -9716,35 +9732,35 @@
       </c>
       <c r="M29" s="9">
         <f t="shared" ref="M29:Q29" si="14">$G29/H29</f>
-        <v>8.8266197231714436</v>
+        <v>12.140329985157566</v>
       </c>
       <c r="N29" s="9">
         <f t="shared" si="14"/>
-        <v>67.612316218232806</v>
+        <v>92.995490424870937</v>
       </c>
       <c r="O29" s="9">
         <f t="shared" si="14"/>
-        <v>21.106693138695682</v>
+        <v>29.030617341148773</v>
       </c>
       <c r="P29" s="9">
         <f t="shared" si="14"/>
-        <v>13.349479947575611</v>
+        <v>18.361172994499466</v>
       </c>
       <c r="Q29" s="9">
         <f t="shared" si="14"/>
-        <v>11.416895724316491</v>
+        <v>15.703053473061075</v>
       </c>
       <c r="R29" s="9">
         <f>G29/[26]Model!$AJ$30</f>
-        <v>8.468507911560673</v>
+        <v>11.64777499798347</v>
       </c>
       <c r="S29" s="10">
         <f>[26]Model!$Y$7</f>
         <v>24121.1</v>
       </c>
-      <c r="T29" s="31">
+      <c r="T29" s="30">
         <f t="shared" si="8"/>
-        <v>1.0601340734875275</v>
+        <v>1.4581320918200249</v>
       </c>
       <c r="U29" s="11">
         <f>[26]Model!$X$38</f>
@@ -9768,11 +9784,11 @@
       </c>
       <c r="Z29" s="11">
         <f>[26]Model!$AN$42</f>
-        <v>0.11667361343101468</v>
+        <v>-0.17187588343470517</v>
       </c>
       <c r="AA29" s="7" t="str">
         <f>[26]Model!$AN$43</f>
-        <v>Slightly undervalued</v>
+        <v>Slightly overvalued</v>
       </c>
       <c r="AB29" s="7" t="s">
         <v>94</v>
@@ -9782,7 +9798,7 @@
       </c>
       <c r="AE29" s="17">
         <f>[26]Main!$E$3</f>
-        <v>45779</v>
+        <v>45804</v>
       </c>
       <c r="AF29" s="17">
         <f>[26]Main!$G$3</f>
@@ -9790,7 +9806,7 @@
       </c>
     </row>
     <row r="30" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="29" t="s">
         <v>122</v>
       </c>
       <c r="C30" s="7" t="s">
@@ -9857,7 +9873,7 @@
         <f>[27]Model!$V$3</f>
         <v>1300.3</v>
       </c>
-      <c r="T30" s="31">
+      <c r="T30" s="30">
         <f t="shared" si="8"/>
         <v>12.123809890025377</v>
       </c>
@@ -9905,7 +9921,7 @@
       </c>
     </row>
     <row r="31" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="26" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="7" t="s">
@@ -9913,11 +9929,11 @@
       </c>
       <c r="D31" s="12">
         <f>[28]Main!$D$3</f>
-        <v>7.86</v>
+        <v>8.39</v>
       </c>
       <c r="E31" s="8">
         <f>[28]Main!$D$5</f>
-        <v>13332.918</v>
+        <v>14231.957</v>
       </c>
       <c r="F31" s="8">
         <f>[28]Main!$D$8</f>
@@ -9925,7 +9941,7 @@
       </c>
       <c r="G31" s="8">
         <f>[28]Main!$D$9</f>
-        <v>13738.918</v>
+        <v>14637.957</v>
       </c>
       <c r="H31" s="8">
         <f>[28]Model!AQ15</f>
@@ -9952,23 +9968,23 @@
       <c r="O31" s="9"/>
       <c r="P31" s="9">
         <f t="shared" ref="P31:Q42" si="15">$G31/K31</f>
-        <v>103.46889807377723</v>
+        <v>110.23963319683064</v>
       </c>
       <c r="Q31" s="9">
         <f t="shared" si="15"/>
-        <v>63.484471809725598</v>
+        <v>67.638730249243466</v>
       </c>
       <c r="R31" s="9">
         <f>G31/[28]Model!$BB$15</f>
-        <v>28.778171318253424</v>
+        <v>30.661339873724188</v>
       </c>
       <c r="S31" s="10">
         <f>[28]Model!$AQ$3</f>
         <v>5361.4</v>
       </c>
-      <c r="T31" s="31">
+      <c r="T31" s="30">
         <f t="shared" si="8"/>
-        <v>2.5625616443466259</v>
+        <v>2.7302490021263104</v>
       </c>
       <c r="U31" s="11">
         <f>[28]Model!AP$19</f>
@@ -9992,7 +10008,7 @@
       </c>
       <c r="Z31" s="11">
         <f>[28]Model!$BE$54</f>
-        <v>-0.33764030354459329</v>
+        <v>-0.37948185767109699</v>
       </c>
       <c r="AA31" s="7" t="s">
         <v>184</v>
@@ -10005,7 +10021,7 @@
       </c>
       <c r="AE31" s="17">
         <f>[28]Main!$E$3</f>
-        <v>45777</v>
+        <v>45804</v>
       </c>
       <c r="AF31" s="17">
         <f>[28]Main!$G$3</f>
@@ -10013,7 +10029,7 @@
       </c>
     </row>
     <row r="32" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="29" t="s">
         <v>39</v>
       </c>
       <c r="C32" s="7" t="s">
@@ -10083,7 +10099,7 @@
         <f>[29]Model!$AP$3</f>
         <v>4665.2999999999993</v>
       </c>
-      <c r="T32" s="31">
+      <c r="T32" s="30">
         <f t="shared" si="8"/>
         <v>3.0170085525046626</v>
       </c>
@@ -10125,7 +10141,7 @@
       </c>
     </row>
     <row r="33" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="27" t="s">
         <v>160</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -10133,11 +10149,11 @@
       </c>
       <c r="D33" s="12">
         <f>[30]Main!$D$3</f>
-        <v>486.42</v>
+        <v>528.66999999999996</v>
       </c>
       <c r="E33" s="8">
         <f>[30]Main!$D$5</f>
-        <v>22132.11</v>
+        <v>24054.484999999997</v>
       </c>
       <c r="F33" s="8">
         <f>[30]Main!$D$8</f>
@@ -10145,7 +10161,7 @@
       </c>
       <c r="G33" s="8">
         <f>[30]Main!$D$9</f>
-        <v>21049.510000000002</v>
+        <v>22971.884999999998</v>
       </c>
       <c r="H33" s="8">
         <f>[30]Model!AC$15</f>
@@ -10169,35 +10185,35 @@
       </c>
       <c r="M33" s="9">
         <f t="shared" si="16"/>
-        <v>237.31127395715905</v>
+        <v>258.98404735062013</v>
       </c>
       <c r="N33" s="9">
         <f t="shared" ref="N33" si="17">$G33/I33</f>
-        <v>168.37221155528988</v>
+        <v>183.74903173726082</v>
       </c>
       <c r="O33" s="9">
         <f t="shared" ref="O33" si="18">$G33/J33</f>
-        <v>113.8076311665087</v>
+        <v>124.20126716866345</v>
       </c>
       <c r="P33" s="9">
         <f t="shared" si="15"/>
-        <v>77.890464887976265</v>
+        <v>85.003917050949326</v>
       </c>
       <c r="Q33" s="9">
         <f t="shared" si="15"/>
-        <v>59.423582708710811</v>
+        <v>64.850521854071332</v>
       </c>
       <c r="R33" s="9">
         <f>G33/[30]Model!$AN$43</f>
-        <v>23.125533064302203</v>
+        <v>25.237503681408629</v>
       </c>
       <c r="S33" s="10">
         <f>[30]Model!$AC$3</f>
         <v>748.1</v>
       </c>
-      <c r="T33" s="31">
+      <c r="T33" s="30">
         <f t="shared" si="8"/>
-        <v>28.137294479347684</v>
+        <v>30.706970993182725</v>
       </c>
       <c r="U33" s="11">
         <f>[30]Model!$AB$19</f>
@@ -10221,11 +10237,11 @@
       </c>
       <c r="Z33" s="11">
         <f>[30]Model!$AR$28</f>
-        <v>-0.65814945001941016</v>
+        <v>-0.68546930122466088</v>
       </c>
       <c r="AA33" s="7" t="str">
         <f>[30]Model!$AR$29</f>
-        <v>Overvalued</v>
+        <v>Heavily overvalued</v>
       </c>
       <c r="AB33" s="7" t="s">
         <v>54</v>
@@ -10235,7 +10251,7 @@
       </c>
       <c r="AE33" s="17">
         <f>[30]Main!$E$3</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="AF33" s="17">
         <f>[30]Main!$G$3</f>
@@ -10243,7 +10259,7 @@
       </c>
     </row>
     <row r="34" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="26" t="s">
         <v>137</v>
       </c>
       <c r="C34" s="7" t="s">
@@ -10251,11 +10267,11 @@
       </c>
       <c r="D34" s="12">
         <f>[31]Main!$D$3</f>
-        <v>12.7</v>
+        <v>13.43</v>
       </c>
       <c r="E34" s="8">
         <f>[31]Main!$D$5</f>
-        <v>13944.599999999999</v>
+        <v>14746.14</v>
       </c>
       <c r="F34" s="8">
         <f>[31]Main!$D$8</f>
@@ -10263,7 +10279,7 @@
       </c>
       <c r="G34" s="8">
         <f>[31]Main!$D$9</f>
-        <v>12121.699999999997</v>
+        <v>12923.239999999998</v>
       </c>
       <c r="H34" s="8">
         <f>[31]Model!Z17</f>
@@ -10287,35 +10303,35 @@
       </c>
       <c r="M34" s="9">
         <f t="shared" si="16"/>
-        <v>40.831373917831911</v>
+        <v>43.531323549492406</v>
       </c>
       <c r="N34" s="9">
         <f t="shared" si="16"/>
-        <v>28.823804965552</v>
+        <v>30.729761442951091</v>
       </c>
       <c r="O34" s="9">
         <f t="shared" si="16"/>
-        <v>23.091522767120356</v>
+        <v>24.618435589476768</v>
       </c>
       <c r="P34" s="9">
         <f t="shared" si="15"/>
-        <v>21.177552018381419</v>
+        <v>22.577904695383282</v>
       </c>
       <c r="Q34" s="9">
         <f t="shared" si="15"/>
-        <v>19.666409164820859</v>
+        <v>20.966838444704912</v>
       </c>
       <c r="R34" s="9">
         <f>G34/[31]Model!$AJ$17</f>
-        <v>16.732418313974762</v>
+        <v>17.838839243001495</v>
       </c>
       <c r="S34" s="10">
         <f>[31]Model!$Y$7</f>
         <v>3766.2000000000003</v>
       </c>
-      <c r="T34" s="31">
+      <c r="T34" s="30">
         <f t="shared" si="8"/>
-        <v>3.2185492007859371</v>
+        <v>3.4313737985237101</v>
       </c>
       <c r="U34" s="11">
         <f>[31]Model!X$24</f>
@@ -10339,7 +10355,7 @@
       </c>
       <c r="Z34" s="11">
         <f>[31]Model!$AN$29</f>
-        <v>-0.32894234972067471</v>
+        <v>-0.36541830539483011</v>
       </c>
       <c r="AA34" s="7" t="str">
         <f>[31]Model!$AN$30</f>
@@ -10353,7 +10369,7 @@
       </c>
       <c r="AE34" s="17">
         <f>[31]Main!$E$3</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="AF34" s="17">
         <f>[31]Main!$G$3</f>
@@ -10361,7 +10377,7 @@
       </c>
     </row>
     <row r="35" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="26" t="s">
         <v>104</v>
       </c>
       <c r="C35" s="7" t="s">
@@ -10369,11 +10385,11 @@
       </c>
       <c r="D35" s="12">
         <f>[32]Main!$D$3</f>
-        <v>78.150000000000006</v>
+        <v>85.53</v>
       </c>
       <c r="E35" s="8">
         <f>[32]Main!$D$5</f>
-        <v>11644.35</v>
+        <v>12743.97</v>
       </c>
       <c r="F35" s="8">
         <f>[32]Main!$D$8</f>
@@ -10381,7 +10397,7 @@
       </c>
       <c r="G35" s="8">
         <f>[32]Main!$D$9</f>
-        <v>10141.15</v>
+        <v>11240.769999999999</v>
       </c>
       <c r="H35" s="8">
         <f>[32]Model!AV$18</f>
@@ -10405,35 +10421,35 @@
       </c>
       <c r="M35" s="9">
         <f>$G35/H35</f>
-        <v>16.058828186856694</v>
+        <v>17.800110847189234</v>
       </c>
       <c r="N35" s="9">
         <f>$G35/I35</f>
-        <v>15.631647773952817</v>
+        <v>17.326610625818137</v>
       </c>
       <c r="O35" s="9">
         <f>$G35/J35</f>
-        <v>13.552537452591492</v>
+        <v>15.022059275424075</v>
       </c>
       <c r="P35" s="9">
         <f>$G35/K35</f>
-        <v>13.160237228239321</v>
+        <v>14.587221353404271</v>
       </c>
       <c r="Q35" s="9">
         <f>$G35/L35</f>
-        <v>12.946379281121663</v>
+        <v>14.35017447053381</v>
       </c>
       <c r="R35" s="9">
         <f>G35/[32]Model!$BF$18</f>
-        <v>11.481797743963707</v>
+        <v>12.726786175770489</v>
       </c>
       <c r="S35" s="10">
         <f>[32]Model!$AV$3</f>
         <v>4554.8999999999996</v>
       </c>
-      <c r="T35" s="31">
+      <c r="T35" s="30">
         <f>G35/S35</f>
-        <v>2.2264264857625853</v>
+        <v>2.4678412259325122</v>
       </c>
       <c r="U35" s="11">
         <f>[32]Model!AU$22</f>
@@ -10457,11 +10473,11 @@
       </c>
       <c r="Z35" s="11">
         <f>[32]Model!$BI$31</f>
-        <v>-4.3547613894122761E-2</v>
+        <v>-0.12607559950690628</v>
       </c>
       <c r="AA35" s="7" t="str">
         <f>[32]Model!$BI$32</f>
-        <v>Fairly valued</v>
+        <v>Slightly overvalued</v>
       </c>
       <c r="AB35" s="7" t="s">
         <v>84</v>
@@ -10471,7 +10487,7 @@
       </c>
       <c r="AE35" s="17">
         <f>[32]Main!$E$3</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="AF35" s="17">
         <f>[32]Main!$G$3</f>
@@ -10479,7 +10495,7 @@
       </c>
     </row>
     <row r="36" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="29" t="s">
         <v>171</v>
       </c>
       <c r="C36" s="7" t="s">
@@ -10546,7 +10562,7 @@
         <f>[33]Model!$X$6</f>
         <v>1800.3999999999999</v>
       </c>
-      <c r="T36" s="31">
+      <c r="T36" s="30">
         <f t="shared" si="8"/>
         <v>5.3955209953343726</v>
       </c>
@@ -10588,7 +10604,7 @@
       </c>
     </row>
     <row r="37" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="26" t="s">
         <v>191</v>
       </c>
       <c r="C37" s="7" t="s">
@@ -10596,11 +10612,11 @@
       </c>
       <c r="D37" s="12">
         <f>[34]Main!$D$3</f>
-        <v>82.36</v>
+        <v>90.43</v>
       </c>
       <c r="E37" s="8">
         <f>[34]Main!$D$5</f>
-        <v>7338.2759999999998</v>
+        <v>8057.3130000000001</v>
       </c>
       <c r="F37" s="8">
         <f>[34]Main!$D$8</f>
@@ -10608,7 +10624,7 @@
       </c>
       <c r="G37" s="8">
         <f>[34]Main!$D$9</f>
-        <v>9014.4760000000006</v>
+        <v>9733.5130000000008</v>
       </c>
       <c r="H37" s="8">
         <f>[34]Model!Z$23</f>
@@ -10632,35 +10648,35 @@
       </c>
       <c r="M37" s="9">
         <f t="shared" ref="M37:O37" si="19">$G37/H37</f>
-        <v>45.253393574297121</v>
+        <v>48.863017068273024</v>
       </c>
       <c r="N37" s="9">
         <f t="shared" si="19"/>
-        <v>59.988877023066976</v>
+        <v>64.773871976521292</v>
       </c>
       <c r="O37" s="9">
         <f t="shared" si="19"/>
-        <v>25.137500548217854</v>
+        <v>27.142585811264642</v>
       </c>
       <c r="P37" s="9">
         <f t="shared" si="15"/>
-        <v>20.820995301694204</v>
+        <v>22.481775806156616</v>
       </c>
       <c r="Q37" s="9">
         <f t="shared" si="15"/>
-        <v>18.452882289224107</v>
+        <v>19.924770962797236</v>
       </c>
       <c r="R37" s="9">
         <f>G37/[34]Model!$AK$23</f>
-        <v>11.745275561814704</v>
+        <v>12.68213397756073</v>
       </c>
       <c r="S37" s="10">
         <f>[34]Model!$Z$3</f>
         <v>3330.6000000000004</v>
       </c>
-      <c r="T37" s="31">
+      <c r="T37" s="30">
         <f t="shared" si="8"/>
-        <v>2.7065621809884104</v>
+        <v>2.9224503092535881</v>
       </c>
       <c r="U37" s="11"/>
       <c r="V37" s="11">
@@ -10681,7 +10697,7 @@
       </c>
       <c r="Z37" s="11">
         <f>[34]Model!$AO$36</f>
-        <v>-0.35523475844729624</v>
+        <v>-0.41277379968726446</v>
       </c>
       <c r="AA37" s="7" t="str">
         <f>[34]Model!$AO$37</f>
@@ -10695,7 +10711,7 @@
       </c>
       <c r="AE37" s="17">
         <f>[34]Main!$E$3</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="AF37" s="17">
         <f>[34]Main!$G$3</f>
@@ -10703,237 +10719,237 @@
       </c>
     </row>
     <row r="38" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B38" s="27" t="s">
-        <v>59</v>
+      <c r="B38" s="26" t="s">
+        <v>71</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D38" s="12">
         <f>[35]Main!$D$3</f>
-        <v>149.62</v>
+        <v>70.45</v>
       </c>
       <c r="E38" s="8">
         <f>[35]Main!$D$5</f>
-        <v>8513.3780000000006</v>
+        <v>10327.969999999999</v>
       </c>
       <c r="F38" s="8">
         <f>[35]Main!$D$8</f>
-        <v>1262.8</v>
+        <v>2256.1</v>
       </c>
       <c r="G38" s="8">
         <f>[35]Main!$D$9</f>
-        <v>7250.5780000000004</v>
+        <v>8071.869999999999</v>
       </c>
       <c r="H38" s="8">
-        <f>[35]Model!AZ$13</f>
-        <v>454.49999999999966</v>
+        <f>[35]Model!AP18</f>
+        <v>-129.40000000000018</v>
       </c>
       <c r="I38" s="8">
-        <f>[35]Model!BA$13</f>
-        <v>449.57382599999983</v>
+        <f>[35]Model!AQ18</f>
+        <v>-8.2235920000007852</v>
       </c>
       <c r="J38" s="8">
-        <f>[35]Model!BB$13</f>
-        <v>445.48834746</v>
+        <f>[35]Model!AR18</f>
+        <v>196.63455295999964</v>
       </c>
       <c r="K38" s="8">
-        <f>[35]Model!BC$13</f>
-        <v>441.07713379859996</v>
+        <f>[35]Model!AS18</f>
+        <v>342.45798946879961</v>
       </c>
       <c r="L38" s="8">
-        <f>[35]Model!BD$13</f>
-        <v>443.01880423842584</v>
-      </c>
-      <c r="M38" s="9">
-        <f>$G38/H38</f>
-        <v>15.952866886688682</v>
-      </c>
-      <c r="N38" s="9">
-        <f>$G38/I38</f>
-        <v>16.127669318542587</v>
-      </c>
+        <f>[35]Model!AT18</f>
+        <v>465.99155682684778</v>
+      </c>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
       <c r="O38" s="9">
-        <f>$G38/J38</f>
-        <v>16.275572731228451</v>
+        <f t="shared" ref="O38:Q39" si="20">$G38/J38</f>
+        <v>41.050109853490596</v>
       </c>
       <c r="P38" s="9">
-        <f>$G38/K38</f>
-        <v>16.438344780100714</v>
+        <f t="shared" si="20"/>
+        <v>23.570394758553018</v>
       </c>
       <c r="Q38" s="9">
-        <f>$G38/L38</f>
-        <v>16.366298519685074</v>
+        <f t="shared" si="20"/>
+        <v>17.321923287548596</v>
       </c>
       <c r="R38" s="9">
-        <f>G38/[35]Model!$BK$13</f>
-        <v>16.044350612290323</v>
+        <f>G38/[35]Model!$BA$18</f>
+        <v>12.527668620442165</v>
       </c>
       <c r="S38" s="10">
-        <f>[35]Model!$AZ$3</f>
-        <v>4727.8999999999996</v>
-      </c>
-      <c r="T38" s="31">
+        <f>[35]Model!$AP$5</f>
+        <v>4112.7</v>
+      </c>
+      <c r="T38" s="30">
         <f>G38/S38</f>
-        <v>1.5335726220943762</v>
+        <v>1.9626692926787754</v>
       </c>
       <c r="U38" s="11">
-        <f>[35]Model!$AY$17</f>
-        <v>-2.7815200945136453E-2</v>
+        <f>[35]Model!AO$24</f>
+        <v>0.11452969584546024</v>
       </c>
       <c r="V38" s="11">
-        <f>[35]Model!$AZ$17</f>
-        <v>7.9735635859716769E-3</v>
+        <f>[35]Model!AP$24</f>
+        <v>0.18018250688705217</v>
       </c>
       <c r="W38" s="11">
-        <f>[35]Model!$AZ$18</f>
-        <v>0.30677467797542246</v>
+        <f>[35]Model!$AP$27</f>
+        <v>0.43898169086001887</v>
       </c>
       <c r="X38" s="11">
-        <f>[35]Model!$AZ$19</f>
-        <v>0.11516741047822494</v>
+        <f>[35]Model!$AP$28</f>
+        <v>-5.3079485496146134E-2</v>
       </c>
       <c r="Y38" s="11">
-        <f>[35]Model!$BN$20</f>
+        <f>[35]Model!$BD$26</f>
         <v>0.09</v>
       </c>
       <c r="Z38" s="11">
-        <f>[35]Model!$BN$26</f>
-        <v>-0.29684783704459616</v>
+        <f>[35]Model!$BD$32</f>
+        <v>-0.324767276419479</v>
       </c>
       <c r="AA38" s="7" t="str">
-        <f>[35]Model!$BN$27</f>
+        <f>[35]Model!$BD$33</f>
         <v>Overvalued</v>
       </c>
       <c r="AB38" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AC38" s="7">
-        <v>1993</v>
+        <v>2002</v>
       </c>
       <c r="AE38" s="17">
         <f>[35]Main!$E$3</f>
-        <v>45764</v>
+        <v>45804</v>
       </c>
       <c r="AF38" s="17">
         <f>[35]Main!$G$3</f>
-        <v>45785</v>
+        <v>45869</v>
       </c>
     </row>
     <row r="39" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B39" s="27" t="s">
-        <v>71</v>
+      <c r="B39" s="29" t="s">
+        <v>59</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D39" s="12">
         <f>[36]Main!$D$3</f>
-        <v>59.53</v>
+        <v>149.62</v>
       </c>
       <c r="E39" s="8">
         <f>[36]Main!$D$5</f>
-        <v>8727.098</v>
+        <v>8513.3780000000006</v>
       </c>
       <c r="F39" s="8">
         <f>[36]Main!$D$8</f>
-        <v>2256.1</v>
+        <v>1262.8</v>
       </c>
       <c r="G39" s="8">
         <f>[36]Main!$D$9</f>
-        <v>6470.9979999999996</v>
+        <v>7250.5780000000004</v>
       </c>
       <c r="H39" s="8">
-        <f>[36]Model!AP18</f>
-        <v>-129.40000000000018</v>
+        <f>[36]Model!AZ$13</f>
+        <v>454.49999999999966</v>
       </c>
       <c r="I39" s="8">
-        <f>[36]Model!AQ18</f>
-        <v>-8.2235920000007852</v>
+        <f>[36]Model!BA$13</f>
+        <v>449.57382599999983</v>
       </c>
       <c r="J39" s="8">
-        <f>[36]Model!AR18</f>
-        <v>196.63455295999964</v>
+        <f>[36]Model!BB$13</f>
+        <v>445.48834746</v>
       </c>
       <c r="K39" s="8">
-        <f>[36]Model!AS18</f>
-        <v>342.45798946879961</v>
+        <f>[36]Model!BC$13</f>
+        <v>441.07713379859996</v>
       </c>
       <c r="L39" s="8">
-        <f>[36]Model!AT18</f>
-        <v>465.99155682684778</v>
-      </c>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
+        <f>[36]Model!BD$13</f>
+        <v>443.01880423842584</v>
+      </c>
+      <c r="M39" s="9">
+        <f>$G39/H39</f>
+        <v>15.952866886688682</v>
+      </c>
+      <c r="N39" s="9">
+        <f>$G39/I39</f>
+        <v>16.127669318542587</v>
+      </c>
       <c r="O39" s="9">
-        <f>$G39/J39</f>
-        <v>32.908753332464215</v>
+        <f t="shared" si="20"/>
+        <v>16.275572731228451</v>
       </c>
       <c r="P39" s="9">
-        <f t="shared" si="15"/>
-        <v>18.895742540676085</v>
+        <f t="shared" si="20"/>
+        <v>16.438344780100714</v>
       </c>
       <c r="Q39" s="9">
-        <f t="shared" si="15"/>
-        <v>13.886513403942381</v>
+        <f t="shared" si="20"/>
+        <v>16.366298519685074</v>
       </c>
       <c r="R39" s="9">
-        <f>G39/[36]Model!$BA$18</f>
-        <v>10.043090211753164</v>
+        <f>G39/[36]Model!$BK$13</f>
+        <v>16.044350612290323</v>
       </c>
       <c r="S39" s="10">
-        <f>[36]Model!$AP$5</f>
-        <v>4112.7</v>
-      </c>
-      <c r="T39" s="31">
-        <f t="shared" si="8"/>
-        <v>1.5734184355776011</v>
+        <f>[36]Model!$AZ$3</f>
+        <v>4727.8999999999996</v>
+      </c>
+      <c r="T39" s="30">
+        <f>G39/S39</f>
+        <v>1.5335726220943762</v>
       </c>
       <c r="U39" s="11">
-        <f>[36]Model!AO$24</f>
-        <v>0.11452969584546024</v>
+        <f>[36]Model!$AY$17</f>
+        <v>-2.7815200945136453E-2</v>
       </c>
       <c r="V39" s="11">
-        <f>[36]Model!AP$24</f>
-        <v>0.18018250688705217</v>
+        <f>[36]Model!$AZ$17</f>
+        <v>7.9735635859716769E-3</v>
       </c>
       <c r="W39" s="11">
-        <f>[36]Model!$AP$27</f>
-        <v>0.43898169086001887</v>
+        <f>[36]Model!$AZ$18</f>
+        <v>0.30677467797542246</v>
       </c>
       <c r="X39" s="11">
-        <f>[36]Model!$AP$28</f>
-        <v>-5.3079485496146134E-2</v>
+        <f>[36]Model!$AZ$19</f>
+        <v>0.11516741047822494</v>
       </c>
       <c r="Y39" s="11">
-        <f>[36]Model!$BD$26</f>
+        <f>[36]Model!$BN$20</f>
         <v>0.09</v>
       </c>
       <c r="Z39" s="11">
-        <f>[36]Model!$BD$32</f>
-        <v>-0.2009046635940247</v>
+        <f>[36]Model!$BN$26</f>
+        <v>-0.29684783704459616</v>
       </c>
       <c r="AA39" s="7" t="str">
-        <f>[36]Model!$BD$33</f>
-        <v>Slightly overvalued</v>
+        <f>[36]Model!$BN$27</f>
+        <v>Overvalued</v>
       </c>
       <c r="AB39" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AC39" s="7">
-        <v>2002</v>
+        <v>1993</v>
       </c>
       <c r="AE39" s="17">
         <f>[36]Main!$E$3</f>
-        <v>45783</v>
+        <v>45764</v>
       </c>
       <c r="AF39" s="17">
         <f>[36]Main!$G$3</f>
-        <v>45869</v>
+        <v>45785</v>
       </c>
     </row>
     <row r="40" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="26" t="s">
         <v>197</v>
       </c>
       <c r="C40" s="7" t="s">
@@ -10976,15 +10992,15 @@
         <v>512.97105644649412</v>
       </c>
       <c r="M40" s="9">
-        <f t="shared" ref="M40" si="20">$G40/H40</f>
+        <f t="shared" ref="M40" si="21">$G40/H40</f>
         <v>19.901344289078015</v>
       </c>
       <c r="N40" s="9">
-        <f t="shared" ref="N40" si="21">$G40/I40</f>
+        <f t="shared" ref="N40" si="22">$G40/I40</f>
         <v>16.278514585888253</v>
       </c>
       <c r="O40" s="9">
-        <f t="shared" ref="O40" si="22">$G40/J40</f>
+        <f t="shared" ref="O40" si="23">$G40/J40</f>
         <v>14.429306029225401</v>
       </c>
       <c r="P40" s="9">
@@ -11003,7 +11019,7 @@
         <f>[37]Model!$Z$3</f>
         <v>2366.0300000000002</v>
       </c>
-      <c r="T40" s="31">
+      <c r="T40" s="30">
         <f t="shared" si="8"/>
         <v>2.8033139901015622</v>
       </c>
@@ -11051,7 +11067,7 @@
       </c>
     </row>
     <row r="41" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C41" s="7" t="s">
@@ -11094,15 +11110,15 @@
         <v>413.39704472070275</v>
       </c>
       <c r="M41" s="9">
-        <f t="shared" ref="M41:O42" si="23">$G41/H41</f>
+        <f t="shared" ref="M41:O42" si="24">$G41/H41</f>
         <v>38.501326219512343</v>
       </c>
       <c r="N41" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>22.940466489979588</v>
       </c>
       <c r="O41" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>13.896804358052199</v>
       </c>
       <c r="P41" s="9">
@@ -11121,8 +11137,8 @@
         <f>[38]Model!$BO$6</f>
         <v>3823</v>
       </c>
-      <c r="T41" s="31">
-        <f t="shared" ref="T41:T53" si="24">G41/S41</f>
+      <c r="T41" s="30">
+        <f t="shared" ref="T41:T53" si="25">G41/S41</f>
         <v>1.3213115354433695</v>
       </c>
       <c r="U41" s="11">
@@ -11169,7 +11185,7 @@
       </c>
     </row>
     <row r="42" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B42" s="27" t="s">
+      <c r="B42" s="26" t="s">
         <v>167</v>
       </c>
       <c r="C42" s="7" t="s">
@@ -11212,15 +11228,15 @@
         <v>396.42219656109609</v>
       </c>
       <c r="M42" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>23.851387377584334</v>
       </c>
       <c r="N42" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>17.475443592178202</v>
       </c>
       <c r="O42" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>14.606119208811638</v>
       </c>
       <c r="P42" s="9">
@@ -11239,8 +11255,8 @@
         <f>[39]Model!$AC$5</f>
         <v>672.3</v>
       </c>
-      <c r="T42" s="31">
-        <f t="shared" si="24"/>
+      <c r="T42" s="30">
+        <f t="shared" si="25"/>
         <v>6.5207273538598836</v>
       </c>
       <c r="U42" s="11">
@@ -11281,7 +11297,7 @@
       </c>
     </row>
     <row r="43" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B43" s="28" t="s">
+      <c r="B43" s="27" t="s">
         <v>175</v>
       </c>
       <c r="C43" s="7" t="s">
@@ -11289,19 +11305,19 @@
       </c>
       <c r="D43" s="12">
         <f>[40]Main!$D$3</f>
-        <v>22.57</v>
+        <v>47.13</v>
       </c>
       <c r="E43" s="8">
         <f>[40]Main!$D$5</f>
-        <v>4918.0030000000006</v>
+        <v>11678.814</v>
       </c>
       <c r="F43" s="8">
         <f>[40]Main!$D$8</f>
-        <v>364.29999999999995</v>
+        <v>697.19999999999993</v>
       </c>
       <c r="G43" s="8">
         <f>[40]Main!$D$9</f>
-        <v>4553.7030000000004</v>
+        <v>10981.614</v>
       </c>
       <c r="H43" s="8">
         <f>[40]Model!AA$18</f>
@@ -11309,19 +11325,19 @@
       </c>
       <c r="I43" s="8">
         <f>[40]Model!AB$18</f>
-        <v>-240.65150000000003</v>
+        <v>-241.196</v>
       </c>
       <c r="J43" s="8">
         <f>[40]Model!AC$18</f>
-        <v>-249.37895000000003</v>
+        <v>-251.43716000000001</v>
       </c>
       <c r="K43" s="8">
         <f>[40]Model!AD$18</f>
-        <v>-234.94165740000014</v>
+        <v>-239.27369940000014</v>
       </c>
       <c r="L43" s="8">
         <f>[40]Model!AE$18</f>
-        <v>-201.95642231800011</v>
+        <v>-209.42086391800015</v>
       </c>
       <c r="M43" s="9"/>
       <c r="N43" s="9"/>
@@ -11330,15 +11346,15 @@
       <c r="Q43" s="9"/>
       <c r="R43" s="9">
         <f>G43/[40]Model!$AL$18</f>
-        <v>9.6482710670175837</v>
+        <v>26.512239102639239</v>
       </c>
       <c r="S43" s="10">
         <f>[40]Model!$AA$3</f>
         <v>43.099999999999994</v>
       </c>
-      <c r="T43" s="31">
-        <f t="shared" si="24"/>
-        <v>105.65436194895594</v>
+      <c r="T43" s="30">
+        <f t="shared" si="25"/>
+        <v>254.79382830626452</v>
       </c>
       <c r="U43" s="11">
         <f>[40]Model!Z$22</f>
@@ -11356,7 +11372,7 @@
       </c>
       <c r="Z43" s="11">
         <f>[40]Model!$AP$30</f>
-        <v>-0.68463910360246483</v>
+        <v>-0.84815666913938215</v>
       </c>
       <c r="AA43" s="7" t="str">
         <f>[40]Model!$AP$31</f>
@@ -11378,7 +11394,7 @@
       </c>
     </row>
     <row r="44" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="26" t="s">
         <v>118</v>
       </c>
       <c r="C44" s="7" t="s">
@@ -11386,11 +11402,11 @@
       </c>
       <c r="D44" s="21">
         <f>[41]Main!$D$3</f>
-        <v>8.98</v>
+        <v>11.17</v>
       </c>
       <c r="E44" s="8">
         <f>[41]Main!$D$5</f>
-        <v>9241.3179999999993</v>
+        <v>11495.046999999999</v>
       </c>
       <c r="F44" s="8">
         <f>[41]Main!$D$8</f>
@@ -11398,7 +11414,7 @@
       </c>
       <c r="G44" s="8">
         <f>[41]Main!$D$9</f>
-        <v>4372.1179999999995</v>
+        <v>6625.8469999999988</v>
       </c>
       <c r="H44" s="8">
         <f>[41]Model!R25</f>
@@ -11421,36 +11437,36 @@
         <v>639.76869922577112</v>
       </c>
       <c r="M44" s="9">
-        <f t="shared" ref="M44:Q48" si="25">$G44/H44</f>
-        <v>9.2427156175185079</v>
+        <f t="shared" ref="M44:Q48" si="26">$G44/H44</f>
+        <v>14.007128706541808</v>
       </c>
       <c r="N44" s="9">
-        <f t="shared" si="25"/>
-        <v>8.1788615191660483</v>
+        <f t="shared" si="26"/>
+        <v>12.394881624919959</v>
       </c>
       <c r="O44" s="9">
-        <f t="shared" si="25"/>
-        <v>7.5562825996239029</v>
+        <f t="shared" si="26"/>
+        <v>11.451377202964384</v>
       </c>
       <c r="P44" s="9">
-        <f t="shared" si="25"/>
-        <v>7.149941238926969</v>
+        <f t="shared" si="26"/>
+        <v>10.835575962981908</v>
       </c>
       <c r="Q44" s="9">
-        <f t="shared" si="25"/>
-        <v>6.8339041989566001</v>
+        <f t="shared" si="26"/>
+        <v>10.356628900442301</v>
       </c>
       <c r="R44" s="9">
         <f>G44/[41]Model!$AB$25</f>
-        <v>5.8821043501978698</v>
+        <v>8.9141975267926217</v>
       </c>
       <c r="S44" s="19">
         <f>[41]Model!$Q$12</f>
         <v>1537.2</v>
       </c>
-      <c r="T44" s="31">
-        <f t="shared" si="24"/>
-        <v>2.8442089513400983</v>
+      <c r="T44" s="30">
+        <f t="shared" si="25"/>
+        <v>4.3103350247202696</v>
       </c>
       <c r="U44" s="11">
         <f>[41]Model!P$36</f>
@@ -11474,11 +11490,11 @@
       </c>
       <c r="Z44" s="11">
         <f>[41]Model!$AE$42</f>
-        <v>0.29282192477201852</v>
+        <v>3.9350123943842963E-2</v>
       </c>
       <c r="AA44" s="7" t="str">
         <f>[41]Model!$AE$43</f>
-        <v>Undervalued</v>
+        <v>Fairly valued</v>
       </c>
       <c r="AB44" s="7" t="s">
         <v>94</v>
@@ -11539,23 +11555,23 @@
         <v>542.918339415834</v>
       </c>
       <c r="M45" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>11.628233280073065</v>
       </c>
       <c r="N45" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>10.406077979668463</v>
       </c>
       <c r="O45" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>9.4962160444857595</v>
       </c>
       <c r="P45" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8.7628369974055786</v>
       </c>
       <c r="Q45" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8.2309056900362272</v>
       </c>
       <c r="R45" s="9">
@@ -11566,8 +11582,8 @@
         <f>[42]Model!$AD$6/[42]Main!$D$13</f>
         <v>3299.9649122807009</v>
       </c>
-      <c r="T45" s="31">
-        <f t="shared" si="24"/>
+      <c r="T45" s="30">
+        <f t="shared" si="25"/>
         <v>1.3541688375208674</v>
       </c>
       <c r="U45" s="11">
@@ -11608,7 +11624,7 @@
       </c>
     </row>
     <row r="46" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B46" s="25" t="s">
+      <c r="B46" s="26" t="s">
         <v>130</v>
       </c>
       <c r="C46" s="7" t="s">
@@ -11616,19 +11632,19 @@
       </c>
       <c r="D46" s="12">
         <f>[43]Main!$D$3</f>
-        <v>13.77</v>
+        <v>13.28</v>
       </c>
       <c r="E46" s="8">
         <f>[43]Main!$D$5</f>
-        <v>4035.9870000000001</v>
+        <v>3715.7440000000001</v>
       </c>
       <c r="F46" s="8">
         <f>[43]Main!$D$10</f>
-        <v>-1257.5441696113076</v>
+        <v>-1344.0106007067136</v>
       </c>
       <c r="G46" s="8">
         <f>[43]Main!$D$11</f>
-        <v>5293.5311696113076</v>
+        <v>5059.754600706714</v>
       </c>
       <c r="H46" s="8">
         <f>[43]Model!AM18/[43]Main!$D$13</f>
@@ -11636,51 +11652,51 @@
       </c>
       <c r="I46" s="8">
         <f>[43]Model!AN18/[43]Main!$D$13</f>
-        <v>414.80106289752655</v>
+        <v>438.60357879858697</v>
       </c>
       <c r="J46" s="8">
         <f>[43]Model!AO18/[43]Main!$D$13</f>
-        <v>492.43325546819767</v>
+        <v>541.4587499257949</v>
       </c>
       <c r="K46" s="8">
         <f>[43]Model!AP18/[43]Main!$D$13</f>
-        <v>535.46431115782684</v>
+        <v>589.69790701240299</v>
       </c>
       <c r="L46" s="8">
         <f>[43]Model!AQ18/[43]Main!$D$13</f>
-        <v>567.73125562529424</v>
+        <v>626.05711041012842</v>
       </c>
       <c r="M46" s="9">
-        <f t="shared" si="25"/>
-        <v>-19.800017459688092</v>
+        <f t="shared" si="26"/>
+        <v>-18.92559545334392</v>
       </c>
       <c r="N46" s="9">
-        <f t="shared" si="25"/>
-        <v>12.761614284771094</v>
+        <f t="shared" si="26"/>
+        <v>11.536054070890803</v>
       </c>
       <c r="O46" s="9">
-        <f t="shared" si="25"/>
-        <v>10.749743464377325</v>
+        <f t="shared" si="26"/>
+        <v>9.3446723345040343</v>
       </c>
       <c r="P46" s="9">
-        <f t="shared" si="25"/>
-        <v>9.8858711202716396</v>
+        <f t="shared" si="26"/>
+        <v>8.5802485315592154</v>
       </c>
       <c r="Q46" s="9">
-        <f t="shared" si="25"/>
-        <v>9.3240087051065359</v>
+        <f t="shared" si="26"/>
+        <v>8.081937760266122</v>
       </c>
       <c r="R46" s="9">
         <f>G46/([43]Model!$AX$18/[43]Main!$D$13)</f>
-        <v>8.6391255971361911</v>
+        <v>7.4486617629369425</v>
       </c>
       <c r="S46" s="10">
         <f>[43]Model!$AM$6/[43]Main!$D$13</f>
         <v>2250.7420494699645</v>
       </c>
-      <c r="T46" s="31">
-        <f t="shared" si="24"/>
-        <v>2.3519048621577494</v>
+      <c r="T46" s="30">
+        <f t="shared" si="25"/>
+        <v>2.2480384199949763</v>
       </c>
       <c r="U46" s="11">
         <f>[43]Model!AL$25</f>
@@ -11704,11 +11720,11 @@
       </c>
       <c r="Z46" s="11">
         <f>[43]Model!$BC$31</f>
-        <v>0.21988243594280066</v>
+        <v>0.44726581851393532</v>
       </c>
       <c r="AA46" s="7" t="str">
         <f>[43]Model!$BC$32</f>
-        <v>Slightly undervalued</v>
+        <v>Undervalued</v>
       </c>
       <c r="AB46" s="7" t="s">
         <v>94</v>
@@ -11718,15 +11734,15 @@
       </c>
       <c r="AE46" s="17">
         <f>[43]Main!$E$3</f>
-        <v>45780</v>
+        <v>45804</v>
       </c>
       <c r="AF46" s="17">
         <f>[43]Main!$G$3</f>
-        <v>45832</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="47" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="29" t="s">
         <v>102</v>
       </c>
       <c r="C47" s="7" t="s">
@@ -11769,23 +11785,23 @@
         <v>21.999999999999979</v>
       </c>
       <c r="M47" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-24.017395422257316</v>
       </c>
       <c r="N47" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-27.414450450450488</v>
       </c>
       <c r="O47" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-1.6054679750976046</v>
       </c>
       <c r="P47" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-149.16686274509783</v>
       </c>
       <c r="Q47" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>138.31836363636376</v>
       </c>
       <c r="R47" s="9"/>
@@ -11793,8 +11809,8 @@
         <f>[44]Model!$AD$3</f>
         <v>1426.5</v>
       </c>
-      <c r="T47" s="31">
-        <f t="shared" si="24"/>
+      <c r="T47" s="30">
+        <f t="shared" si="25"/>
         <v>2.1331959341044513</v>
       </c>
       <c r="U47" s="11">
@@ -11835,7 +11851,7 @@
       </c>
     </row>
     <row r="48" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="26" t="s">
         <v>149</v>
       </c>
       <c r="C48" s="7" t="s">
@@ -11843,11 +11859,11 @@
       </c>
       <c r="D48" s="12">
         <f>[45]Main!$D$3</f>
-        <v>16.87</v>
+        <v>17.59</v>
       </c>
       <c r="E48" s="8">
         <f>[45]Main!$D$5</f>
-        <v>1509.865</v>
+        <v>1574.3050000000001</v>
       </c>
       <c r="F48" s="8">
         <f>[45]Main!$D$8</f>
@@ -11855,7 +11871,7 @@
       </c>
       <c r="G48" s="8">
         <f>[45]Main!$D$9</f>
-        <v>1383.0650000000001</v>
+        <v>1447.5050000000001</v>
       </c>
       <c r="H48" s="8">
         <f>[45]Model!AB27</f>
@@ -11878,36 +11894,36 @@
         <v>186.25340380022882</v>
       </c>
       <c r="M48" s="9">
-        <f t="shared" si="25"/>
-        <v>12.212968980693296</v>
+        <f t="shared" si="26"/>
+        <v>12.781997711169359</v>
       </c>
       <c r="N48" s="9">
-        <f t="shared" si="25"/>
-        <v>10.005283525268531</v>
+        <f t="shared" si="26"/>
+        <v>10.471451399062103</v>
       </c>
       <c r="O48" s="9">
-        <f t="shared" si="25"/>
-        <v>8.2984694698613559</v>
+        <f t="shared" si="26"/>
+        <v>8.6851131725346704</v>
       </c>
       <c r="P48" s="9">
-        <f t="shared" si="25"/>
-        <v>7.7545507600549985</v>
+        <f t="shared" si="26"/>
+        <v>8.1158521095779381</v>
       </c>
       <c r="Q48" s="9">
-        <f t="shared" si="25"/>
-        <v>7.4257166407731487</v>
+        <f t="shared" si="26"/>
+        <v>7.7716968950138554</v>
       </c>
       <c r="R48" s="9">
         <f>G48/[45]Model!$AL$27</f>
-        <v>6.2758149935393668</v>
+        <v>6.5682188344171832</v>
       </c>
       <c r="S48" s="10">
         <f>[45]Model!$AA$8</f>
         <v>482.9</v>
       </c>
-      <c r="T48" s="31">
-        <f t="shared" si="24"/>
-        <v>2.8640815903913857</v>
+      <c r="T48" s="30">
+        <f t="shared" si="25"/>
+        <v>2.9975253675709261</v>
       </c>
       <c r="U48" s="11">
         <f>[45]Model!Z$34</f>
@@ -11931,7 +11947,7 @@
       </c>
       <c r="Z48" s="11">
         <f>[45]Model!$AO$47</f>
-        <v>0.11399138868960712</v>
+        <v>6.8393105582357894E-2</v>
       </c>
       <c r="AA48" s="7" t="str">
         <f>[45]Model!$AO$48</f>
@@ -11945,7 +11961,7 @@
       </c>
       <c r="AE48" s="17">
         <f>[45]Main!$E$3</f>
-        <v>45776</v>
+        <v>45804</v>
       </c>
       <c r="AF48" s="17">
         <f>[45]Main!$G$3</f>
@@ -11953,7 +11969,7 @@
       </c>
     </row>
     <row r="49" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B49" s="28" t="s">
+      <c r="B49" s="29" t="s">
         <v>70</v>
       </c>
       <c r="C49" s="7" t="s">
@@ -12008,8 +12024,8 @@
         <f>[46]Model!$AR$3</f>
         <v>1402.8980000000001</v>
       </c>
-      <c r="T49" s="31">
-        <f t="shared" si="24"/>
+      <c r="T49" s="30">
+        <f t="shared" si="25"/>
         <v>0.5218412172517175</v>
       </c>
       <c r="U49" s="11">
@@ -12050,7 +12066,7 @@
       </c>
     </row>
     <row r="50" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="29" t="s">
         <v>90</v>
       </c>
       <c r="C50" s="7" t="s">
@@ -12117,8 +12133,8 @@
         <f>[47]Model!$AK$3</f>
         <v>1316.4</v>
       </c>
-      <c r="T50" s="31">
-        <f t="shared" si="24"/>
+      <c r="T50" s="30">
+        <f t="shared" si="25"/>
         <v>0.63598678213309023</v>
       </c>
       <c r="U50" s="11">
@@ -12158,7 +12174,7 @@
       </c>
     </row>
     <row r="51" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="29" t="s">
         <v>155</v>
       </c>
       <c r="C51" s="7" t="s">
@@ -12216,8 +12232,8 @@
         <f>[48]Model!$AA$8</f>
         <v>628.79999999999995</v>
       </c>
-      <c r="T51" s="31">
-        <f t="shared" si="24"/>
+      <c r="T51" s="30">
+        <f t="shared" si="25"/>
         <v>1.2062531806615777</v>
       </c>
       <c r="U51" s="11">
@@ -12258,7 +12274,7 @@
       </c>
     </row>
     <row r="52" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B52" s="29" t="s">
+      <c r="B52" s="32" t="s">
         <v>188</v>
       </c>
       <c r="C52" s="7" t="s">
@@ -12266,19 +12282,19 @@
       </c>
       <c r="D52" s="21">
         <f>[49]Main!$D$3</f>
-        <v>12.25</v>
+        <v>12.02</v>
       </c>
       <c r="E52" s="8">
         <f>[49]Main!$D$5</f>
-        <v>426.29999999999995</v>
+        <v>427.91199999999998</v>
       </c>
       <c r="F52" s="8">
         <f>[49]Main!$D$8</f>
-        <v>-9.2000000000000028</v>
+        <v>-67</v>
       </c>
       <c r="G52" s="8">
         <f>[49]Main!$D$9</f>
-        <v>435.49999999999994</v>
+        <v>494.91199999999998</v>
       </c>
       <c r="H52" s="8">
         <f>[49]Model!Y$18</f>
@@ -12290,47 +12306,47 @@
       </c>
       <c r="J52" s="8">
         <f>[49]Model!AA$18</f>
-        <v>51.848129999999976</v>
+        <v>53.957115999999999</v>
       </c>
       <c r="K52" s="8">
         <f>[49]Model!AB$18</f>
-        <v>55.878580949999979</v>
+        <v>59.411664090000002</v>
       </c>
       <c r="L52" s="8">
         <f>[49]Model!AC$18</f>
-        <v>60.321196610999991</v>
+        <v>64.116644099999988</v>
       </c>
       <c r="M52" s="9">
-        <f t="shared" ref="M52:Q52" si="26">$G52/H52</f>
-        <v>14.13961038961039</v>
+        <f t="shared" ref="M52:Q52" si="27">$G52/H52</f>
+        <v>16.068571428571428</v>
       </c>
       <c r="N52" s="9">
-        <f t="shared" si="26"/>
-        <v>9.8772544181151822</v>
+        <f t="shared" si="27"/>
+        <v>11.224734187320831</v>
       </c>
       <c r="O52" s="9">
-        <f t="shared" si="26"/>
-        <v>8.3995314777987193</v>
+        <f t="shared" si="27"/>
+        <v>9.1723212189472836</v>
       </c>
       <c r="P52" s="9">
-        <f t="shared" si="26"/>
-        <v>7.7936839589696154</v>
+        <f t="shared" si="27"/>
+        <v>8.330216087707635</v>
       </c>
       <c r="Q52" s="9">
-        <f t="shared" si="26"/>
-        <v>7.2196843641623563</v>
+        <f t="shared" si="27"/>
+        <v>7.7189317523872099</v>
       </c>
       <c r="R52" s="9">
         <f>G52/[49]Model!$AJ$18</f>
-        <v>4.5433065175162497</v>
+        <v>4.7350891887931654</v>
       </c>
       <c r="S52" s="10">
         <f>[49]Model!$Y$3</f>
         <v>127.2</v>
       </c>
-      <c r="T52" s="31">
-        <f t="shared" si="24"/>
-        <v>3.4237421383647795</v>
+      <c r="T52" s="30">
+        <f t="shared" si="25"/>
+        <v>3.8908176100628928</v>
       </c>
       <c r="U52" s="11">
         <f>[49]Model!$X$22</f>
@@ -12354,7 +12370,7 @@
       </c>
       <c r="Z52" s="11">
         <f>[49]Model!$AM$31</f>
-        <v>0.5144913850915962</v>
+        <v>0.51669166859676285</v>
       </c>
       <c r="AA52" s="7" t="str">
         <f>[49]Model!$AM$32</f>
@@ -12368,15 +12384,15 @@
       </c>
       <c r="AE52" s="17">
         <f>[49]Main!$E$3</f>
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="AF52" s="17">
         <f>[49]Main!$G$3</f>
-        <v>45792</v>
+        <v>45883</v>
       </c>
     </row>
     <row r="53" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B53" s="29" t="s">
+      <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C53" s="7" t="s">
@@ -12384,19 +12400,19 @@
       </c>
       <c r="D53" s="12">
         <f>[50]Main!$D$3</f>
-        <v>6.1</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="E53" s="8">
         <f>[50]Main!$D$5</f>
-        <v>85.399999999999991</v>
+        <v>127.05000000000001</v>
       </c>
       <c r="F53" s="8">
         <f>[50]Main!$D$8</f>
-        <v>-17.099999999999994</v>
+        <v>-21.599999999999994</v>
       </c>
       <c r="G53" s="8">
         <f>[50]Main!$D$9</f>
-        <v>102.49999999999999</v>
+        <v>148.65</v>
       </c>
       <c r="H53" s="8">
         <f>[50]Model!AU23</f>
@@ -12404,45 +12420,45 @@
       </c>
       <c r="I53" s="8">
         <f>[50]Model!AV23</f>
-        <v>0.61426499999996054</v>
+        <v>-2.171889999999951</v>
       </c>
       <c r="J53" s="8">
         <f>[50]Model!AW23</f>
-        <v>13.698367175999968</v>
+        <v>11.015718799999986</v>
       </c>
       <c r="K53" s="8">
         <f>[50]Model!AX23</f>
-        <v>17.129505912479978</v>
+        <v>14.285659768000007</v>
       </c>
       <c r="L53" s="8">
         <f>[50]Model!AY23</f>
-        <v>19.595469755830393</v>
+        <v>16.629577081600026</v>
       </c>
       <c r="M53" s="9"/>
       <c r="N53" s="9">
         <f>$G53/I53</f>
-        <v>166.86609199613613</v>
+        <v>-68.442692769893213</v>
       </c>
       <c r="O53" s="9">
         <f>$G53/J53</f>
-        <v>7.482643637964653</v>
+        <v>13.494353178296471</v>
       </c>
       <c r="P53" s="9">
         <f>$G53/K53</f>
-        <v>5.983827001415257</v>
+        <v>10.405539710036859</v>
       </c>
       <c r="Q53" s="9">
         <f>$G53/L53</f>
-        <v>5.2308008574023779</v>
+        <v>8.9388923885788643</v>
       </c>
       <c r="R53" s="9"/>
       <c r="S53" s="10">
         <f>[50]Model!$AU$7</f>
         <v>206.39999999999998</v>
       </c>
-      <c r="T53" s="31">
-        <f t="shared" si="24"/>
-        <v>0.49660852713178294</v>
+      <c r="T53" s="30">
+        <f t="shared" si="25"/>
+        <v>0.72020348837209314</v>
       </c>
       <c r="U53" s="11">
         <f>[50]Model!AT$31</f>
@@ -12460,11 +12476,11 @@
       </c>
       <c r="Z53" s="11">
         <f>[50]Model!$BI$39</f>
-        <v>0.51120802229567275</v>
+        <v>-0.18276999339899935</v>
       </c>
       <c r="AA53" s="7" t="str">
         <f>[50]Model!$BI$40</f>
-        <v>Heavily undervalued</v>
+        <v>Slightly overvalued</v>
       </c>
       <c r="AB53" s="7" t="s">
         <v>65</v>
@@ -12474,15 +12490,15 @@
       </c>
       <c r="AE53" s="17">
         <f>[50]Main!$E$3</f>
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="AF53" s="17">
         <f>[50]Main!$G$3</f>
-        <v>45777</v>
+        <v>45875</v>
       </c>
     </row>
     <row r="54" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B54" s="30" t="s">
+      <c r="B54" s="29" t="s">
         <v>87</v>
       </c>
       <c r="C54" s="7" t="s">
@@ -12549,7 +12565,7 @@
       </c>
     </row>
     <row r="55" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="26" t="s">
         <v>153</v>
       </c>
       <c r="C55" s="7" t="s">
@@ -12557,90 +12573,90 @@
       </c>
       <c r="D55" s="12">
         <f>[52]Main!$D$3</f>
-        <v>0.56620000000000004</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E55" s="8">
         <f>[52]Main!$D$5</f>
-        <v>59.507620000000003</v>
+        <v>104.47865999999999</v>
       </c>
       <c r="F55" s="8">
         <f>[52]Main!$D$8</f>
-        <v>401.09999999999997</v>
+        <v>63.900000000000006</v>
       </c>
       <c r="G55" s="8">
         <f>[52]Main!$D$9</f>
-        <v>-341.59237999999993</v>
+        <v>40.578659999999985</v>
       </c>
       <c r="H55" s="8">
-        <f>[52]Model!AD$15</f>
+        <f>[52]Model!AD$16</f>
         <v>-29.899999999999945</v>
       </c>
       <c r="I55" s="8">
-        <f>[52]Model!AE$15</f>
-        <v>-99.47824999999996</v>
+        <f>[52]Model!AE$16</f>
+        <v>-76.877200000000073</v>
       </c>
       <c r="J55" s="8">
-        <f>[52]Model!AF$15</f>
-        <v>-83.16289500000002</v>
+        <f>[52]Model!AF$16</f>
+        <v>-44.391073200000065</v>
       </c>
       <c r="K55" s="8">
-        <f>[52]Model!AG$15</f>
-        <v>-59.940097869999995</v>
+        <f>[52]Model!AG$16</f>
+        <v>-18.839740000000013</v>
       </c>
       <c r="L55" s="8">
-        <f>[52]Model!AH$15</f>
-        <v>-44.752185381000011</v>
+        <f>[52]Model!AH$16</f>
+        <v>-1.8089114494499596</v>
       </c>
       <c r="M55" s="9">
-        <f t="shared" ref="M55:Q56" si="27">$G55/H55</f>
-        <v>11.42449431438129</v>
+        <f t="shared" ref="M55:Q56" si="28">$G55/H55</f>
+        <v>-1.3571458193979953</v>
       </c>
       <c r="N55" s="9">
-        <f t="shared" si="27"/>
-        <v>3.4338398594667687</v>
+        <f t="shared" si="28"/>
+        <v>-0.52783738221475218</v>
       </c>
       <c r="O55" s="9">
-        <f t="shared" si="27"/>
-        <v>4.1075094848489808</v>
+        <f t="shared" si="28"/>
+        <v>-0.91411757082727896</v>
       </c>
       <c r="P55" s="9">
-        <f t="shared" si="27"/>
-        <v>5.698895933417667</v>
+        <f t="shared" si="28"/>
+        <v>-2.1538864124451802</v>
       </c>
       <c r="Q55" s="9">
-        <f t="shared" si="27"/>
-        <v>7.6329765148190152</v>
+        <f t="shared" si="28"/>
+        <v>-22.432640366303637</v>
       </c>
       <c r="R55" s="9"/>
       <c r="S55" s="10">
         <f>[52]Model!$AD$3</f>
         <v>617.6</v>
       </c>
-      <c r="T55" s="31">
-        <f t="shared" ref="T55:T60" si="28">G55/S55</f>
-        <v>-0.55309647020725372</v>
+      <c r="T55" s="30">
+        <f t="shared" ref="T55:T60" si="29">G55/S55</f>
+        <v>6.5703788860103599E-2</v>
       </c>
       <c r="U55" s="11">
-        <f>[52]Model!AC$19</f>
+        <f>[52]Model!AC$20</f>
         <v>-6.5727699530516381E-2</v>
       </c>
       <c r="V55" s="11">
-        <f>[52]Model!AD$19</f>
+        <f>[52]Model!AD$20</f>
         <v>-0.13791178112786151</v>
       </c>
       <c r="W55" s="11"/>
       <c r="X55" s="11"/>
       <c r="Y55" s="11">
-        <f>[52]Model!$AS$21</f>
+        <f>[52]Model!$AS$22</f>
         <v>0.12</v>
       </c>
       <c r="Z55" s="11">
-        <f>[52]Model!$AS$27</f>
-        <v>0.25066821021641306</v>
+        <f>[52]Model!$AS$28</f>
+        <v>-9.9901697844603232E-2</v>
       </c>
       <c r="AA55" s="7" t="str">
-        <f>[52]Model!$AS$28</f>
-        <v>Slightly undervalued</v>
+        <f>[52]Model!$AS$29</f>
+        <v>Slightly overvalued</v>
       </c>
       <c r="AB55" s="7" t="s">
         <v>65</v>
@@ -12650,15 +12666,15 @@
       </c>
       <c r="AE55" s="17">
         <f>[52]Main!$E$3</f>
-        <v>45751</v>
+        <v>45799</v>
       </c>
       <c r="AF55" s="17">
         <f>[52]Main!$G$3</f>
-        <v>45802</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="56" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B56" s="27" t="s">
+      <c r="B56" s="29" t="s">
         <v>106</v>
       </c>
       <c r="C56" s="7" t="s">
@@ -12701,23 +12717,23 @@
         <v>-18.632540500000005</v>
       </c>
       <c r="M56" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1.7824068157614481</v>
       </c>
       <c r="N56" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>2.7909319059172728</v>
       </c>
       <c r="O56" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>3.9787824262043157</v>
       </c>
       <c r="P56" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>5.709461081854144</v>
       </c>
       <c r="Q56" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8.9825646695897401</v>
       </c>
       <c r="R56" s="9">
@@ -12728,8 +12744,8 @@
         <f>[53]Model!$AI$3</f>
         <v>95.5</v>
       </c>
-      <c r="T56" s="31">
-        <f t="shared" si="28"/>
+      <c r="T56" s="30">
+        <f t="shared" si="29"/>
         <v>-1.752544502617801</v>
       </c>
       <c r="U56" s="11">
@@ -12770,7 +12786,7 @@
       </c>
     </row>
     <row r="57" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B57" s="25" t="s">
+      <c r="B57" s="28" t="s">
         <v>109</v>
       </c>
       <c r="C57" s="7" t="s">
@@ -12837,8 +12853,8 @@
         <f>[54]Model!$T$3</f>
         <v>46.9</v>
       </c>
-      <c r="T57" s="31">
-        <f t="shared" si="28"/>
+      <c r="T57" s="30">
+        <f t="shared" si="29"/>
         <v>2.3397441364605545</v>
       </c>
       <c r="U57" s="11">
@@ -12879,7 +12895,7 @@
       </c>
     </row>
     <row r="58" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B58" s="29" t="s">
+      <c r="B58" s="28" t="s">
         <v>141</v>
       </c>
       <c r="C58" s="7" t="s">
@@ -12887,11 +12903,11 @@
       </c>
       <c r="D58" s="12">
         <f>[55]Main!$D$3</f>
-        <v>3.72</v>
+        <v>5.6</v>
       </c>
       <c r="E58" s="8">
         <f>[55]Main!$D$5</f>
-        <v>78.492000000000004</v>
+        <v>118.16</v>
       </c>
       <c r="F58" s="8">
         <f>[55]Main!$D$8</f>
@@ -12899,7 +12915,7 @@
       </c>
       <c r="G58" s="8">
         <f>[55]Main!$D$9</f>
-        <v>-49.507999999999996</v>
+        <v>-9.8400000000000034</v>
       </c>
       <c r="H58" s="8">
         <f>[55]Model!Z23</f>
@@ -12923,35 +12939,35 @@
       </c>
       <c r="M58" s="9">
         <f>$E$58/H58</f>
-        <v>2.4997452229299362</v>
+        <v>3.7630573248407639</v>
       </c>
       <c r="N58" s="9">
         <f>$E$58/I58</f>
-        <v>1.5921298174442193</v>
+        <v>2.3967545638945236</v>
       </c>
       <c r="O58" s="9">
         <f>$E$58/J58</f>
-        <v>0.6867191601049869</v>
+        <v>1.0337707786526684</v>
       </c>
       <c r="P58" s="9">
         <f>$E$58/K58</f>
-        <v>0.62493630573248415</v>
+        <v>0.9407643312101911</v>
       </c>
       <c r="Q58" s="9">
         <f>$E$58/L58</f>
-        <v>0.64022838499184342</v>
+        <v>0.96378466557911913</v>
       </c>
       <c r="R58" s="9">
         <f>E58/[55]Model!$AO$31</f>
-        <v>0.97320338848112853</v>
+        <v>1.4650373590038492</v>
       </c>
       <c r="S58" s="10">
         <f>[55]Model!$AE$13</f>
         <v>139.44</v>
       </c>
-      <c r="T58" s="31">
-        <f t="shared" si="28"/>
-        <v>-0.35504876649454958</v>
+      <c r="T58" s="30">
+        <f t="shared" si="29"/>
+        <v>-7.0567986230636856E-2</v>
       </c>
       <c r="U58" s="11">
         <f>[55]Model!AD$44</f>
@@ -12969,11 +12985,11 @@
       </c>
       <c r="Z58" s="11">
         <f>[55]Model!$AS$48</f>
-        <v>0.5117314448778445</v>
+        <v>4.2216026688539632E-3</v>
       </c>
       <c r="AA58" s="7" t="str">
         <f>[55]Model!$AS$49</f>
-        <v>Heavily undervalued</v>
+        <v>Fairly valued</v>
       </c>
       <c r="AB58" s="7" t="s">
         <v>143</v>
@@ -12983,7 +12999,7 @@
       </c>
       <c r="AE58" s="17">
         <f>[55]Main!$E$3</f>
-        <v>45772</v>
+        <v>45804</v>
       </c>
       <c r="AF58" s="17">
         <f>[55]Main!$G$3</f>
@@ -12991,7 +13007,7 @@
       </c>
     </row>
     <row r="59" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="29" t="s">
         <v>157</v>
       </c>
       <c r="C59" s="7" t="s">
@@ -13055,8 +13071,8 @@
         <f>[56]Model!$AA$3</f>
         <v>12.3</v>
       </c>
-      <c r="T59" s="31">
-        <f t="shared" si="28"/>
+      <c r="T59" s="30">
+        <f t="shared" si="29"/>
         <v>1.7074796747967484</v>
       </c>
       <c r="U59" s="11">
@@ -13097,7 +13113,7 @@
       </c>
     </row>
     <row r="60" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B60" s="29" t="s">
+      <c r="B60" s="28" t="s">
         <v>169</v>
       </c>
       <c r="C60" s="7" t="s">
@@ -13161,8 +13177,8 @@
         <f>[57]Model!$O$5</f>
         <v>334.37624999999997</v>
       </c>
-      <c r="T60" s="31">
-        <f t="shared" si="28"/>
+      <c r="T60" s="30">
+        <f t="shared" si="29"/>
         <v>-0.29136993340476636</v>
       </c>
       <c r="U60" s="11">
@@ -13203,7 +13219,7 @@
       </c>
     </row>
     <row r="61" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B61" s="27" t="s">
+      <c r="B61" s="26" t="s">
         <v>165</v>
       </c>
       <c r="C61" s="7" t="s">
@@ -13490,15 +13506,15 @@
     <hyperlink ref="B19" r:id="rId7" xr:uid="{5F163C80-38C2-464D-A54B-1991DBE92DAE}"/>
     <hyperlink ref="B15" r:id="rId8" display="Salesforce.com" xr:uid="{93D87434-2443-4971-9137-D6F1AC82040E}"/>
     <hyperlink ref="B41" r:id="rId9" xr:uid="{0A593B9D-DB8E-4D20-9333-4BFFE4871798}"/>
-    <hyperlink ref="B38" r:id="rId10" xr:uid="{10E4FD51-7038-45AA-AC3C-1594C7E69E7F}"/>
+    <hyperlink ref="B39" r:id="rId10" xr:uid="{10E4FD51-7038-45AA-AC3C-1594C7E69E7F}"/>
     <hyperlink ref="B53" r:id="rId11" xr:uid="{E2DF0D1C-29B2-4E00-84AF-31CF689ABFB3}"/>
     <hyperlink ref="B14" r:id="rId12" xr:uid="{EE0E652E-C275-4798-8F34-5D9204EC3F09}"/>
     <hyperlink ref="B31" r:id="rId13" xr:uid="{00E5FEAB-AC7E-4A58-8E54-A8AFBC200B27}"/>
     <hyperlink ref="B10" r:id="rId14" xr:uid="{36D0E700-6724-4ECE-805A-A69DF2511058}"/>
-    <hyperlink ref="B39" r:id="rId15" xr:uid="{D6E6111D-085D-4AD7-B108-54A545359473}"/>
+    <hyperlink ref="B38" r:id="rId15" xr:uid="{D6E6111D-085D-4AD7-B108-54A545359473}"/>
     <hyperlink ref="B49" r:id="rId16" xr:uid="{BAA20A0A-ED96-43D5-9159-C8669F65FEC8}"/>
     <hyperlink ref="B17" r:id="rId17" xr:uid="{499D2878-2294-4D2B-97BC-62D9C52B6F67}"/>
-    <hyperlink ref="B28" r:id="rId18" xr:uid="{26827201-FDC2-4F19-A8D2-20FC3BB18B40}"/>
+    <hyperlink ref="B27" r:id="rId18" xr:uid="{26827201-FDC2-4F19-A8D2-20FC3BB18B40}"/>
     <hyperlink ref="B54" r:id="rId19" xr:uid="{582B8A04-7FC6-4DFB-B7AE-827EA6E42A84}"/>
     <hyperlink ref="B26" r:id="rId20" xr:uid="{4DE42159-792A-4573-831E-56201D6A438A}"/>
     <hyperlink ref="B32" r:id="rId21" xr:uid="{E573422A-BA41-412F-AE13-CE6E5F747D4C}"/>
@@ -13511,12 +13527,12 @@
     <hyperlink ref="B57" r:id="rId28" xr:uid="{966096F2-578C-439D-9F69-51648E2559C1}"/>
     <hyperlink ref="B5" r:id="rId29" xr:uid="{72B93C8C-F457-48A0-AAA2-2D120A01F301}"/>
     <hyperlink ref="B24" r:id="rId30" xr:uid="{521D2BEF-7C6B-4E69-B7DB-C4A11DC7F03D}"/>
-    <hyperlink ref="B27" r:id="rId31" xr:uid="{726807AA-7E47-4743-9CB3-25D49F7C8821}"/>
+    <hyperlink ref="B28" r:id="rId31" xr:uid="{726807AA-7E47-4743-9CB3-25D49F7C8821}"/>
     <hyperlink ref="B12" r:id="rId32" xr:uid="{15312B10-4081-4DD8-B770-7475AD3247C2}"/>
     <hyperlink ref="B13" r:id="rId33" xr:uid="{DA6C35BB-FDB4-4FCC-862D-D80F72891D1C}"/>
     <hyperlink ref="B44" r:id="rId34" xr:uid="{21B77EB6-7439-4B9C-B015-92F05D642187}"/>
     <hyperlink ref="B30" r:id="rId35" xr:uid="{992F30A7-9484-40C5-B181-EF3E2B75BB5B}"/>
-    <hyperlink ref="B23" r:id="rId36" xr:uid="{D71D0207-8577-4517-9CFA-69A248404CEE}"/>
+    <hyperlink ref="B21" r:id="rId36" xr:uid="{D71D0207-8577-4517-9CFA-69A248404CEE}"/>
     <hyperlink ref="B46" r:id="rId37" xr:uid="{50E1C81F-2265-4E38-B629-C63B8E7103B8}"/>
     <hyperlink ref="B34" r:id="rId38" display="SOFI.xlsx" xr:uid="{56EADF64-15FA-4DC2-B8F1-8E237685384B}"/>
     <hyperlink ref="B58" r:id="rId39" xr:uid="{EE9850D5-05A9-4AEF-B4C3-F4C54EBE90C5}"/>
@@ -13528,7 +13544,7 @@
     <hyperlink ref="B74" r:id="rId45" xr:uid="{DE49A12B-6A45-47DC-94D1-4C4CC03A6F40}"/>
     <hyperlink ref="B61" r:id="rId46" xr:uid="{40AFBA70-BAFD-48F6-B0BE-86FDE0718294}"/>
     <hyperlink ref="B59" r:id="rId47" xr:uid="{F340AFAD-8588-4C00-B23B-2A90F3B6AD07}"/>
-    <hyperlink ref="B22" r:id="rId48" xr:uid="{69026323-396B-43F9-BC64-FC907C80D469}"/>
+    <hyperlink ref="B23" r:id="rId48" xr:uid="{69026323-396B-43F9-BC64-FC907C80D469}"/>
     <hyperlink ref="B60" r:id="rId49" xr:uid="{FF0A9E29-1E9D-4622-8331-45E15C5FC212}"/>
     <hyperlink ref="B20" r:id="rId50" xr:uid="{CF98E437-C519-4533-BBF7-B4AB4704929D}"/>
     <hyperlink ref="B43" r:id="rId51" xr:uid="{38D75976-69D3-4C6C-B181-44019574BD92}"/>
@@ -13537,7 +13553,7 @@
     <hyperlink ref="B52" r:id="rId54" xr:uid="{C56234F2-911B-4144-AA8B-EA39512F2749}"/>
     <hyperlink ref="B33" r:id="rId55" xr:uid="{41FD82F1-FA88-47A8-B89A-C49B5EFF1DC5}"/>
     <hyperlink ref="B29" r:id="rId56" xr:uid="{AE50C18A-BCF5-4ED8-881B-37D12746B425}"/>
-    <hyperlink ref="B21" r:id="rId57" xr:uid="{A9FB40FB-BCAE-4E3A-9EF1-A59DFEE9D933}"/>
+    <hyperlink ref="B22" r:id="rId57" xr:uid="{A9FB40FB-BCAE-4E3A-9EF1-A59DFEE9D933}"/>
     <hyperlink ref="B40" r:id="rId58" xr:uid="{7A10496F-0F74-4C71-BA4B-2A10A8E34983}"/>
     <hyperlink ref="B37" r:id="rId59" xr:uid="{693B9C0C-5FA9-48F0-B874-61231FBB3976}"/>
   </hyperlinks>

--- a/Financial Analysis/Models (Tech).xlsx
+++ b/Financial Analysis/Models (Tech).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC13FAD-C056-483E-B7B1-AFED7EC55407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66ABFA90-D238-49A0-AFD3-E2ECF06AAE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4E122305-8C8A-4700-8BB3-18DD9512A165}"/>
   </bookViews>
@@ -853,7 +853,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -941,15 +941,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -7717,85 +7708,88 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>35.03</v>
+            <v>17.52</v>
           </cell>
           <cell r="E3">
-            <v>45905</v>
+            <v>45927</v>
           </cell>
           <cell r="G3">
-            <v>45994</v>
+            <v>45960</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>637.54600000000005</v>
+            <v>492.31200000000001</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>47.5</v>
+            <v>-186.5</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>590.04600000000005</v>
+            <v>678.81200000000001</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
-          <cell r="M3">
-            <v>76.099999999999994</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="M14">
-            <v>-42.300000000000011</v>
-          </cell>
-          <cell r="N14">
-            <v>-20.811699999999991</v>
-          </cell>
-          <cell r="O14">
-            <v>-11.897724999999994</v>
-          </cell>
-          <cell r="P14">
-            <v>-7.5577599999999938</v>
-          </cell>
-          <cell r="Q14">
-            <v>1.4139300000000246</v>
-          </cell>
-          <cell r="X14">
-            <v>92.000345403668746</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="M18">
-            <v>0.16183206106870229</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="M19">
-            <v>0.31931668856767409</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="AA20">
+          <cell r="R3">
+            <v>756.4</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="Q17">
+            <v>-6.4999999999999982</v>
+          </cell>
+          <cell r="R17">
+            <v>-12.812000000000056</v>
+          </cell>
+          <cell r="S17">
+            <v>62.024759999999965</v>
+          </cell>
+          <cell r="T17">
+            <v>68.689998399999979</v>
+          </cell>
+          <cell r="U17">
+            <v>70.159895087999971</v>
+          </cell>
+          <cell r="AB17">
+            <v>89.581963606742363</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="P21">
+            <v>4.8674110258199565E-2</v>
+          </cell>
+          <cell r="Q21">
+            <v>0.24521710197970381</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="R22">
+            <v>0.40179666842940243</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="AE23">
             <v>0.11</v>
           </cell>
         </row>
-        <row r="23">
-          <cell r="M23">
-            <v>-0.53350854139290427</v>
-          </cell>
-        </row>
         <row r="26">
-          <cell r="AA26">
-            <v>-0.30871809322658095</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="AA27" t="str">
-            <v>Overvalued</v>
+          <cell r="R26">
+            <v>-1.1253305129561155E-2</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="AE29">
+            <v>-0.1323068950304066</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AE30" t="str">
+            <v>Slightly overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -7818,88 +7812,85 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>8.02</v>
+            <v>35.03</v>
           </cell>
           <cell r="E3">
-            <v>45910</v>
+            <v>45905</v>
           </cell>
           <cell r="G3">
-            <v>45974</v>
+            <v>45994</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>286.31400000000002</v>
+            <v>637.54600000000005</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-71.5</v>
+            <v>47.5</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>357.81400000000002</v>
+            <v>590.04600000000005</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
-          <cell r="Y3">
-            <v>127.2</v>
+          <cell r="M3">
+            <v>76.099999999999994</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="M14">
+            <v>-42.300000000000011</v>
+          </cell>
+          <cell r="N14">
+            <v>-20.811699999999991</v>
+          </cell>
+          <cell r="O14">
+            <v>-11.897724999999994</v>
+          </cell>
+          <cell r="P14">
+            <v>-7.5577599999999938</v>
+          </cell>
+          <cell r="Q14">
+            <v>1.4139300000000246</v>
+          </cell>
+          <cell r="X14">
+            <v>92.000345403668746</v>
           </cell>
         </row>
         <row r="18">
-          <cell r="Y18">
-            <v>30.799999999999997</v>
-          </cell>
-          <cell r="Z18">
-            <v>21.632190000000008</v>
-          </cell>
-          <cell r="AA18">
-            <v>44.623238034999986</v>
-          </cell>
-          <cell r="AB18">
-            <v>47.244279367299995</v>
-          </cell>
-          <cell r="AC18">
-            <v>51.957359563301495</v>
-          </cell>
-          <cell r="AJ18">
-            <v>71.467957034042854</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="X22">
-            <v>0.42091503267973862</v>
-          </cell>
-          <cell r="Y22">
-            <v>0.170193192272309</v>
+          <cell r="M18">
+            <v>0.16183206106870229</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="M19">
+            <v>0.31931668856767409</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="AA20">
+            <v>0.11</v>
           </cell>
         </row>
         <row r="23">
-          <cell r="Y23">
-            <v>0.94103773584905659</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="AM25">
-            <v>0.11</v>
+          <cell r="M23">
+            <v>-0.53350854139290427</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="AA26">
+            <v>-0.30871809322658095</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="Y27">
-            <v>0.285377358490566</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="AM31">
-            <v>0.53776133996255537</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="AM32" t="str">
-            <v>Heavily undervalued</v>
+          <cell r="AA27" t="str">
+            <v>Overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -7922,75 +7913,88 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>12.28</v>
+            <v>8.02</v>
           </cell>
           <cell r="E3">
-            <v>45898</v>
+            <v>45910</v>
           </cell>
           <cell r="G3">
-            <v>45959</v>
+            <v>45974</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>184.2</v>
+            <v>286.31400000000002</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-21.599999999999994</v>
+            <v>-71.5</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>205.79999999999998</v>
+            <v>357.81400000000002</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="7">
-          <cell r="AU7">
-            <v>206.39999999999998</v>
+        <row r="3">
+          <cell r="Y3">
+            <v>127.2</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="Y18">
+            <v>30.799999999999997</v>
+          </cell>
+          <cell r="Z18">
+            <v>21.632190000000008</v>
+          </cell>
+          <cell r="AA18">
+            <v>44.623238034999986</v>
+          </cell>
+          <cell r="AB18">
+            <v>47.244279367299995</v>
+          </cell>
+          <cell r="AC18">
+            <v>51.957359563301495</v>
+          </cell>
+          <cell r="AJ18">
+            <v>71.467957034042854</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="X22">
+            <v>0.42091503267973862</v>
+          </cell>
+          <cell r="Y22">
+            <v>0.170193192272309</v>
           </cell>
         </row>
         <row r="23">
-          <cell r="AU23">
-            <v>3.1999999999999886</v>
-          </cell>
-          <cell r="AV23">
-            <v>-3.5082000000000235</v>
-          </cell>
-          <cell r="AW23">
-            <v>7.3717279999999858</v>
-          </cell>
-          <cell r="AX23">
-            <v>10.802357279999994</v>
-          </cell>
-          <cell r="AY23">
-            <v>13.440192995199988</v>
+          <cell r="Y23">
+            <v>0.94103773584905659</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="AM25">
+            <v>0.11</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="Y27">
+            <v>0.285377358490566</v>
           </cell>
         </row>
         <row r="31">
-          <cell r="AT31">
-            <v>-0.23368678629690032</v>
-          </cell>
-          <cell r="AU31">
-            <v>9.8456625864821401E-2</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="BI33">
-            <v>0.12</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="BI39">
-            <v>-0.48992193040360954</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="BI40" t="str">
-            <v>Overvalued</v>
+          <cell r="AM31">
+            <v>0.53776133996255537</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="AM32" t="str">
+            <v>Heavily undervalued</v>
           </cell>
         </row>
       </sheetData>
@@ -8013,45 +8017,75 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>0.73199999999999998</v>
+            <v>12.28</v>
           </cell>
           <cell r="E3">
-            <v>44279</v>
+            <v>45898</v>
           </cell>
           <cell r="G3">
-            <v>44406</v>
+            <v>45959</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>187.61160000000001</v>
+            <v>184.2</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>0</v>
+            <v>-21.599999999999994</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>187.61160000000001</v>
+            <v>205.79999999999998</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="24">
-          <cell r="AE24">
-            <v>0.11</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="AE30">
-            <v>-0.25169013126318518</v>
+        <row r="7">
+          <cell r="AU7">
+            <v>206.39999999999998</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="AU23">
+            <v>3.1999999999999886</v>
+          </cell>
+          <cell r="AV23">
+            <v>-3.5082000000000235</v>
+          </cell>
+          <cell r="AW23">
+            <v>7.3717279999999858</v>
+          </cell>
+          <cell r="AX23">
+            <v>10.802357279999994</v>
+          </cell>
+          <cell r="AY23">
+            <v>13.440192995199988</v>
           </cell>
         </row>
         <row r="31">
-          <cell r="AE31" t="str">
-            <v>Slightly overvalued</v>
+          <cell r="AT31">
+            <v>-0.23368678629690032</v>
+          </cell>
+          <cell r="AU31">
+            <v>9.8456625864821401E-2</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="BI33">
+            <v>0.12</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="BI39">
+            <v>-0.48992193040360954</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="BI40" t="str">
+            <v>Overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -8074,75 +8108,45 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>1.68</v>
+            <v>0.73199999999999998</v>
           </cell>
           <cell r="E3">
-            <v>45905</v>
+            <v>44279</v>
           </cell>
           <cell r="G3">
-            <v>45964</v>
+            <v>44406</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>179.59200000000001</v>
+            <v>187.61160000000001</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>51.599999999999994</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>127.99200000000002</v>
+            <v>187.61160000000001</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="3">
-          <cell r="AE3">
-            <v>395.77499999999998</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="AD16">
-            <v>-29.899999999999945</v>
-          </cell>
-          <cell r="AE16">
-            <v>-126.39400000000002</v>
-          </cell>
-          <cell r="AF16">
-            <v>-27.913519750000027</v>
-          </cell>
-          <cell r="AG16">
-            <v>-1.4263918424999869</v>
-          </cell>
-          <cell r="AH16">
-            <v>14.796638968349985</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="AC20">
-            <v>-6.5727699530516381E-2</v>
-          </cell>
-          <cell r="AD20">
-            <v>-0.13791178112786151</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="AS22">
-            <v>0.12</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="AS28">
-            <v>0.16576302502726192</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="AS29" t="str">
-            <v>Undervalued</v>
+        <row r="24">
+          <cell r="AE24">
+            <v>0.11</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AE30">
+            <v>-0.25169013126318518</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="AE31" t="str">
+            <v>Slightly overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -8165,78 +8169,75 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>1.27</v>
+            <v>1.68</v>
           </cell>
           <cell r="E3">
-            <v>45751</v>
+            <v>45905</v>
           </cell>
           <cell r="G3">
-            <v>45845</v>
+            <v>45964</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>94.234000000000009</v>
+            <v>179.59200000000001</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-15.5</v>
+            <v>51.599999999999994</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>109.73400000000001</v>
+            <v>127.99200000000002</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
-          <cell r="T3">
-            <v>46.9</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="T17">
-            <v>-76.160000000000011</v>
-          </cell>
-          <cell r="U17">
-            <v>2.1120000000000005</v>
-          </cell>
-          <cell r="V17">
-            <v>8.7361250000000013</v>
-          </cell>
-          <cell r="W17">
-            <v>15.032579999999999</v>
-          </cell>
-          <cell r="X17">
-            <v>20.612932799999989</v>
-          </cell>
-          <cell r="AE17">
-            <v>50.431172568710124</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="S21">
-            <v>2.4338235294117649</v>
-          </cell>
-          <cell r="T21">
-            <v>4.2826552462524869E-3</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="AH24">
+          <cell r="AE3">
+            <v>395.77499999999998</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="AD16">
+            <v>-29.899999999999945</v>
+          </cell>
+          <cell r="AE16">
+            <v>-126.39400000000002</v>
+          </cell>
+          <cell r="AF16">
+            <v>-27.913519750000027</v>
+          </cell>
+          <cell r="AG16">
+            <v>-1.4263918424999869</v>
+          </cell>
+          <cell r="AH16">
+            <v>14.796638968349985</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="AC20">
+            <v>-6.5727699530516381E-2</v>
+          </cell>
+          <cell r="AD20">
+            <v>-0.13791178112786151</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="AS22">
             <v>0.12</v>
           </cell>
         </row>
-        <row r="30">
-          <cell r="AH30">
-            <v>0.51192284558708812</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="AH31" t="str">
-            <v>Heavily undervalued</v>
+        <row r="28">
+          <cell r="AS28">
+            <v>0.16576302502726192</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="AS29" t="str">
+            <v>Undervalued</v>
           </cell>
         </row>
       </sheetData>
@@ -8356,78 +8357,78 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>5.79</v>
+            <v>1.27</v>
           </cell>
           <cell r="E3">
-            <v>45817</v>
+            <v>45751</v>
           </cell>
           <cell r="G3">
-            <v>45785</v>
+            <v>45845</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>54.426000000000002</v>
+            <v>94.234000000000009</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>20</v>
+            <v>-15.5</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>34.426000000000002</v>
+            <v>109.73400000000001</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
-          <cell r="AA3">
-            <v>12.3</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="AC12">
-            <v>-0.29201399999999977</v>
-          </cell>
-          <cell r="AD12">
-            <v>-2.4455999999972722E-4</v>
-          </cell>
-          <cell r="AE12">
-            <v>0.24468274320000027</v>
-          </cell>
-          <cell r="AF12">
-            <v>0.43762034426400065</v>
-          </cell>
-          <cell r="AG12">
-            <v>0.63253625788728018</v>
-          </cell>
-          <cell r="AL12">
-            <v>1.638868218616484</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="AA16">
-            <v>-6.1068702290076216E-2</v>
-          </cell>
-          <cell r="AB16">
-            <v>3.9837398373983701E-2</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="AO18">
-            <v>0.13</v>
+          <cell r="T3">
+            <v>46.9</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="T17">
+            <v>-76.160000000000011</v>
+          </cell>
+          <cell r="U17">
+            <v>2.1120000000000005</v>
+          </cell>
+          <cell r="V17">
+            <v>8.7361250000000013</v>
+          </cell>
+          <cell r="W17">
+            <v>15.032579999999999</v>
+          </cell>
+          <cell r="X17">
+            <v>20.612932799999989</v>
+          </cell>
+          <cell r="AE17">
+            <v>50.431172568710124</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="S21">
+            <v>2.4338235294117649</v>
+          </cell>
+          <cell r="T21">
+            <v>4.2826552462524869E-3</v>
           </cell>
         </row>
         <row r="24">
-          <cell r="AO24">
-            <v>-0.54344337476902149</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="AO25" t="str">
-            <v>Heavily overvalued</v>
+          <cell r="AH24">
+            <v>0.12</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AH30">
+            <v>0.51192284558708812</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="AH31" t="str">
+            <v>Heavily undervalued</v>
           </cell>
         </row>
       </sheetData>
@@ -8552,78 +8553,78 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>4.4400000000000004</v>
+            <v>5.79</v>
           </cell>
           <cell r="E3">
-            <v>45780</v>
-          </cell>
-          <cell r="G3" t="str">
-            <v>?</v>
+            <v>45817</v>
+          </cell>
+          <cell r="G3">
+            <v>45785</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>43.067999999999998</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="D10">
-            <v>140.4951856946355</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="D11">
-            <v>-97.427185694635497</v>
+            <v>54.426000000000002</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>34.426000000000002</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="5">
-          <cell r="O5">
-            <v>334.37624999999997</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="O23">
-            <v>-65.195625000000021</v>
-          </cell>
-          <cell r="P23">
-            <v>-75.811683750000014</v>
-          </cell>
-          <cell r="Q23">
-            <v>-85.133768362500035</v>
-          </cell>
-          <cell r="R23">
-            <v>-92.999013768375065</v>
-          </cell>
-          <cell r="S23">
-            <v>-99.507942011156317</v>
-          </cell>
-          <cell r="Z23">
-            <v>-121.34020466225257</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="N27">
-            <v>-5.0000000000000044E-2</v>
-          </cell>
-          <cell r="O27">
-            <v>-0.35</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="AA30">
-            <v>0.15</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="AA37">
-            <v>0.42025776126590375</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="AA38" t="str">
-            <v>Undervalued</v>
+        <row r="3">
+          <cell r="AA3">
+            <v>12.3</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="AC12">
+            <v>-0.29201399999999977</v>
+          </cell>
+          <cell r="AD12">
+            <v>-2.4455999999972722E-4</v>
+          </cell>
+          <cell r="AE12">
+            <v>0.24468274320000027</v>
+          </cell>
+          <cell r="AF12">
+            <v>0.43762034426400065</v>
+          </cell>
+          <cell r="AG12">
+            <v>0.63253625788728018</v>
+          </cell>
+          <cell r="AL12">
+            <v>1.638868218616484</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="AA16">
+            <v>-6.1068702290076216E-2</v>
+          </cell>
+          <cell r="AB16">
+            <v>3.9837398373983701E-2</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="AO18">
+            <v>0.13</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="AO24">
+            <v>-0.54344337476902149</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="AO25" t="str">
+            <v>Heavily overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -8646,78 +8647,78 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>4.07</v>
+            <v>4.4400000000000004</v>
           </cell>
           <cell r="E3">
-            <v>45751</v>
-          </cell>
-          <cell r="G3">
-            <v>45777</v>
+            <v>45780</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>?</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>71.632000000000005</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="D8">
-            <v>239</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="D9">
-            <v>-167.36799999999999</v>
+            <v>43.067999999999998</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="D10">
+            <v>140.4951856946355</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="D11">
+            <v>-97.427185694635497</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="3">
-          <cell r="AI3">
-            <v>95.5</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="AI14">
-            <v>-93.9</v>
-          </cell>
-          <cell r="AJ14">
-            <v>-59.968500000000006</v>
-          </cell>
-          <cell r="AK14">
-            <v>-42.065130000000011</v>
-          </cell>
-          <cell r="AL14">
-            <v>-29.314150250000012</v>
-          </cell>
-          <cell r="AM14">
-            <v>-18.632540500000005</v>
-          </cell>
-          <cell r="AS14">
-            <v>0.69729380650535155</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="AH18">
-            <v>-0.43604004449388212</v>
-          </cell>
-          <cell r="AI18">
-            <v>-0.37212360289283364</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="AW21">
-            <v>0.12</v>
+        <row r="5">
+          <cell r="O5">
+            <v>334.37624999999997</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="O23">
+            <v>-65.195625000000021</v>
+          </cell>
+          <cell r="P23">
+            <v>-75.811683750000014</v>
+          </cell>
+          <cell r="Q23">
+            <v>-85.133768362500035</v>
+          </cell>
+          <cell r="R23">
+            <v>-92.999013768375065</v>
+          </cell>
+          <cell r="S23">
+            <v>-99.507942011156317</v>
+          </cell>
+          <cell r="Z23">
+            <v>-121.34020466225257</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="AW27">
-            <v>-0.52302112324583339</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="AW28" t="str">
-            <v>Heavily overvalued</v>
+          <cell r="N27">
+            <v>-5.0000000000000044E-2</v>
+          </cell>
+          <cell r="O27">
+            <v>-0.35</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AA30">
+            <v>0.15</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="AA37">
+            <v>0.42025776126590375</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="AA38" t="str">
+            <v>Undervalued</v>
           </cell>
         </row>
       </sheetData>
@@ -8740,88 +8741,78 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>17.52</v>
+            <v>4.07</v>
           </cell>
           <cell r="E3">
-            <v>45927</v>
+            <v>45751</v>
           </cell>
           <cell r="G3">
-            <v>45960</v>
+            <v>45777</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>492.31200000000001</v>
+            <v>71.632000000000005</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-186.5</v>
+            <v>239</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>678.81200000000001</v>
+            <v>-167.36799999999999</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
-          <cell r="R3">
-            <v>756.4</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="Q17">
-            <v>-6.4999999999999982</v>
-          </cell>
-          <cell r="R17">
-            <v>-12.812000000000056</v>
-          </cell>
-          <cell r="S17">
-            <v>62.024759999999965</v>
-          </cell>
-          <cell r="T17">
-            <v>68.689998399999979</v>
-          </cell>
-          <cell r="U17">
-            <v>70.159895087999971</v>
-          </cell>
-          <cell r="AB17">
-            <v>89.581963606742363</v>
+          <cell r="AI3">
+            <v>95.5</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="AI14">
+            <v>-93.9</v>
+          </cell>
+          <cell r="AJ14">
+            <v>-59.968500000000006</v>
+          </cell>
+          <cell r="AK14">
+            <v>-42.065130000000011</v>
+          </cell>
+          <cell r="AL14">
+            <v>-29.314150250000012</v>
+          </cell>
+          <cell r="AM14">
+            <v>-18.632540500000005</v>
+          </cell>
+          <cell r="AS14">
+            <v>0.69729380650535155</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="AH18">
+            <v>-0.43604004449388212</v>
+          </cell>
+          <cell r="AI18">
+            <v>-0.37212360289283364</v>
           </cell>
         </row>
         <row r="21">
-          <cell r="P21">
-            <v>4.8674110258199565E-2</v>
-          </cell>
-          <cell r="Q21">
-            <v>0.24521710197970381</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="R22">
-            <v>0.40179666842940243</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="AE23">
-            <v>0.11</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="R26">
-            <v>-1.1253305129561155E-2</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="AE29">
-            <v>-0.1323068950304066</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="AE30" t="str">
-            <v>Slightly overvalued</v>
+          <cell r="AW21">
+            <v>0.12</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="AW27">
+            <v>-0.52302112324583339</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="AW28" t="str">
+            <v>Heavily overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -9524,56 +9515,56 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="4">
-        <f>TRIMMEAN(M4:M1048576,80%)</f>
+        <f t="shared" ref="M3:R3" si="0">TRIMMEAN(M4:M1048576,80%)</f>
         <v>28.570362146051316</v>
       </c>
       <c r="N3" s="4">
-        <f>TRIMMEAN(N4:N1048576,80%)</f>
+        <f t="shared" si="0"/>
         <v>27.722623235186219</v>
       </c>
       <c r="O3" s="4">
-        <f>TRIMMEAN(O4:O1048576,80%)</f>
+        <f t="shared" si="0"/>
         <v>26.383508603815013</v>
       </c>
       <c r="P3" s="4">
-        <f>TRIMMEAN(P4:P1048576,80%)</f>
+        <f t="shared" si="0"/>
         <v>20.704966255264747</v>
       </c>
       <c r="Q3" s="4">
-        <f>TRIMMEAN(Q4:Q1048576,80%)</f>
+        <f t="shared" si="0"/>
         <v>20.175930948236129</v>
       </c>
       <c r="R3" s="4">
-        <f>TRIMMEAN(R4:R1048576,80%)</f>
+        <f t="shared" si="0"/>
         <v>15.837986078940949</v>
       </c>
       <c r="S3" s="21"/>
       <c r="T3" s="28">
-        <f>TRIMMEAN(T4:T1048576,80%)</f>
+        <f t="shared" ref="T3:Z3" si="1">TRIMMEAN(T4:T1048576,80%)</f>
         <v>4.1199516612244071</v>
       </c>
       <c r="U3" s="5">
-        <f>TRIMMEAN(U4:U1048576,80%)</f>
+        <f t="shared" si="1"/>
         <v>0.10832328453266284</v>
       </c>
       <c r="V3" s="5">
-        <f>TRIMMEAN(V4:V1048576,80%)</f>
+        <f t="shared" si="1"/>
         <v>0.1155300562218613</v>
       </c>
       <c r="W3" s="5">
-        <f>TRIMMEAN(W4:W1048576,80%)</f>
+        <f t="shared" si="1"/>
         <v>0.54853886240198946</v>
       </c>
       <c r="X3" s="5">
-        <f>TRIMMEAN(X4:X1048576,80%)</f>
+        <f t="shared" si="1"/>
         <v>0.12745147108317756</v>
       </c>
       <c r="Y3" s="5">
-        <f>TRIMMEAN(Y4:Y1048576,80%)</f>
+        <f t="shared" si="1"/>
         <v>8.142857142857142E-2</v>
       </c>
       <c r="Z3" s="5">
-        <f>TRIMMEAN(Z4:Z1048576,80%)</f>
+        <f t="shared" si="1"/>
         <v>-0.28177309827873842</v>
       </c>
       <c r="AA3" s="14" t="str">
@@ -9604,7 +9595,7 @@
         <v>48325</v>
       </c>
       <c r="G4" s="8">
-        <f t="shared" ref="G4:G9" si="0">E4-F4</f>
+        <f t="shared" ref="G4:G9" si="2">E4-F4</f>
         <v>4189166.0599999996</v>
       </c>
       <c r="H4" s="8">
@@ -9628,23 +9619,23 @@
         <v>174495.29195930838</v>
       </c>
       <c r="M4" s="9">
-        <f t="shared" ref="M4:Q11" si="1">$G4/H4</f>
+        <f t="shared" ref="M4:Q11" si="3">$G4/H4</f>
         <v>57.480324643249169</v>
       </c>
       <c r="N4" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>39.870454073786135</v>
       </c>
       <c r="O4" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>30.070238512075235</v>
       </c>
       <c r="P4" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>26.183861100671159</v>
       </c>
       <c r="Q4" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>24.007330014249877</v>
       </c>
       <c r="R4" s="9">
@@ -9656,7 +9647,7 @@
         <v>201159.59000000003</v>
       </c>
       <c r="T4" s="33">
-        <f t="shared" ref="T4:T11" si="2">G4/S4</f>
+        <f t="shared" ref="T4:T11" si="4">G4/S4</f>
         <v>20.82508748402201</v>
       </c>
       <c r="U4" s="11">
@@ -9722,7 +9713,7 @@
         <v>66819</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3803766.5999999996</v>
       </c>
       <c r="H5" s="8">
@@ -9746,23 +9737,23 @@
         <v>134376.19905452224</v>
       </c>
       <c r="M5" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>42.986242202332512</v>
       </c>
       <c r="N5" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>37.353352580721186</v>
       </c>
       <c r="O5" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>32.523031815064265</v>
       </c>
       <c r="P5" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>30.091490533802368</v>
       </c>
       <c r="Q5" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>28.306847691507087</v>
       </c>
       <c r="R5" s="9">
@@ -9774,7 +9765,7 @@
         <v>239781</v>
       </c>
       <c r="T5" s="32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>15.863502946438624</v>
       </c>
       <c r="U5" s="11">
@@ -9840,7 +9831,7 @@
         <v>31288</v>
       </c>
       <c r="G6" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3411579.9580000001</v>
       </c>
       <c r="H6" s="8">
@@ -9864,23 +9855,23 @@
         <v>123138.95805643471</v>
       </c>
       <c r="M6" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>36.395621298113852</v>
       </c>
       <c r="N6" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>31.161835298436664</v>
       </c>
       <c r="O6" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>30.085590948671452</v>
       </c>
       <c r="P6" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>28.713763164635481</v>
       </c>
       <c r="Q6" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>27.705122829092556</v>
       </c>
       <c r="R6" s="9">
@@ -9892,7 +9883,7 @@
         <v>391035</v>
       </c>
       <c r="T6" s="32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.7244874704310362</v>
       </c>
       <c r="U6" s="11">
@@ -9958,7 +9949,7 @@
         <v>124115</v>
       </c>
       <c r="G7" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2904566.6999999997</v>
       </c>
       <c r="H7" s="8">
@@ -9982,23 +9973,23 @@
         <v>144729.99966097245</v>
       </c>
       <c r="M7" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>29.011433508460016</v>
       </c>
       <c r="N7" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>23.495794245715917</v>
       </c>
       <c r="O7" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>22.826399737734281</v>
       </c>
       <c r="P7" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>21.233831770804095</v>
       </c>
       <c r="Q7" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>20.068864138768035</v>
       </c>
       <c r="R7" s="9">
@@ -10010,7 +10001,7 @@
         <v>350018</v>
       </c>
       <c r="T7" s="32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.2983352284739631</v>
       </c>
       <c r="U7" s="11">
@@ -10076,7 +10067,7 @@
         <v>48579</v>
       </c>
       <c r="G8" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2395803.6</v>
       </c>
       <c r="H8" s="8">
@@ -10100,23 +10091,23 @@
         <v>119994.74901963281</v>
       </c>
       <c r="M8" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>40.436868755063465</v>
       </c>
       <c r="N8" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>32.676185568759536</v>
       </c>
       <c r="O8" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>26.491614552710722</v>
       </c>
       <c r="P8" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>22.67247933061125</v>
       </c>
       <c r="Q8" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>19.965903671401598</v>
       </c>
       <c r="R8" s="9">
@@ -10128,7 +10119,7 @@
         <v>637959</v>
       </c>
       <c r="T8" s="32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.7554193921552952</v>
       </c>
       <c r="U8" s="11">
@@ -10194,7 +10185,7 @@
         <v>40227</v>
       </c>
       <c r="G9" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1931316.6400000001</v>
       </c>
       <c r="H9" s="8">
@@ -10218,23 +10209,23 @@
         <v>105322.50927113106</v>
       </c>
       <c r="M9" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>31.759852655813191</v>
       </c>
       <c r="N9" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>25.305947126918404</v>
       </c>
       <c r="O9" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>21.969186276911511</v>
       </c>
       <c r="P9" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>19.807172349803388</v>
       </c>
       <c r="Q9" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>18.337168885980716</v>
       </c>
       <c r="R9" s="9">
@@ -10246,7 +10237,7 @@
         <v>164500</v>
       </c>
       <c r="T9" s="32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>11.740526686930092</v>
       </c>
       <c r="U9" s="11">
@@ -10336,23 +10327,23 @@
         <v>8985.0711792893107</v>
       </c>
       <c r="M10" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>137.91394725708645</v>
       </c>
       <c r="N10" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>314.60572313906039</v>
       </c>
       <c r="O10" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>144.73878741279162</v>
       </c>
       <c r="P10" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>129.61014336153644</v>
       </c>
       <c r="Q10" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>108.84140820767014</v>
       </c>
       <c r="R10" s="9">
@@ -10364,7 +10355,7 @@
         <v>97690</v>
       </c>
       <c r="T10" s="32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>10.010725765175556</v>
       </c>
       <c r="U10" s="11">
@@ -10454,23 +10445,23 @@
         <v>20997.064242786695</v>
       </c>
       <c r="M11" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>89.796105187732877</v>
       </c>
       <c r="N11" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>75.536111307562479</v>
       </c>
       <c r="O11" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>65.52485557953031</v>
       </c>
       <c r="P11" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>52.833791730797969</v>
       </c>
       <c r="Q11" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>44.763202233040296</v>
       </c>
       <c r="R11" s="9">
@@ -10482,7 +10473,7 @@
         <v>57399</v>
       </c>
       <c r="T11" s="33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>16.374777138974547</v>
       </c>
       <c r="U11" s="11">
@@ -10638,23 +10629,23 @@
         <v>27970.458104098721</v>
       </c>
       <c r="M13" s="9">
-        <f t="shared" ref="M13:Q19" si="3">$G13/H13</f>
+        <f t="shared" ref="M13:Q19" si="5">$G13/H13</f>
         <v>32.395094463860609</v>
       </c>
       <c r="N13" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>31.416677877405874</v>
       </c>
       <c r="O13" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>26.134711571837641</v>
       </c>
       <c r="P13" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>24.042397176928105</v>
       </c>
       <c r="Q13" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>22.866137823687559</v>
       </c>
       <c r="R13" s="9">
@@ -10666,7 +10657,7 @@
         <v>35926</v>
       </c>
       <c r="T13" s="32">
-        <f t="shared" ref="T13:T19" si="4">G13/S13</f>
+        <f t="shared" ref="T13:T19" si="6">G13/S13</f>
         <v>17.802603963703167</v>
       </c>
       <c r="U13" s="11">
@@ -10756,23 +10747,23 @@
         <v>8711.3999999999924</v>
       </c>
       <c r="M14" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>192.50865431337706</v>
       </c>
       <c r="N14" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>103.74648062379084</v>
       </c>
       <c r="O14" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>118.18894786054594</v>
       </c>
       <c r="P14" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>98.165886834319508</v>
       </c>
       <c r="Q14" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60.940964253736524</v>
       </c>
       <c r="R14" s="9">
@@ -10784,7 +10775,7 @@
         <v>24992</v>
       </c>
       <c r="T14" s="32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>21.242042093469909</v>
       </c>
       <c r="U14" s="11">
@@ -10874,23 +10865,23 @@
         <v>20751.739974825352</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>41.122575734037596</v>
       </c>
       <c r="N15" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>37.090555827583216</v>
       </c>
       <c r="O15" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>30.336873140787539</v>
       </c>
       <c r="P15" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>27.32608515401208</v>
       </c>
       <c r="Q15" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>25.511693990106274</v>
       </c>
       <c r="R15" s="9">
@@ -10902,7 +10893,7 @@
         <v>28167</v>
       </c>
       <c r="T15" s="32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>18.795471296197679</v>
       </c>
       <c r="U15" s="11">
@@ -10992,23 +10983,23 @@
         <v>3539.2762139451202</v>
       </c>
       <c r="M16" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>918.24785175608645</v>
       </c>
       <c r="N16" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>382.4728961886583</v>
       </c>
       <c r="O16" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>263.73239043818319</v>
       </c>
       <c r="P16" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>172.26177279265755</v>
       </c>
       <c r="Q16" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>120.4084683531874</v>
       </c>
       <c r="R16" s="9">
@@ -11020,7 +11011,7 @@
         <v>4206.7849999999999</v>
       </c>
       <c r="T16" s="33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>101.30273546187883</v>
       </c>
       <c r="U16" s="11">
@@ -11110,23 +11101,23 @@
         <v>13096.804697724794</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>147.47228519195613</v>
       </c>
       <c r="N17" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>61.632292688398003</v>
       </c>
       <c r="O17" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>30.829723300750384</v>
       </c>
       <c r="P17" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>22.776625496370556</v>
       </c>
       <c r="Q17" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>18.477943711113074</v>
       </c>
       <c r="R17" s="9">
@@ -11138,7 +11129,7 @@
         <v>25785</v>
       </c>
       <c r="T17" s="32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9.3853798720186159</v>
       </c>
       <c r="U17" s="11">
@@ -11228,23 +11219,23 @@
         <v>12256.439405230325</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>23.371372790996148</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>22.464793732948667</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20.126374180640607</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>19.688575232584363</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>19.31463348963959</v>
       </c>
       <c r="R18" s="9">
@@ -11256,7 +11247,7 @@
         <v>74201</v>
       </c>
       <c r="T18" s="32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.1903698737213784</v>
       </c>
       <c r="U18" s="11">
@@ -11346,23 +11337,23 @@
         <v>8985.8563423912037</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>36.914448926900114</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>36.884806387072238</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>28.987495588227702</v>
       </c>
       <c r="P19" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>26.365140336509342</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>25.457656041174317</v>
       </c>
       <c r="R19" s="9">
@@ -11374,7 +11365,7 @@
         <v>40168.700000000004</v>
       </c>
       <c r="T19" s="33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5.694952537672366</v>
       </c>
       <c r="U19" s="11">
@@ -11531,23 +11522,23 @@
         <v>4983.7860456229982</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" ref="M21:Q24" si="5">$G21/H21</f>
+        <f t="shared" ref="M21:Q24" si="7">$G21/H21</f>
         <v>-8.7472478140328427</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>-34.86601097588143</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>113.57083556265273</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>42.294468168919018</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>32.919426816905272</v>
       </c>
       <c r="R21" s="9">
@@ -11559,7 +11550,7 @@
         <v>53101</v>
       </c>
       <c r="T21" s="32">
-        <f t="shared" ref="T21:T60" si="6">G21/S21</f>
+        <f t="shared" ref="T21:T60" si="8">G21/S21</f>
         <v>3.0896476525865806</v>
       </c>
       <c r="U21" s="11">
@@ -11649,23 +11640,23 @@
         <v>9527.4991916066156</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>27.713221942446044</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20.992141970142356</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>18.541155371841448</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>17.172619969512091</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>16.172713416312206</v>
       </c>
       <c r="R22" s="9">
@@ -11677,7 +11668,7 @@
         <v>23695.26</v>
       </c>
       <c r="T22" s="33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>6.5027990408208227</v>
       </c>
       <c r="U22" s="11">
@@ -11767,23 +11758,23 @@
         <v>2268.1938767268002</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>118.82290190126217</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>140.64652074610922</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>92.69233421431629</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>72.745137793728176</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>59.615918970194542</v>
       </c>
       <c r="R23" s="9">
@@ -11795,7 +11786,7 @@
         <v>15673</v>
       </c>
       <c r="T23" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>8.6276055869097394</v>
       </c>
       <c r="U23" s="11">
@@ -11885,23 +11876,23 @@
         <v>5168.0762698254402</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>33.928871287128715</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>24.61588244908577</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>22.540294755784622</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>21.425223068139015</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20.555287974414536</v>
       </c>
       <c r="R24" s="9">
@@ -11913,7 +11904,7 @@
         <v>20456</v>
       </c>
       <c r="T24" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>5.1931607352366056</v>
       </c>
       <c r="U24" s="11">
@@ -12006,11 +11997,11 @@
       <c r="N25" s="9"/>
       <c r="O25" s="9"/>
       <c r="P25" s="9">
-        <f t="shared" ref="P25:P38" si="7">$G25/K25</f>
+        <f t="shared" ref="P25:P38" si="9">$G25/K25</f>
         <v>-256.28190435176953</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" ref="Q25:Q38" si="8">$G25/L25</f>
+        <f t="shared" ref="Q25:Q38" si="10">$G25/L25</f>
         <v>1897.555692466442</v>
       </c>
       <c r="R25" s="9">
@@ -12022,7 +12013,7 @@
         <v>3602</v>
       </c>
       <c r="T25" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>21.964755691282619</v>
       </c>
       <c r="U25" s="11">
@@ -12113,19 +12104,19 @@
       </c>
       <c r="M26" s="9"/>
       <c r="N26" s="9">
-        <f t="shared" ref="N26:N35" si="9">$G26/I26</f>
+        <f t="shared" ref="N26:N35" si="11">$G26/I26</f>
         <v>101.7051588098139</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" ref="O26:O35" si="10">$G26/J26</f>
+        <f t="shared" ref="O26:O35" si="12">$G26/J26</f>
         <v>64.839806193388696</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>51.886448980803863</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>46.415356566781611</v>
       </c>
       <c r="R26" s="9">
@@ -12137,7 +12128,7 @@
         <v>4539.4639999999999</v>
       </c>
       <c r="T26" s="33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>16.125254435325406</v>
       </c>
       <c r="U26" s="11">
@@ -12231,19 +12222,19 @@
         <v>29.06560313775714</v>
       </c>
       <c r="N27" s="9">
+        <f t="shared" si="11"/>
+        <v>30.771321034948457</v>
+      </c>
+      <c r="O27" s="9">
+        <f t="shared" si="12"/>
+        <v>37.612700969388094</v>
+      </c>
+      <c r="P27" s="9">
         <f t="shared" si="9"/>
-        <v>30.771321034948457</v>
-      </c>
-      <c r="O27" s="9">
+        <v>31.545927043811364</v>
+      </c>
+      <c r="Q27" s="9">
         <f t="shared" si="10"/>
-        <v>37.612700969388094</v>
-      </c>
-      <c r="P27" s="9">
-        <f t="shared" si="7"/>
-        <v>31.545927043811364</v>
-      </c>
-      <c r="Q27" s="9">
-        <f t="shared" si="8"/>
         <v>27.753160396128099</v>
       </c>
       <c r="R27" s="9">
@@ -12255,7 +12246,7 @@
         <v>6564</v>
       </c>
       <c r="T27" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>11.063881170018281</v>
       </c>
       <c r="U27" s="11">
@@ -12349,19 +12340,19 @@
         <v>16.122177477694724</v>
       </c>
       <c r="N28" s="9">
+        <f t="shared" si="11"/>
+        <v>13.509094472597361</v>
+      </c>
+      <c r="O28" s="9">
+        <f t="shared" si="12"/>
+        <v>12.59682846743377</v>
+      </c>
+      <c r="P28" s="9">
         <f t="shared" si="9"/>
-        <v>13.509094472597361</v>
-      </c>
-      <c r="O28" s="9">
+        <v>11.672664433600669</v>
+      </c>
+      <c r="Q28" s="9">
         <f t="shared" si="10"/>
-        <v>12.59682846743377</v>
-      </c>
-      <c r="P28" s="9">
-        <f t="shared" si="7"/>
-        <v>11.672664433600669</v>
-      </c>
-      <c r="Q28" s="9">
-        <f t="shared" si="8"/>
         <v>11.358809063688398</v>
       </c>
       <c r="R28" s="9">
@@ -12373,7 +12364,7 @@
         <v>31797</v>
       </c>
       <c r="T28" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.1026722646790583</v>
       </c>
       <c r="U28" s="11">
@@ -12467,19 +12458,19 @@
         <v>-10.787673312643731</v>
       </c>
       <c r="N29" s="9">
+        <f t="shared" si="11"/>
+        <v>-119.05253060710538</v>
+      </c>
+      <c r="O29" s="9">
+        <f t="shared" si="12"/>
+        <v>34.796020724209249</v>
+      </c>
+      <c r="P29" s="9">
         <f t="shared" si="9"/>
-        <v>-119.05253060710538</v>
-      </c>
-      <c r="O29" s="9">
+        <v>40.024792542863082</v>
+      </c>
+      <c r="Q29" s="9">
         <f t="shared" si="10"/>
-        <v>34.796020724209249</v>
-      </c>
-      <c r="P29" s="9">
-        <f t="shared" si="7"/>
-        <v>40.024792542863082</v>
-      </c>
-      <c r="Q29" s="9">
-        <f t="shared" si="8"/>
         <v>39.239992689081447</v>
       </c>
       <c r="R29" s="9">
@@ -12491,7 +12482,7 @@
         <v>5633.6</v>
       </c>
       <c r="T29" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>8.5765602811701207</v>
       </c>
       <c r="U29" s="11">
@@ -12582,19 +12573,19 @@
       </c>
       <c r="M30" s="9"/>
       <c r="N30" s="9">
+        <f t="shared" si="11"/>
+        <v>124.8168836034674</v>
+      </c>
+      <c r="O30" s="9">
+        <f t="shared" si="12"/>
+        <v>57.695362969285391</v>
+      </c>
+      <c r="P30" s="9">
         <f t="shared" si="9"/>
-        <v>124.8168836034674</v>
-      </c>
-      <c r="O30" s="9">
+        <v>35.011285554673961</v>
+      </c>
+      <c r="Q30" s="9">
         <f t="shared" si="10"/>
-        <v>57.695362969285391</v>
-      </c>
-      <c r="P30" s="9">
-        <f t="shared" si="7"/>
-        <v>35.011285554673961</v>
-      </c>
-      <c r="Q30" s="9">
-        <f t="shared" si="8"/>
         <v>27.683056721790191</v>
       </c>
       <c r="R30" s="9">
@@ -12606,7 +12597,7 @@
         <v>1300.3</v>
       </c>
       <c r="T30" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>33.56233176959163</v>
       </c>
       <c r="U30" s="11">
@@ -12700,19 +12691,19 @@
         <v>13.93198370784577</v>
       </c>
       <c r="N31" s="9">
+        <f t="shared" si="11"/>
+        <v>106.71964098887003</v>
+      </c>
+      <c r="O31" s="9">
+        <f t="shared" si="12"/>
+        <v>33.314917166177857</v>
+      </c>
+      <c r="P31" s="9">
         <f t="shared" si="9"/>
-        <v>106.71964098887003</v>
-      </c>
-      <c r="O31" s="9">
+        <v>21.070890439473029</v>
+      </c>
+      <c r="Q31" s="9">
         <f t="shared" si="10"/>
-        <v>33.314917166177857</v>
-      </c>
-      <c r="P31" s="9">
-        <f t="shared" si="7"/>
-        <v>21.070890439473029</v>
-      </c>
-      <c r="Q31" s="9">
-        <f t="shared" si="8"/>
         <v>18.020489180902477</v>
       </c>
       <c r="R31" s="9">
@@ -12724,7 +12715,7 @@
         <v>24121.1</v>
       </c>
       <c r="T31" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.6733212830260644</v>
       </c>
       <c r="U31" s="11">
@@ -12818,19 +12809,19 @@
         <v>21.719449821701488</v>
       </c>
       <c r="N32" s="9">
+        <f t="shared" si="11"/>
+        <v>54.6273627284315</v>
+      </c>
+      <c r="O32" s="9">
+        <f t="shared" si="12"/>
+        <v>19.740476157659948</v>
+      </c>
+      <c r="P32" s="9">
         <f t="shared" si="9"/>
-        <v>54.6273627284315</v>
-      </c>
-      <c r="O32" s="9">
+        <v>19.184704856313111</v>
+      </c>
+      <c r="Q32" s="9">
         <f t="shared" si="10"/>
-        <v>19.740476157659948</v>
-      </c>
-      <c r="P32" s="9">
-        <f t="shared" si="7"/>
-        <v>19.184704856313111</v>
-      </c>
-      <c r="Q32" s="9">
-        <f t="shared" si="8"/>
         <v>18.65032211153499</v>
       </c>
       <c r="R32" s="9">
@@ -12842,7 +12833,7 @@
         <v>10106</v>
       </c>
       <c r="T32" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>3.3750469028300021</v>
       </c>
       <c r="U32" s="11">
@@ -12933,19 +12924,19 @@
       </c>
       <c r="M33" s="9"/>
       <c r="N33" s="9">
+        <f t="shared" si="11"/>
+        <v>-2456.4074942119732</v>
+      </c>
+      <c r="O33" s="9">
+        <f t="shared" si="12"/>
+        <v>455.41177547840903</v>
+      </c>
+      <c r="P33" s="9">
         <f t="shared" si="9"/>
-        <v>-2456.4074942119732</v>
-      </c>
-      <c r="O33" s="9">
+        <v>145.94071240918308</v>
+      </c>
+      <c r="Q33" s="9">
         <f t="shared" si="10"/>
-        <v>455.41177547840903</v>
-      </c>
-      <c r="P33" s="9">
-        <f t="shared" si="7"/>
-        <v>145.94071240918308</v>
-      </c>
-      <c r="Q33" s="9">
-        <f t="shared" si="8"/>
         <v>92.480956382474901</v>
       </c>
       <c r="R33" s="9">
@@ -12957,7 +12948,7 @@
         <v>1800.3999999999999</v>
       </c>
       <c r="T33" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>14.724558431459677</v>
       </c>
       <c r="U33" s="11">
@@ -13045,19 +13036,19 @@
         <v>61.826746837321757</v>
       </c>
       <c r="N34" s="9">
+        <f t="shared" si="11"/>
+        <v>43.186684655582482</v>
+      </c>
+      <c r="O34" s="9">
+        <f t="shared" si="12"/>
+        <v>35.35178377400883</v>
+      </c>
+      <c r="P34" s="9">
         <f t="shared" si="9"/>
-        <v>43.186684655582482</v>
-      </c>
-      <c r="O34" s="9">
+        <v>30.291896240348962</v>
+      </c>
+      <c r="Q34" s="9">
         <f t="shared" si="10"/>
-        <v>35.35178377400883</v>
-      </c>
-      <c r="P34" s="9">
-        <f t="shared" si="7"/>
-        <v>30.291896240348962</v>
-      </c>
-      <c r="Q34" s="9">
-        <f t="shared" si="8"/>
         <v>28.488425079671067</v>
       </c>
       <c r="R34" s="9">
@@ -13069,7 +13060,7 @@
         <v>3766.2000000000003</v>
       </c>
       <c r="T34" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>6.6820030800276129</v>
       </c>
       <c r="U34" s="11">
@@ -13163,19 +13154,19 @@
         <v>15.543103277552239</v>
       </c>
       <c r="N35" s="9">
+        <f t="shared" si="11"/>
+        <v>13.175137873960487</v>
+      </c>
+      <c r="O35" s="9">
+        <f t="shared" si="12"/>
+        <v>13.034213052181057</v>
+      </c>
+      <c r="P35" s="9">
         <f t="shared" si="9"/>
-        <v>13.175137873960487</v>
-      </c>
-      <c r="O35" s="9">
+        <v>13.017977657202124</v>
+      </c>
+      <c r="Q35" s="9">
         <f t="shared" si="10"/>
-        <v>13.034213052181057</v>
-      </c>
-      <c r="P35" s="9">
-        <f t="shared" si="7"/>
-        <v>13.017977657202124</v>
-      </c>
-      <c r="Q35" s="9">
-        <f t="shared" si="8"/>
         <v>12.928267392526452</v>
       </c>
       <c r="R35" s="9">
@@ -13187,7 +13178,7 @@
         <v>4665.2999999999993</v>
       </c>
       <c r="T35" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>3.3646239255782051</v>
       </c>
       <c r="U35" s="11">
@@ -13280,11 +13271,11 @@
       <c r="N36" s="9"/>
       <c r="O36" s="9"/>
       <c r="P36" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-67.931526267062239</v>
       </c>
       <c r="Q36" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-91.424579021685105</v>
       </c>
       <c r="R36" s="9">
@@ -13296,7 +13287,7 @@
         <v>5361.4</v>
       </c>
       <c r="T36" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.5828354534263442</v>
       </c>
       <c r="U36" s="11">
@@ -13385,23 +13376,23 @@
         <v>785.13023250450681</v>
       </c>
       <c r="M37" s="9">
-        <f t="shared" ref="M37:O38" si="11">$G37/H37</f>
+        <f t="shared" ref="M37:O38" si="13">$G37/H37</f>
         <v>20.343100554235953</v>
       </c>
       <c r="N37" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>20.217508692565595</v>
       </c>
       <c r="O37" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>17.192551754383128</v>
       </c>
       <c r="P37" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>16.693220617896461</v>
       </c>
       <c r="Q37" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>16.362467611290537</v>
       </c>
       <c r="R37" s="9">
@@ -13413,7 +13404,7 @@
         <v>4554.8999999999996</v>
       </c>
       <c r="T37" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.8204061560078162</v>
       </c>
       <c r="U37" s="11">
@@ -13503,23 +13494,23 @@
         <v>438.86296241324982</v>
       </c>
       <c r="M38" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>131.54895152198426</v>
       </c>
       <c r="N38" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>73.70294315500918</v>
       </c>
       <c r="O38" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>49.781864907355803</v>
       </c>
       <c r="P38" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>33.914500181596061</v>
       </c>
       <c r="Q38" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>26.587780239729149</v>
       </c>
       <c r="R38" s="9">
@@ -13531,7 +13522,7 @@
         <v>748.1</v>
       </c>
       <c r="T38" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>15.597369335650313</v>
       </c>
       <c r="U38" s="11">
@@ -13637,7 +13628,7 @@
         <v>82.3</v>
       </c>
       <c r="T39" s="33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>135.77822600243016</v>
       </c>
       <c r="U39" s="11">
@@ -13723,15 +13714,15 @@
       <c r="M40" s="9"/>
       <c r="N40" s="9"/>
       <c r="O40" s="9">
-        <f t="shared" ref="O40:O50" si="12">$G40/J40</f>
+        <f t="shared" ref="O40:O50" si="14">$G40/J40</f>
         <v>46.453008883350471</v>
       </c>
       <c r="P40" s="9">
-        <f t="shared" ref="P40:P50" si="13">$G40/K40</f>
+        <f t="shared" ref="P40:P50" si="15">$G40/K40</f>
         <v>28.526696391397731</v>
       </c>
       <c r="Q40" s="9">
-        <f t="shared" ref="Q40:Q50" si="14">$G40/L40</f>
+        <f t="shared" ref="Q40:Q50" si="16">$G40/L40</f>
         <v>21.482426109656544</v>
       </c>
       <c r="R40" s="9">
@@ -13743,7 +13734,7 @@
         <v>4112.7</v>
       </c>
       <c r="T40" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.6489289274685732</v>
       </c>
       <c r="U40" s="11">
@@ -13841,15 +13832,15 @@
         <v>60.089477042058888</v>
       </c>
       <c r="O41" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>22.858718918047266</v>
       </c>
       <c r="P41" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>19.683505998908714</v>
       </c>
       <c r="Q41" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>18.48193715774482</v>
       </c>
       <c r="R41" s="9">
@@ -13861,7 +13852,7 @@
         <v>3330.6000000000004</v>
       </c>
       <c r="T41" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.5168714345763519</v>
       </c>
       <c r="U41" s="11"/>
@@ -13949,19 +13940,19 @@
       </c>
       <c r="M42" s="9"/>
       <c r="N42" s="9">
-        <f t="shared" ref="N42:N50" si="15">$G42/I42</f>
+        <f t="shared" ref="N42:N50" si="17">$G42/I42</f>
         <v>214.79933678772309</v>
       </c>
       <c r="O42" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>81.86336317351963</v>
       </c>
       <c r="P42" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>47.64614567947374</v>
       </c>
       <c r="Q42" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>33.176933495408214</v>
       </c>
       <c r="R42" s="9">
@@ -13973,7 +13964,7 @@
         <v>496.77</v>
       </c>
       <c r="T42" s="33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>15.837560641745677</v>
       </c>
       <c r="U42" s="11">
@@ -14063,23 +14054,23 @@
         <v>716.71150665191999</v>
       </c>
       <c r="M43" s="9">
-        <f t="shared" ref="M43:M52" si="16">$G43/H43</f>
+        <f t="shared" ref="M43:M52" si="18">$G43/H43</f>
         <v>16.63019141914193</v>
       </c>
       <c r="N43" s="9">
+        <f t="shared" si="17"/>
+        <v>18.164792845468796</v>
+      </c>
+      <c r="O43" s="9">
+        <f t="shared" si="14"/>
+        <v>12.064385441865083</v>
+      </c>
+      <c r="P43" s="9">
         <f t="shared" si="15"/>
-        <v>18.164792845468796</v>
-      </c>
-      <c r="O43" s="9">
-        <f t="shared" si="12"/>
-        <v>12.064385441865083</v>
-      </c>
-      <c r="P43" s="9">
-        <f t="shared" si="13"/>
         <v>11.107008711725983</v>
       </c>
       <c r="Q43" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>10.545975514344358</v>
       </c>
       <c r="R43" s="9">
@@ -14091,7 +14082,7 @@
         <v>5443.3289999999997</v>
       </c>
       <c r="T43" s="33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.3885660778541957</v>
       </c>
       <c r="U43" s="11">
@@ -14181,23 +14172,23 @@
         <v>458.17865373511</v>
       </c>
       <c r="M44" s="9">
+        <f t="shared" si="18"/>
+        <v>39.977018498367798</v>
+      </c>
+      <c r="N44" s="9">
+        <f t="shared" si="17"/>
+        <v>25.163469895614533</v>
+      </c>
+      <c r="O44" s="9">
+        <f t="shared" si="14"/>
+        <v>20.690114851429911</v>
+      </c>
+      <c r="P44" s="9">
+        <f t="shared" si="15"/>
+        <v>17.822792072663354</v>
+      </c>
+      <c r="Q44" s="9">
         <f t="shared" si="16"/>
-        <v>39.977018498367798</v>
-      </c>
-      <c r="N44" s="9">
-        <f t="shared" si="15"/>
-        <v>25.163469895614533</v>
-      </c>
-      <c r="O44" s="9">
-        <f t="shared" si="12"/>
-        <v>20.690114851429911</v>
-      </c>
-      <c r="P44" s="9">
-        <f t="shared" si="13"/>
-        <v>17.822792072663354</v>
-      </c>
-      <c r="Q44" s="9">
-        <f t="shared" si="14"/>
         <v>16.036923457913907</v>
       </c>
       <c r="R44" s="9">
@@ -14209,7 +14200,7 @@
         <v>943.53100000000006</v>
       </c>
       <c r="T44" s="33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>7.7875300334594195</v>
       </c>
       <c r="U44" s="11">
@@ -14299,23 +14290,23 @@
         <v>590.86033903550401</v>
       </c>
       <c r="M45" s="9">
+        <f t="shared" si="18"/>
+        <v>47.048643292683089</v>
+      </c>
+      <c r="N45" s="9">
+        <f t="shared" si="17"/>
+        <v>12.426486132638003</v>
+      </c>
+      <c r="O45" s="9">
+        <f t="shared" si="14"/>
+        <v>12.037789631777283</v>
+      </c>
+      <c r="P45" s="9">
+        <f t="shared" si="15"/>
+        <v>10.803874494923734</v>
+      </c>
+      <c r="Q45" s="9">
         <f t="shared" si="16"/>
-        <v>47.048643292683089</v>
-      </c>
-      <c r="N45" s="9">
-        <f t="shared" si="15"/>
-        <v>12.426486132638003</v>
-      </c>
-      <c r="O45" s="9">
-        <f t="shared" si="12"/>
-        <v>12.037789631777283</v>
-      </c>
-      <c r="P45" s="9">
-        <f t="shared" si="13"/>
-        <v>10.803874494923734</v>
-      </c>
-      <c r="Q45" s="9">
-        <f t="shared" si="14"/>
         <v>10.447108381104396</v>
       </c>
       <c r="R45" s="9">
@@ -14327,7 +14318,7 @@
         <v>3946.1359999999995</v>
       </c>
       <c r="T45" s="33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.5642598227734674</v>
       </c>
       <c r="U45" s="11">
@@ -14417,23 +14408,23 @@
         <v>650.23700219008219</v>
       </c>
       <c r="M46" s="9">
+        <f t="shared" si="18"/>
+        <v>-20.703024980174479</v>
+      </c>
+      <c r="N46" s="9">
+        <f t="shared" si="17"/>
+        <v>13.253712673904129</v>
+      </c>
+      <c r="O46" s="9">
+        <f t="shared" si="14"/>
+        <v>10.624410543004588</v>
+      </c>
+      <c r="P46" s="9">
+        <f t="shared" si="15"/>
+        <v>9.5642637927223628</v>
+      </c>
+      <c r="Q46" s="9">
         <f t="shared" si="16"/>
-        <v>-20.703024980174479</v>
-      </c>
-      <c r="N46" s="9">
-        <f t="shared" si="15"/>
-        <v>13.253712673904129</v>
-      </c>
-      <c r="O46" s="9">
-        <f t="shared" si="12"/>
-        <v>10.624410543004588</v>
-      </c>
-      <c r="P46" s="9">
-        <f t="shared" si="13"/>
-        <v>9.5642637927223628</v>
-      </c>
-      <c r="Q46" s="9">
-        <f t="shared" si="14"/>
         <v>8.8891282582092153</v>
       </c>
       <c r="R46" s="9">
@@ -14445,7 +14436,7 @@
         <v>2532.6282287822874</v>
       </c>
       <c r="T46" s="33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.2822299953121057</v>
       </c>
       <c r="U46" s="11">
@@ -14535,23 +14526,23 @@
         <v>714.9940225586721</v>
       </c>
       <c r="M47" s="9">
+        <f t="shared" si="18"/>
+        <v>19.719847062912738</v>
+      </c>
+      <c r="N47" s="9">
+        <f t="shared" si="17"/>
+        <v>11.889165267519763</v>
+      </c>
+      <c r="O47" s="9">
+        <f t="shared" si="14"/>
+        <v>9.6019314379207792</v>
+      </c>
+      <c r="P47" s="9">
+        <f t="shared" si="15"/>
+        <v>8.5230834095737489</v>
+      </c>
+      <c r="Q47" s="9">
         <f t="shared" si="16"/>
-        <v>19.719847062912738</v>
-      </c>
-      <c r="N47" s="9">
-        <f t="shared" si="15"/>
-        <v>11.889165267519763</v>
-      </c>
-      <c r="O47" s="9">
-        <f t="shared" si="12"/>
-        <v>9.6019314379207792</v>
-      </c>
-      <c r="P47" s="9">
-        <f t="shared" si="13"/>
-        <v>8.5230834095737489</v>
-      </c>
-      <c r="Q47" s="9">
-        <f t="shared" si="14"/>
         <v>7.9348915109768541</v>
       </c>
       <c r="R47" s="9">
@@ -14563,7 +14554,7 @@
         <v>2405.3000000000002</v>
       </c>
       <c r="T47" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.3587078534902091</v>
       </c>
       <c r="U47" s="11">
@@ -14653,23 +14644,23 @@
         <v>576.68778799147537</v>
       </c>
       <c r="M48" s="9">
+        <f t="shared" si="18"/>
+        <v>11.149412047036243</v>
+      </c>
+      <c r="N48" s="9">
+        <f t="shared" si="17"/>
+        <v>9.5990360716224465</v>
+      </c>
+      <c r="O48" s="9">
+        <f t="shared" si="14"/>
+        <v>8.9013735911478626</v>
+      </c>
+      <c r="P48" s="9">
+        <f t="shared" si="15"/>
+        <v>8.4401475981584024</v>
+      </c>
+      <c r="Q48" s="9">
         <f t="shared" si="16"/>
-        <v>11.149412047036243</v>
-      </c>
-      <c r="N48" s="9">
-        <f t="shared" si="15"/>
-        <v>9.5990360716224465</v>
-      </c>
-      <c r="O48" s="9">
-        <f t="shared" si="12"/>
-        <v>8.9013735911478626</v>
-      </c>
-      <c r="P48" s="9">
-        <f t="shared" si="13"/>
-        <v>8.4401475981584024</v>
-      </c>
-      <c r="Q48" s="9">
-        <f t="shared" si="14"/>
         <v>8.0562829606315134</v>
       </c>
       <c r="R48" s="9">
@@ -14681,7 +14672,7 @@
         <v>1537.2</v>
       </c>
       <c r="T48" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>3.0223523289097072</v>
       </c>
       <c r="U48" s="11">
@@ -14771,23 +14762,23 @@
         <v>471.20446674269516</v>
       </c>
       <c r="M49" s="9">
+        <f t="shared" si="18"/>
+        <v>9.0410038986532903</v>
+      </c>
+      <c r="N49" s="9">
+        <f t="shared" si="17"/>
+        <v>9.9438749105351896</v>
+      </c>
+      <c r="O49" s="9">
+        <f t="shared" si="14"/>
+        <v>9.3610508499972127</v>
+      </c>
+      <c r="P49" s="9">
+        <f t="shared" si="15"/>
+        <v>7.9916369765650614</v>
+      </c>
+      <c r="Q49" s="9">
         <f t="shared" si="16"/>
-        <v>9.0410038986532903</v>
-      </c>
-      <c r="N49" s="9">
-        <f t="shared" si="15"/>
-        <v>9.9438749105351896</v>
-      </c>
-      <c r="O49" s="9">
-        <f t="shared" si="12"/>
-        <v>9.3610508499972127</v>
-      </c>
-      <c r="P49" s="9">
-        <f t="shared" si="13"/>
-        <v>7.9916369765650614</v>
-      </c>
-      <c r="Q49" s="9">
-        <f t="shared" si="14"/>
         <v>7.4519753799868207</v>
       </c>
       <c r="R49" s="9">
@@ -14799,7 +14790,7 @@
         <v>3335.0709219858149</v>
       </c>
       <c r="T49" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.0528723877978503</v>
       </c>
       <c r="U49" s="11">
@@ -14889,23 +14880,23 @@
         <v>21.999999999999979</v>
       </c>
       <c r="M50" s="9">
+        <f t="shared" si="18"/>
+        <v>-23.250702446724556</v>
+      </c>
+      <c r="N50" s="9">
+        <f t="shared" si="17"/>
+        <v>-26.539315315315349</v>
+      </c>
+      <c r="O50" s="9">
+        <f t="shared" si="14"/>
+        <v>-1.5542175794027644</v>
+      </c>
+      <c r="P50" s="9">
+        <f t="shared" si="15"/>
+        <v>-144.40509803921549</v>
+      </c>
+      <c r="Q50" s="9">
         <f t="shared" si="16"/>
-        <v>-23.250702446724556</v>
-      </c>
-      <c r="N50" s="9">
-        <f t="shared" si="15"/>
-        <v>-26.539315315315349</v>
-      </c>
-      <c r="O50" s="9">
-        <f t="shared" si="12"/>
-        <v>-1.5542175794027644</v>
-      </c>
-      <c r="P50" s="9">
-        <f t="shared" si="13"/>
-        <v>-144.40509803921549</v>
-      </c>
-      <c r="Q50" s="9">
-        <f t="shared" si="14"/>
         <v>133.90290909090919</v>
       </c>
       <c r="R50" s="9">
@@ -14917,7 +14908,7 @@
         <v>1426.5</v>
       </c>
       <c r="T50" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.0650991938310548</v>
       </c>
       <c r="U50" s="11">
@@ -15007,7 +14998,7 @@
         <v>-191.72685569219993</v>
       </c>
       <c r="M51" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-1.0597063993538887</v>
       </c>
       <c r="N51" s="9"/>
@@ -15023,7 +15014,7 @@
         <v>628.79999999999995</v>
       </c>
       <c r="T51" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>3.5473536895674309</v>
       </c>
       <c r="U51" s="11">
@@ -15107,7 +15098,7 @@
         <v>200.97624470114883</v>
       </c>
       <c r="M52" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>16.944510182606543</v>
       </c>
       <c r="N52" s="9">
@@ -15135,7 +15126,7 @@
         <v>482.9</v>
       </c>
       <c r="T52" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>3.3212362808034794</v>
       </c>
       <c r="U52" s="11">
@@ -15238,7 +15229,7 @@
         <v>1418.5619999999999</v>
       </c>
       <c r="T53" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.118102698366374</v>
       </c>
       <c r="U53" s="11">
@@ -15330,15 +15321,15 @@
       <c r="M54" s="9"/>
       <c r="N54" s="9"/>
       <c r="O54" s="9">
-        <f t="shared" ref="O54:Q57" si="17">$G54/J54</f>
+        <f t="shared" ref="O54:Q57" si="19">$G54/J54</f>
         <v>156.17431221963986</v>
       </c>
       <c r="P54" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>40.503000465598639</v>
       </c>
       <c r="Q54" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>23.556584607811065</v>
       </c>
       <c r="R54" s="9">
@@ -15350,7 +15341,7 @@
         <v>748.14400000000001</v>
       </c>
       <c r="T54" s="33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.4365015291173893</v>
       </c>
       <c r="U54" s="11">
@@ -15445,15 +15436,15 @@
         <v>232.8931152588427</v>
       </c>
       <c r="O55" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>34.046256239027386</v>
       </c>
       <c r="P55" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>14.388264068529866</v>
       </c>
       <c r="Q55" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>8.7909603304675592</v>
       </c>
       <c r="R55" s="9">
@@ -15465,7 +15456,7 @@
         <v>1316.4</v>
       </c>
       <c r="T55" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.72810695837131578</v>
       </c>
       <c r="U55" s="11">
@@ -15562,15 +15553,15 @@
         <v>58.571875034353958</v>
       </c>
       <c r="O56" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>31.208903130202106</v>
       </c>
       <c r="P56" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>24.790357009862777</v>
       </c>
       <c r="Q56" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>20.353961697081026</v>
       </c>
       <c r="R56" s="9">
@@ -15582,7 +15573,7 @@
         <v>391.49999999999994</v>
       </c>
       <c r="T56" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.9052720306513415</v>
       </c>
       <c r="U56" s="11">
@@ -15636,93 +15627,93 @@
         <v>214</v>
       </c>
       <c r="D57" s="12">
-        <f>[64]Main!$D$3</f>
+        <f>[54]Main!$D$3</f>
         <v>17.52</v>
       </c>
       <c r="E57" s="8">
-        <f>[64]Main!$D$5</f>
+        <f>[54]Main!$D$5</f>
         <v>492.31200000000001</v>
       </c>
       <c r="F57" s="8">
-        <f>[64]Main!$D$8</f>
+        <f>[54]Main!$D$8</f>
         <v>-186.5</v>
       </c>
       <c r="G57" s="8">
-        <f>[64]Main!$D$9</f>
+        <f>[54]Main!$D$9</f>
         <v>678.81200000000001</v>
       </c>
       <c r="H57" s="8">
-        <f>[64]Model!Q$17</f>
+        <f>[54]Model!Q$17</f>
         <v>-6.4999999999999982</v>
       </c>
       <c r="I57" s="8">
-        <f>[64]Model!R$17</f>
+        <f>[54]Model!R$17</f>
         <v>-12.812000000000056</v>
       </c>
       <c r="J57" s="8">
-        <f>[64]Model!S$17</f>
+        <f>[54]Model!S$17</f>
         <v>62.024759999999965</v>
       </c>
       <c r="K57" s="8">
-        <f>[64]Model!T$17</f>
+        <f>[54]Model!T$17</f>
         <v>68.689998399999979</v>
       </c>
       <c r="L57" s="8">
-        <f>[64]Model!U$17</f>
+        <f>[54]Model!U$17</f>
         <v>70.159895087999971</v>
       </c>
       <c r="M57" s="9"/>
       <c r="N57" s="9"/>
       <c r="O57" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>10.944210021933182</v>
       </c>
       <c r="P57" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>9.8822538333324559</v>
       </c>
       <c r="Q57" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>9.6752140114887784</v>
       </c>
       <c r="R57" s="9">
-        <f>G57/[64]Model!$AB$17</f>
+        <f>G57/[54]Model!$AB$17</f>
         <v>7.577552139624113</v>
       </c>
-      <c r="S57" s="35">
-        <f>[64]Model!$R$3</f>
+      <c r="S57" s="10">
+        <f>[54]Model!$R$3</f>
         <v>756.4</v>
       </c>
-      <c r="T57" s="36">
-        <f t="shared" si="6"/>
+      <c r="T57" s="33">
+        <f t="shared" si="8"/>
         <v>0.89742464304600744</v>
       </c>
       <c r="U57" s="11">
-        <f>[64]Model!P$21</f>
+        <f>[54]Model!P$21</f>
         <v>4.8674110258199565E-2</v>
       </c>
       <c r="V57" s="11">
-        <f>[64]Model!Q$21</f>
+        <f>[54]Model!Q$21</f>
         <v>0.24521710197970381</v>
       </c>
-      <c r="W57" s="37">
-        <f>[64]Model!$R$22</f>
+      <c r="W57" s="11">
+        <f>[54]Model!$R$22</f>
         <v>0.40179666842940243</v>
       </c>
-      <c r="X57" s="37">
-        <f>[64]Model!$R$26</f>
+      <c r="X57" s="11">
+        <f>[54]Model!$R$26</f>
         <v>-1.1253305129561155E-2</v>
       </c>
       <c r="Y57" s="11">
-        <f>[64]Model!$AE$23</f>
+        <f>[54]Model!$AE$23</f>
         <v>0.11</v>
       </c>
       <c r="Z57" s="11">
-        <f>[64]Model!$AE$29</f>
+        <f>[54]Model!$AE$29</f>
         <v>-0.1323068950304066</v>
       </c>
       <c r="AA57" s="7" t="str">
-        <f>[64]Model!$AE$30</f>
+        <f>[54]Model!$AE$30</f>
         <v>Slightly overvalued</v>
       </c>
       <c r="AB57" s="7" t="s">
@@ -15732,11 +15723,11 @@
         <v>2000</v>
       </c>
       <c r="AE57" s="17">
-        <f>[64]Main!$E$3</f>
+        <f>[54]Main!$E$3</f>
         <v>45927</v>
       </c>
       <c r="AF57" s="17">
-        <f>[64]Main!$G$3</f>
+        <f>[54]Main!$G$3</f>
         <v>45960</v>
       </c>
     </row>
@@ -15748,87 +15739,87 @@
         <v>198</v>
       </c>
       <c r="D58" s="12">
-        <f>[54]Main!$D$3</f>
+        <f>[55]Main!$D$3</f>
         <v>35.03</v>
       </c>
       <c r="E58" s="8">
-        <f>[54]Main!$D$5</f>
+        <f>[55]Main!$D$5</f>
         <v>637.54600000000005</v>
       </c>
       <c r="F58" s="8">
-        <f>[54]Main!$D$8</f>
+        <f>[55]Main!$D$8</f>
         <v>47.5</v>
       </c>
       <c r="G58" s="8">
-        <f>[54]Main!$D$9</f>
+        <f>[55]Main!$D$9</f>
         <v>590.04600000000005</v>
       </c>
       <c r="H58" s="8">
-        <f>[54]Model!M$14</f>
+        <f>[55]Model!M$14</f>
         <v>-42.300000000000011</v>
       </c>
       <c r="I58" s="8">
-        <f>[54]Model!N$14</f>
+        <f>[55]Model!N$14</f>
         <v>-20.811699999999991</v>
       </c>
       <c r="J58" s="8">
-        <f>[54]Model!O$14</f>
+        <f>[55]Model!O$14</f>
         <v>-11.897724999999994</v>
       </c>
       <c r="K58" s="8">
-        <f>[54]Model!P$14</f>
+        <f>[55]Model!P$14</f>
         <v>-7.5577599999999938</v>
       </c>
       <c r="L58" s="8">
-        <f>[54]Model!Q$14</f>
+        <f>[55]Model!Q$14</f>
         <v>1.4139300000000246</v>
       </c>
       <c r="M58" s="9"/>
       <c r="N58" s="9"/>
       <c r="O58" s="9"/>
       <c r="P58" s="9">
-        <f t="shared" ref="P58:Q60" si="18">$G58/K58</f>
+        <f t="shared" ref="P58:Q60" si="20">$G58/K58</f>
         <v>-78.071545008044779</v>
       </c>
       <c r="Q58" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>417.30920201140776</v>
       </c>
       <c r="R58" s="9">
-        <f>G58/[54]Model!$X$14</f>
+        <f>G58/[55]Model!$X$14</f>
         <v>6.4135193994224995</v>
       </c>
       <c r="S58" s="29">
-        <f>[54]Model!$M$3</f>
+        <f>[55]Model!$M$3</f>
         <v>76.099999999999994</v>
       </c>
       <c r="T58" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>7.7535611038107763</v>
       </c>
       <c r="U58" s="11"/>
       <c r="V58" s="11">
-        <f>[54]Model!$M$18</f>
+        <f>[55]Model!$M$18</f>
         <v>0.16183206106870229</v>
       </c>
       <c r="W58" s="34">
-        <f>[54]Model!$M$19</f>
+        <f>[55]Model!$M$19</f>
         <v>0.31931668856767409</v>
       </c>
       <c r="X58" s="34">
-        <f>[54]Model!$M$23</f>
+        <f>[55]Model!$M$23</f>
         <v>-0.53350854139290427</v>
       </c>
       <c r="Y58" s="11">
-        <f>[54]Model!$AA$20</f>
+        <f>[55]Model!$AA$20</f>
         <v>0.11</v>
       </c>
       <c r="Z58" s="11">
-        <f>[54]Model!$AA$26</f>
+        <f>[55]Model!$AA$26</f>
         <v>-0.30871809322658095</v>
       </c>
       <c r="AA58" s="7" t="str">
-        <f>[54]Model!$AA$27</f>
+        <f>[55]Model!$AA$27</f>
         <v>Overvalued</v>
       </c>
       <c r="AB58" s="7" t="s">
@@ -15838,11 +15829,11 @@
         <v>2010</v>
       </c>
       <c r="AE58" s="17">
-        <f>[54]Main!$E$3</f>
+        <f>[55]Main!$E$3</f>
         <v>45905</v>
       </c>
       <c r="AF58" s="17">
-        <f>[54]Main!$G$3</f>
+        <f>[55]Main!$G$3</f>
         <v>45994</v>
       </c>
     </row>
@@ -15854,39 +15845,39 @@
         <v>186</v>
       </c>
       <c r="D59" s="19">
-        <f>[55]Main!$D$3</f>
+        <f>[56]Main!$D$3</f>
         <v>8.02</v>
       </c>
       <c r="E59" s="8">
-        <f>[55]Main!$D$5</f>
+        <f>[56]Main!$D$5</f>
         <v>286.31400000000002</v>
       </c>
       <c r="F59" s="8">
-        <f>[55]Main!$D$8</f>
+        <f>[56]Main!$D$8</f>
         <v>-71.5</v>
       </c>
       <c r="G59" s="8">
-        <f>[55]Main!$D$9</f>
+        <f>[56]Main!$D$9</f>
         <v>357.81400000000002</v>
       </c>
       <c r="H59" s="8">
-        <f>[55]Model!Y$18</f>
+        <f>[56]Model!Y$18</f>
         <v>30.799999999999997</v>
       </c>
       <c r="I59" s="8">
-        <f>[55]Model!Z$18</f>
+        <f>[56]Model!Z$18</f>
         <v>21.632190000000008</v>
       </c>
       <c r="J59" s="8">
-        <f>[55]Model!AA$18</f>
+        <f>[56]Model!AA$18</f>
         <v>44.623238034999986</v>
       </c>
       <c r="K59" s="8">
-        <f>[55]Model!AB$18</f>
+        <f>[56]Model!AB$18</f>
         <v>47.244279367299995</v>
       </c>
       <c r="L59" s="8">
-        <f>[55]Model!AC$18</f>
+        <f>[56]Model!AC$18</f>
         <v>51.957359563301495</v>
       </c>
       <c r="M59" s="9">
@@ -15902,51 +15893,51 @@
         <v>8.0185574995555147</v>
       </c>
       <c r="P59" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>7.5737000286993483</v>
       </c>
       <c r="Q59" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>6.8866856015664641</v>
       </c>
       <c r="R59" s="9">
-        <f>G59/[55]Model!$AJ$18</f>
+        <f>G59/[56]Model!$AJ$18</f>
         <v>5.0066353488957276</v>
       </c>
       <c r="S59" s="29">
-        <f>[55]Model!$Y$3</f>
+        <f>[56]Model!$Y$3</f>
         <v>127.2</v>
       </c>
       <c r="T59" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.813003144654088</v>
       </c>
       <c r="U59" s="11">
-        <f>[55]Model!$X$22</f>
+        <f>[56]Model!$X$22</f>
         <v>0.42091503267973862</v>
       </c>
       <c r="V59" s="11">
-        <f>[55]Model!$Y$22</f>
+        <f>[56]Model!$Y$22</f>
         <v>0.170193192272309</v>
       </c>
       <c r="W59" s="34">
-        <f>[55]Model!$Y$23</f>
+        <f>[56]Model!$Y$23</f>
         <v>0.94103773584905659</v>
       </c>
       <c r="X59" s="34">
-        <f>[55]Model!$Y$27</f>
+        <f>[56]Model!$Y$27</f>
         <v>0.285377358490566</v>
       </c>
       <c r="Y59" s="11">
-        <f>[55]Model!$AM$25</f>
+        <f>[56]Model!$AM$25</f>
         <v>0.11</v>
       </c>
       <c r="Z59" s="11">
-        <f>[55]Model!$AM$31</f>
+        <f>[56]Model!$AM$31</f>
         <v>0.53776133996255537</v>
       </c>
       <c r="AA59" s="7" t="str">
-        <f>[55]Model!$AM$32</f>
+        <f>[56]Model!$AM$32</f>
         <v>Heavily undervalued</v>
       </c>
       <c r="AB59" s="7" t="s">
@@ -15956,11 +15947,11 @@
         <v>2006</v>
       </c>
       <c r="AE59" s="17">
-        <f>[55]Main!$E$3</f>
+        <f>[56]Main!$E$3</f>
         <v>45910</v>
       </c>
       <c r="AF59" s="17">
-        <f>[55]Main!$G$3</f>
+        <f>[56]Main!$G$3</f>
         <v>45974</v>
       </c>
     </row>
@@ -15972,39 +15963,39 @@
         <v>64</v>
       </c>
       <c r="D60" s="12">
-        <f>[56]Main!$D$3</f>
+        <f>[57]Main!$D$3</f>
         <v>12.28</v>
       </c>
       <c r="E60" s="8">
-        <f>[56]Main!$D$5</f>
+        <f>[57]Main!$D$5</f>
         <v>184.2</v>
       </c>
       <c r="F60" s="8">
-        <f>[56]Main!$D$8</f>
+        <f>[57]Main!$D$8</f>
         <v>-21.599999999999994</v>
       </c>
       <c r="G60" s="8">
-        <f>[56]Main!$D$9</f>
+        <f>[57]Main!$D$9</f>
         <v>205.79999999999998</v>
       </c>
       <c r="H60" s="8">
-        <f>[56]Model!AU23</f>
+        <f>[57]Model!AU23</f>
         <v>3.1999999999999886</v>
       </c>
       <c r="I60" s="8">
-        <f>[56]Model!AV23</f>
+        <f>[57]Model!AV23</f>
         <v>-3.5082000000000235</v>
       </c>
       <c r="J60" s="8">
-        <f>[56]Model!AW23</f>
+        <f>[57]Model!AW23</f>
         <v>7.3717279999999858</v>
       </c>
       <c r="K60" s="8">
-        <f>[56]Model!AX23</f>
+        <f>[57]Model!AX23</f>
         <v>10.802357279999994</v>
       </c>
       <c r="L60" s="8">
-        <f>[56]Model!AY23</f>
+        <f>[57]Model!AY23</f>
         <v>13.440192995199988</v>
       </c>
       <c r="M60" s="9"/>
@@ -16017,42 +16008,42 @@
         <v>27.917470639177189</v>
       </c>
       <c r="P60" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>19.051397270577972</v>
       </c>
       <c r="Q60" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>15.31228011930328</v>
       </c>
       <c r="R60" s="9"/>
       <c r="S60" s="29">
-        <f>[56]Model!$AU$7</f>
+        <f>[57]Model!$AU$7</f>
         <v>206.39999999999998</v>
       </c>
       <c r="T60" s="32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.99709302325581395</v>
       </c>
       <c r="U60" s="11">
-        <f>[56]Model!AT$31</f>
+        <f>[57]Model!AT$31</f>
         <v>-0.23368678629690032</v>
       </c>
       <c r="V60" s="11">
-        <f>[56]Model!AU$31</f>
+        <f>[57]Model!AU$31</f>
         <v>9.8456625864821401E-2</v>
       </c>
       <c r="W60" s="34"/>
       <c r="X60" s="34"/>
       <c r="Y60" s="11">
-        <f>[56]Model!$BI$33</f>
+        <f>[57]Model!$BI$33</f>
         <v>0.12</v>
       </c>
       <c r="Z60" s="11">
-        <f>[56]Model!$BI$39</f>
+        <f>[57]Model!$BI$39</f>
         <v>-0.48992193040360954</v>
       </c>
       <c r="AA60" s="7" t="str">
-        <f>[56]Model!$BI$40</f>
+        <f>[57]Model!$BI$40</f>
         <v>Overvalued</v>
       </c>
       <c r="AB60" s="7" t="s">
@@ -16062,11 +16053,11 @@
         <v>1996</v>
       </c>
       <c r="AE60" s="17">
-        <f>[56]Main!$E$3</f>
+        <f>[57]Main!$E$3</f>
         <v>45898</v>
       </c>
       <c r="AF60" s="17">
-        <f>[56]Main!$G$3</f>
+        <f>[57]Main!$G$3</f>
         <v>45959</v>
       </c>
     </row>
@@ -16078,19 +16069,19 @@
         <v>88</v>
       </c>
       <c r="D61" s="18">
-        <f>[57]Main!$D$3</f>
+        <f>[58]Main!$D$3</f>
         <v>0.73199999999999998</v>
       </c>
       <c r="E61" s="8">
-        <f>[57]Main!$D$5</f>
+        <f>[58]Main!$D$5</f>
         <v>187.61160000000001</v>
       </c>
       <c r="F61" s="8">
-        <f>[57]Main!$D$8</f>
+        <f>[58]Main!$D$8</f>
         <v>0</v>
       </c>
       <c r="G61" s="8">
-        <f>[57]Main!$D$9</f>
+        <f>[58]Main!$D$9</f>
         <v>187.61160000000001</v>
       </c>
       <c r="H61" s="8"/>
@@ -16111,15 +16102,15 @@
       <c r="W61" s="34"/>
       <c r="X61" s="34"/>
       <c r="Y61" s="11">
-        <f>[57]Model!$AE$24</f>
+        <f>[58]Model!$AE$24</f>
         <v>0.11</v>
       </c>
       <c r="Z61" s="11">
-        <f>[57]Model!$AE$30</f>
+        <f>[58]Model!$AE$30</f>
         <v>-0.25169013126318518</v>
       </c>
       <c r="AA61" s="7" t="str">
-        <f>[57]Model!$AE$31</f>
+        <f>[58]Model!$AE$31</f>
         <v>Slightly overvalued</v>
       </c>
       <c r="AB61" s="7" t="s">
@@ -16129,11 +16120,11 @@
         <v>1972</v>
       </c>
       <c r="AE61" s="17">
-        <f>[57]Main!$E$3</f>
+        <f>[58]Main!$E$3</f>
         <v>44279</v>
       </c>
       <c r="AF61" s="17">
-        <f>[57]Main!$G$3</f>
+        <f>[58]Main!$G$3</f>
         <v>44406</v>
       </c>
     </row>
@@ -16145,39 +16136,39 @@
         <v>154</v>
       </c>
       <c r="D62" s="12">
-        <f>[58]Main!$D$3</f>
+        <f>[59]Main!$D$3</f>
         <v>1.68</v>
       </c>
       <c r="E62" s="8">
-        <f>[58]Main!$D$5</f>
+        <f>[59]Main!$D$5</f>
         <v>179.59200000000001</v>
       </c>
       <c r="F62" s="8">
-        <f>[58]Main!$D$8</f>
+        <f>[59]Main!$D$8</f>
         <v>51.599999999999994</v>
       </c>
       <c r="G62" s="8">
-        <f>[58]Main!$D$9</f>
+        <f>[59]Main!$D$9</f>
         <v>127.99200000000002</v>
       </c>
       <c r="H62" s="8">
-        <f>[58]Model!AD$16</f>
+        <f>[59]Model!AD$16</f>
         <v>-29.899999999999945</v>
       </c>
       <c r="I62" s="8">
-        <f>[58]Model!AE$16</f>
+        <f>[59]Model!AE$16</f>
         <v>-126.39400000000002</v>
       </c>
       <c r="J62" s="8">
-        <f>[58]Model!AF$16</f>
+        <f>[59]Model!AF$16</f>
         <v>-27.913519750000027</v>
       </c>
       <c r="K62" s="8">
-        <f>[58]Model!AG$16</f>
+        <f>[59]Model!AG$16</f>
         <v>-1.4263918424999869</v>
       </c>
       <c r="L62" s="8">
-        <f>[58]Model!AH$16</f>
+        <f>[59]Model!AH$16</f>
         <v>14.796638968349985</v>
       </c>
       <c r="M62" s="9">
@@ -16202,33 +16193,33 @@
       </c>
       <c r="R62" s="9"/>
       <c r="S62" s="10">
-        <f>[58]Model!$AE$3</f>
+        <f>[59]Model!$AE$3</f>
         <v>395.77499999999998</v>
       </c>
       <c r="T62" s="33">
-        <f t="shared" ref="T62:T67" si="19">G62/S62</f>
+        <f t="shared" ref="T62:T67" si="21">G62/S62</f>
         <v>0.32339586886488542</v>
       </c>
       <c r="U62" s="11">
-        <f>[58]Model!AC$20</f>
+        <f>[59]Model!AC$20</f>
         <v>-6.5727699530516381E-2</v>
       </c>
       <c r="V62" s="11">
-        <f>[58]Model!AD$20</f>
+        <f>[59]Model!AD$20</f>
         <v>-0.13791178112786151</v>
       </c>
       <c r="W62" s="34"/>
       <c r="X62" s="34"/>
       <c r="Y62" s="11">
-        <f>[58]Model!$AS$22</f>
+        <f>[59]Model!$AS$22</f>
         <v>0.12</v>
       </c>
       <c r="Z62" s="11">
-        <f>[58]Model!$AS$28</f>
+        <f>[59]Model!$AS$28</f>
         <v>0.16576302502726192</v>
       </c>
       <c r="AA62" s="7" t="str">
-        <f>[58]Model!$AS$29</f>
+        <f>[59]Model!$AS$29</f>
         <v>Undervalued</v>
       </c>
       <c r="AB62" s="7" t="s">
@@ -16238,11 +16229,11 @@
         <v>2005</v>
       </c>
       <c r="AE62" s="17">
-        <f>[58]Main!$E$3</f>
+        <f>[59]Main!$E$3</f>
         <v>45905</v>
       </c>
       <c r="AF62" s="17">
-        <f>[58]Main!$G$3</f>
+        <f>[59]Main!$G$3</f>
         <v>45964</v>
       </c>
     </row>
@@ -16254,90 +16245,90 @@
         <v>110</v>
       </c>
       <c r="D63" s="19">
-        <f>[59]Main!$D$3</f>
+        <f>[60]Main!$D$3</f>
         <v>1.27</v>
       </c>
       <c r="E63" s="8">
-        <f>[59]Main!$D$5</f>
+        <f>[60]Main!$D$5</f>
         <v>94.234000000000009</v>
       </c>
       <c r="F63" s="8">
-        <f>[59]Main!$D$8</f>
+        <f>[60]Main!$D$8</f>
         <v>-15.5</v>
       </c>
       <c r="G63" s="8">
-        <f>[59]Main!$D$9</f>
+        <f>[60]Main!$D$9</f>
         <v>109.73400000000001</v>
       </c>
       <c r="H63" s="8">
-        <f>[59]Model!T17</f>
+        <f>[60]Model!T17</f>
         <v>-76.160000000000011</v>
       </c>
       <c r="I63" s="8">
-        <f>[59]Model!U17</f>
+        <f>[60]Model!U17</f>
         <v>2.1120000000000005</v>
       </c>
       <c r="J63" s="8">
-        <f>[59]Model!V17</f>
+        <f>[60]Model!V17</f>
         <v>8.7361250000000013</v>
       </c>
       <c r="K63" s="8">
-        <f>[59]Model!W17</f>
+        <f>[60]Model!W17</f>
         <v>15.032579999999999</v>
       </c>
       <c r="L63" s="8">
-        <f>[59]Model!X17</f>
+        <f>[60]Model!X17</f>
         <v>20.612932799999989</v>
       </c>
       <c r="M63" s="9"/>
       <c r="N63" s="9">
-        <f>$G63/I63</f>
+        <f t="shared" ref="N63:Q64" si="22">$G63/I63</f>
         <v>51.957386363636353</v>
       </c>
       <c r="O63" s="9">
-        <f>$G63/J63</f>
+        <f t="shared" si="22"/>
         <v>12.560946643964</v>
       </c>
       <c r="P63" s="9">
-        <f>$G63/K63</f>
+        <f t="shared" si="22"/>
         <v>7.2997449539599994</v>
       </c>
       <c r="Q63" s="9">
-        <f>$G63/L63</f>
+        <f t="shared" si="22"/>
         <v>5.3235510475248855</v>
       </c>
       <c r="R63" s="9">
-        <f>G63/[59]Model!$AE$17</f>
+        <f>G63/[60]Model!$AE$17</f>
         <v>2.175916093374441</v>
       </c>
       <c r="S63" s="29">
-        <f>[59]Model!$T$3</f>
+        <f>[60]Model!$T$3</f>
         <v>46.9</v>
       </c>
       <c r="T63" s="32">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>2.3397441364605545</v>
       </c>
       <c r="U63" s="11">
-        <f>[59]Model!S$21</f>
+        <f>[60]Model!S$21</f>
         <v>2.4338235294117649</v>
       </c>
       <c r="V63" s="11">
-        <f>[59]Model!T$21</f>
+        <f>[60]Model!T$21</f>
         <v>4.2826552462524869E-3</v>
       </c>
       <c r="W63" s="34"/>
       <c r="X63" s="34"/>
       <c r="Y63" s="11">
-        <f>[59]Model!$AH$24</f>
+        <f>[60]Model!$AH$24</f>
         <v>0.12</v>
       </c>
       <c r="Z63" s="11">
-        <f>[59]Model!$AH$30</f>
+        <f>[60]Model!$AH$30</f>
         <v>0.51192284558708812</v>
       </c>
       <c r="AA63" s="7" t="str">
-        <f>[59]Model!$AH$31</f>
+        <f>[60]Model!$AH$31</f>
         <v>Heavily undervalued</v>
       </c>
       <c r="AB63" s="7" t="s">
@@ -16347,11 +16338,11 @@
         <v>2015</v>
       </c>
       <c r="AE63" s="17">
-        <f>[59]Main!$E$3</f>
+        <f>[60]Main!$E$3</f>
         <v>45751</v>
       </c>
       <c r="AF63" s="17">
-        <f>[59]Main!$G$3</f>
+        <f>[60]Main!$G$3</f>
         <v>45845</v>
       </c>
     </row>
@@ -16403,19 +16394,19 @@
         <v>-0.70209140201394282</v>
       </c>
       <c r="N64" s="9">
-        <f>$G64/I64</f>
+        <f t="shared" si="22"/>
         <v>-0.46483004779585235</v>
       </c>
       <c r="O64" s="9">
-        <f>$G64/J64</f>
+        <f t="shared" si="22"/>
         <v>-0.98378181837915879</v>
       </c>
       <c r="P64" s="9">
-        <f>$G64/K64</f>
+        <f t="shared" si="22"/>
         <v>-1.3544635019232438</v>
       </c>
       <c r="Q64" s="9">
-        <f>$G64/L64</f>
+        <f t="shared" si="22"/>
         <v>-1.962708265780426</v>
       </c>
       <c r="R64" s="9">
@@ -16481,87 +16472,87 @@
         <v>158</v>
       </c>
       <c r="D65" s="12">
-        <f>[60]Main!$D$3</f>
+        <f>[62]Main!$D$3</f>
         <v>5.79</v>
       </c>
       <c r="E65" s="8">
-        <f>[60]Main!$D$5</f>
+        <f>[62]Main!$D$5</f>
         <v>54.426000000000002</v>
       </c>
       <c r="F65" s="8">
-        <f>[60]Main!$D$8</f>
+        <f>[62]Main!$D$8</f>
         <v>20</v>
       </c>
       <c r="G65" s="8">
-        <f>[60]Main!$D$9</f>
+        <f>[62]Main!$D$9</f>
         <v>34.426000000000002</v>
       </c>
       <c r="H65" s="8">
-        <f>[60]Model!AC$12</f>
+        <f>[62]Model!AC$12</f>
         <v>-0.29201399999999977</v>
       </c>
       <c r="I65" s="8">
-        <f>[60]Model!AD$12</f>
+        <f>[62]Model!AD$12</f>
         <v>-2.4455999999972722E-4</v>
       </c>
       <c r="J65" s="8">
-        <f>[60]Model!AE$12</f>
+        <f>[62]Model!AE$12</f>
         <v>0.24468274320000027</v>
       </c>
       <c r="K65" s="8">
-        <f>[60]Model!AF$12</f>
+        <f>[62]Model!AF$12</f>
         <v>0.43762034426400065</v>
       </c>
       <c r="L65" s="8">
-        <f>[60]Model!AG$12</f>
+        <f>[62]Model!AG$12</f>
         <v>0.63253625788728018</v>
       </c>
       <c r="M65" s="9"/>
       <c r="N65" s="9"/>
       <c r="O65" s="9">
-        <f t="shared" ref="O65:Q65" si="20">$G65/J65</f>
+        <f t="shared" ref="O65:Q65" si="23">$G65/J65</f>
         <v>140.69647720052194</v>
       </c>
       <c r="P65" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>78.666361039266562</v>
       </c>
       <c r="Q65" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>54.425338580566894</v>
       </c>
       <c r="R65" s="9">
-        <f>G65/[60]Model!$AL$12</f>
+        <f>G65/[62]Model!$AL$12</f>
         <v>21.005959850183736</v>
       </c>
       <c r="S65" s="29">
-        <f>[60]Model!$AA$3</f>
+        <f>[62]Model!$AA$3</f>
         <v>12.3</v>
       </c>
       <c r="T65" s="32">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>2.7988617886178861</v>
       </c>
       <c r="U65" s="11">
-        <f>[60]Model!AA$16</f>
+        <f>[62]Model!AA$16</f>
         <v>-6.1068702290076216E-2</v>
       </c>
       <c r="V65" s="11">
-        <f>[60]Model!AB$16</f>
+        <f>[62]Model!AB$16</f>
         <v>3.9837398373983701E-2</v>
       </c>
       <c r="W65" s="11"/>
       <c r="X65" s="11"/>
       <c r="Y65" s="11">
-        <f>[60]Model!$AO$18</f>
+        <f>[62]Model!$AO$18</f>
         <v>0.13</v>
       </c>
       <c r="Z65" s="11">
-        <f>[60]Model!$AO$24</f>
+        <f>[62]Model!$AO$24</f>
         <v>-0.54344337476902149</v>
       </c>
       <c r="AA65" s="7" t="str">
-        <f>[60]Model!$AO$25</f>
+        <f>[62]Model!$AO$25</f>
         <v>Heavily overvalued</v>
       </c>
       <c r="AB65" s="7" t="s">
@@ -16571,11 +16562,11 @@
         <v>1958</v>
       </c>
       <c r="AE65" s="17">
-        <f>[60]Main!$E$3</f>
+        <f>[62]Main!$E$3</f>
         <v>45817</v>
       </c>
       <c r="AF65" s="17">
-        <f>[60]Main!$G$3</f>
+        <f>[62]Main!$G$3</f>
         <v>45785</v>
       </c>
     </row>
@@ -16587,39 +16578,39 @@
         <v>170</v>
       </c>
       <c r="D66" s="12">
-        <f>[62]Main!$D$3</f>
+        <f>[63]Main!$D$3</f>
         <v>4.4400000000000004</v>
       </c>
       <c r="E66" s="8">
-        <f>[62]Main!$D$5</f>
+        <f>[63]Main!$D$5</f>
         <v>43.067999999999998</v>
       </c>
       <c r="F66" s="8">
-        <f>[62]Main!$D$10</f>
+        <f>[63]Main!$D$10</f>
         <v>140.4951856946355</v>
       </c>
       <c r="G66" s="8">
-        <f>[62]Main!$D$11</f>
+        <f>[63]Main!$D$11</f>
         <v>-97.427185694635497</v>
       </c>
       <c r="H66" s="8">
-        <f>[62]Model!O$23</f>
+        <f>[63]Model!O$23</f>
         <v>-65.195625000000021</v>
       </c>
       <c r="I66" s="8">
-        <f>[62]Model!P$23</f>
+        <f>[63]Model!P$23</f>
         <v>-75.811683750000014</v>
       </c>
       <c r="J66" s="8">
-        <f>[62]Model!Q$23</f>
+        <f>[63]Model!Q$23</f>
         <v>-85.133768362500035</v>
       </c>
       <c r="K66" s="8">
-        <f>[62]Model!R$23</f>
+        <f>[63]Model!R$23</f>
         <v>-92.999013768375065</v>
       </c>
       <c r="L66" s="8">
-        <f>[62]Model!S$23</f>
+        <f>[63]Model!S$23</f>
         <v>-99.507942011156317</v>
       </c>
       <c r="M66" s="9"/>
@@ -16637,37 +16628,37 @@
         <v>0</v>
       </c>
       <c r="R66" s="9">
-        <f>E66/[62]Model!$Z$23</f>
+        <f>E66/[63]Model!$Z$23</f>
         <v>-0.35493594328342115</v>
       </c>
       <c r="S66" s="29">
-        <f>[62]Model!$O$5</f>
+        <f>[63]Model!$O$5</f>
         <v>334.37624999999997</v>
       </c>
       <c r="T66" s="32">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-0.29136993340476636</v>
       </c>
       <c r="U66" s="11">
-        <f>[62]Model!N$27</f>
+        <f>[63]Model!N$27</f>
         <v>-5.0000000000000044E-2</v>
       </c>
       <c r="V66" s="11">
-        <f>[62]Model!O$27</f>
+        <f>[63]Model!O$27</f>
         <v>-0.35</v>
       </c>
       <c r="W66" s="11"/>
       <c r="X66" s="11"/>
       <c r="Y66" s="11">
-        <f>[62]Model!$AA$30</f>
+        <f>[63]Model!$AA$30</f>
         <v>0.15</v>
       </c>
       <c r="Z66" s="11">
-        <f>[62]Model!$AA$37</f>
+        <f>[63]Model!$AA$37</f>
         <v>0.42025776126590375</v>
       </c>
       <c r="AA66" s="7" t="str">
-        <f>[62]Model!$AA$38</f>
+        <f>[63]Model!$AA$38</f>
         <v>Undervalued</v>
       </c>
       <c r="AB66" s="7" t="s">
@@ -16677,11 +16668,11 @@
         <v>2018</v>
       </c>
       <c r="AE66" s="17">
-        <f>[62]Main!$E$3</f>
+        <f>[63]Main!$E$3</f>
         <v>45780</v>
       </c>
       <c r="AF66" s="17" t="str">
-        <f>[62]Main!$G$3</f>
+        <f>[63]Main!$G$3</f>
         <v>?</v>
       </c>
     </row>
@@ -16693,39 +16684,39 @@
         <v>107</v>
       </c>
       <c r="D67" s="12">
-        <f>[63]Main!$D$3</f>
+        <f>[64]Main!$D$3</f>
         <v>4.07</v>
       </c>
       <c r="E67" s="8">
-        <f>[63]Main!$D$5</f>
+        <f>[64]Main!$D$5</f>
         <v>71.632000000000005</v>
       </c>
       <c r="F67" s="8">
-        <f>[63]Main!$D$8</f>
+        <f>[64]Main!$D$8</f>
         <v>239</v>
       </c>
       <c r="G67" s="8">
-        <f>[63]Main!$D$9</f>
+        <f>[64]Main!$D$9</f>
         <v>-167.36799999999999</v>
       </c>
       <c r="H67" s="8">
-        <f>[63]Model!AI14</f>
+        <f>[64]Model!AI14</f>
         <v>-93.9</v>
       </c>
       <c r="I67" s="8">
-        <f>[63]Model!AJ14</f>
+        <f>[64]Model!AJ14</f>
         <v>-59.968500000000006</v>
       </c>
       <c r="J67" s="8">
-        <f>[63]Model!AK14</f>
+        <f>[64]Model!AK14</f>
         <v>-42.065130000000011</v>
       </c>
       <c r="K67" s="8">
-        <f>[63]Model!AL14</f>
+        <f>[64]Model!AL14</f>
         <v>-29.314150250000012</v>
       </c>
       <c r="L67" s="8">
-        <f>[63]Model!AM14</f>
+        <f>[64]Model!AM14</f>
         <v>-18.632540500000005</v>
       </c>
       <c r="M67" s="9">
@@ -16749,37 +16740,37 @@
         <v>8.9825646695897401</v>
       </c>
       <c r="R67" s="9">
-        <f>E67/[63]Model!$AS$14</f>
+        <f>E67/[64]Model!$AS$14</f>
         <v>102.72857629268252</v>
       </c>
       <c r="S67" s="29">
-        <f>[63]Model!$AI$3</f>
+        <f>[64]Model!$AI$3</f>
         <v>95.5</v>
       </c>
       <c r="T67" s="32">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-1.752544502617801</v>
       </c>
       <c r="U67" s="11">
-        <f>[63]Model!AH$18</f>
+        <f>[64]Model!AH$18</f>
         <v>-0.43604004449388212</v>
       </c>
       <c r="V67" s="11">
-        <f>[63]Model!AI$18</f>
+        <f>[64]Model!AI$18</f>
         <v>-0.37212360289283364</v>
       </c>
       <c r="W67" s="11"/>
       <c r="X67" s="11"/>
       <c r="Y67" s="11">
-        <f>[63]Model!$AW$21</f>
+        <f>[64]Model!$AW$21</f>
         <v>0.12</v>
       </c>
       <c r="Z67" s="11">
-        <f>[63]Model!$AW$27</f>
+        <f>[64]Model!$AW$27</f>
         <v>-0.52302112324583339</v>
       </c>
       <c r="AA67" s="7" t="str">
-        <f>[63]Model!$AW$28</f>
+        <f>[64]Model!$AW$28</f>
         <v>Heavily overvalued</v>
       </c>
       <c r="AB67" s="7" t="s">
@@ -16789,11 +16780,11 @@
         <v>2012</v>
       </c>
       <c r="AE67" s="17">
-        <f>[63]Main!$E$3</f>
+        <f>[64]Main!$E$3</f>
         <v>45751</v>
       </c>
       <c r="AF67" s="17">
-        <f>[63]Main!$G$3</f>
+        <f>[64]Main!$G$3</f>
         <v>45777</v>
       </c>
     </row>

--- a/Financial Analysis/Models (Tech).xlsx
+++ b/Financial Analysis/Models (Tech).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70233AB3-6BDC-4E20-A004-5ABDC1E421D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83A3A06-5C69-4430-B45B-D2E692D12BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4E122305-8C8A-4700-8BB3-18DD9512A165}"/>
   </bookViews>
@@ -9088,8 +9088,8 @@
           <cell r="BD27">
             <v>14997</v>
           </cell>
-          <cell r="BK27">
-            <v>12025.222429994654</v>
+          <cell r="BP27">
+            <v>16921.027572149789</v>
           </cell>
         </row>
         <row r="31">
@@ -10591,8 +10591,8 @@
         <v>92.158801093552043</v>
       </c>
       <c r="R10" s="9">
-        <f>G10/[7]Model!$BK$27</f>
-        <v>114.93388567620985</v>
+        <f>G10/[7]Model!$BP$27</f>
+        <v>81.679764075013907</v>
       </c>
       <c r="S10" s="10">
         <f>[7]Model!$BF$9</f>
